--- a/data/cluster.xlsx
+++ b/data/cluster.xlsx
@@ -376,7 +376,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CL29"/>
+  <dimension ref="A1:CL31"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -694,7 +694,7 @@
         <v>1</v>
       </c>
       <c r="R2">
-        <v>28.38</v>
+        <v>4.29</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -704,21 +704,18 @@
       </c>
       <c r="U2">
         <v>0</v>
-      </c>
-      <c r="V2">
-        <v>-69.37</v>
       </c>
       <c r="W2">
         <v>3.81</v>
       </c>
       <c r="X2">
-        <v>24.62</v>
+        <v>0.48</v>
       </c>
       <c r="AA2">
-        <v>-69.37</v>
+        <v>0</v>
       </c>
       <c r="AB2">
-        <v>-69.37</v>
+        <v>0</v>
       </c>
       <c r="AC2">
         <v>0</v>
@@ -739,25 +736,25 @@
         <v>0</v>
       </c>
       <c r="AI2">
-        <v>24.62</v>
+        <v>0.48</v>
       </c>
       <c r="AJ2">
-        <v>24.62</v>
+        <v>0.48</v>
       </c>
       <c r="AK2">
-        <v>23.64</v>
+        <v>0</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>23.64</v>
+        <v>0</v>
       </c>
       <c r="AR2">
-        <v>-69.37</v>
+        <v>0</v>
       </c>
       <c r="AS2">
-        <v>-69.37</v>
+        <v>0</v>
       </c>
       <c r="AT2">
         <v>0</v>
@@ -772,19 +769,19 @@
         <v>0</v>
       </c>
       <c r="AX2">
-        <v>24.62</v>
+        <v>0.48</v>
       </c>
       <c r="AY2">
-        <v>24.62</v>
+        <v>0.48</v>
       </c>
       <c r="AZ2">
-        <v>23.64</v>
+        <v>0</v>
       </c>
       <c r="BA2">
-        <v>-69.37</v>
+        <v>0</v>
       </c>
       <c r="BB2">
-        <v>-69.37</v>
+        <v>0</v>
       </c>
       <c r="BC2">
         <v>0</v>
@@ -799,19 +796,19 @@
         <v>0</v>
       </c>
       <c r="BG2">
-        <v>24.62</v>
+        <v>0.48</v>
       </c>
       <c r="BH2">
-        <v>24.62</v>
+        <v>0.48</v>
       </c>
       <c r="BI2">
-        <v>23.64</v>
+        <v>0</v>
       </c>
       <c r="BJ2">
-        <v>-69.37</v>
+        <v>0</v>
       </c>
       <c r="BK2">
-        <v>-69.37</v>
+        <v>0</v>
       </c>
       <c r="BL2">
         <v>0</v>
@@ -826,19 +823,19 @@
         <v>0</v>
       </c>
       <c r="BP2">
-        <v>24.62</v>
+        <v>0.48</v>
       </c>
       <c r="BQ2">
-        <v>24.62</v>
+        <v>0.48</v>
       </c>
       <c r="BR2">
-        <v>23.64</v>
+        <v>0</v>
       </c>
       <c r="BS2">
-        <v>175</v>
+        <v>80.42</v>
       </c>
       <c r="BT2">
-        <v>0.77</v>
+        <v>0</v>
       </c>
       <c r="BU2">
         <v>0</v>
@@ -850,10 +847,10 @@
         <v>0</v>
       </c>
       <c r="BX2">
-        <v>175.77</v>
+        <v>80.42</v>
       </c>
       <c r="BY2">
-        <v>265.1</v>
+        <v>265.34</v>
       </c>
       <c r="BZ2">
         <v>0.77</v>
@@ -868,10 +865,10 @@
         <v>0</v>
       </c>
       <c r="CD2">
-        <v>265.87</v>
+        <v>266.11</v>
       </c>
       <c r="CE2">
-        <v>394.17</v>
+        <v>383.12</v>
       </c>
       <c r="CF2">
         <v>0.77</v>
@@ -886,13 +883,13 @@
         <v>0</v>
       </c>
       <c r="CJ2">
-        <v>394.94</v>
+        <v>383.89</v>
       </c>
       <c r="CK2">
-        <v>1430.8196721311</v>
+        <v>1422.1204188482</v>
       </c>
       <c r="CL2">
-        <v>1479.3220338983</v>
+        <v>1474.4698897371</v>
       </c>
     </row>
     <row r="3">
@@ -942,31 +939,31 @@
         <v>1</v>
       </c>
       <c r="R3">
-        <v>11678.87</v>
+        <v>11673.15</v>
       </c>
       <c r="S3">
-        <v>5003.18</v>
+        <v>4922.05</v>
       </c>
       <c r="T3">
-        <v>6668.33</v>
+        <v>6739.38</v>
       </c>
       <c r="U3">
         <v>0</v>
       </c>
       <c r="V3">
-        <v>-182.27</v>
+        <v>189.24</v>
       </c>
       <c r="W3">
         <v>0.13</v>
       </c>
       <c r="Y3">
-        <v>7.33</v>
+        <v>11.44</v>
       </c>
       <c r="AA3">
-        <v>-182.27</v>
+        <v>189.24</v>
       </c>
       <c r="AB3">
-        <v>-182.27</v>
+        <v>189.24</v>
       </c>
       <c r="AC3">
         <v>0</v>
@@ -1002,10 +999,10 @@
         <v>0</v>
       </c>
       <c r="AR3">
-        <v>-182.27</v>
+        <v>189.24</v>
       </c>
       <c r="AS3">
-        <v>-182.27</v>
+        <v>189.24</v>
       </c>
       <c r="AT3">
         <v>0</v>
@@ -1029,10 +1026,10 @@
         <v>0</v>
       </c>
       <c r="BA3">
-        <v>-182.27</v>
+        <v>189.24</v>
       </c>
       <c r="BB3">
-        <v>-182.27</v>
+        <v>189.24</v>
       </c>
       <c r="BC3">
         <v>0</v>
@@ -1056,10 +1053,10 @@
         <v>0</v>
       </c>
       <c r="BJ3">
-        <v>-182.27</v>
+        <v>189.24</v>
       </c>
       <c r="BK3">
-        <v>-182.27</v>
+        <v>189.24</v>
       </c>
       <c r="BL3">
         <v>0</v>
@@ -1083,10 +1080,10 @@
         <v>0</v>
       </c>
       <c r="BS3">
-        <v>70.25</v>
+        <v>66.18</v>
       </c>
       <c r="BT3">
-        <v>6.91</v>
+        <v>8.72</v>
       </c>
       <c r="BU3">
         <v>0</v>
@@ -1098,13 +1095,13 @@
         <v>0.01</v>
       </c>
       <c r="BX3">
-        <v>77.17</v>
+        <v>74.91</v>
       </c>
       <c r="BY3">
-        <v>73.14</v>
+        <v>70.25</v>
       </c>
       <c r="BZ3">
-        <v>11.65</v>
+        <v>13.63</v>
       </c>
       <c r="CA3">
         <v>0</v>
@@ -1116,13 +1113,13 @@
         <v>0.02</v>
       </c>
       <c r="CD3">
-        <v>84.81</v>
+        <v>83.9</v>
       </c>
       <c r="CE3">
         <v>90.79</v>
       </c>
       <c r="CF3">
-        <v>17.27</v>
+        <v>20.41</v>
       </c>
       <c r="CG3">
         <v>0</v>
@@ -1131,16 +1128,16 @@
         <v>0</v>
       </c>
       <c r="CI3">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="CJ3">
-        <v>108.08</v>
+        <v>111.23</v>
       </c>
       <c r="CK3">
-        <v>1430.8196721311</v>
+        <v>1422.1204188482</v>
       </c>
       <c r="CL3">
-        <v>1479.3220338983</v>
+        <v>1474.4698897371</v>
       </c>
     </row>
     <row r="4">
@@ -1325,10 +1322,10 @@
         <v>0</v>
       </c>
       <c r="CK4">
-        <v>1430.8196721311</v>
+        <v>1422.1204188482</v>
       </c>
       <c r="CL4">
-        <v>1479.3220338983</v>
+        <v>1474.4698897371</v>
       </c>
     </row>
     <row r="5">
@@ -1375,34 +1372,34 @@
         <v>1</v>
       </c>
       <c r="R5">
-        <v>14672.25</v>
+        <v>14733.16</v>
       </c>
       <c r="S5">
-        <v>6856.71</v>
+        <v>6735.59</v>
       </c>
       <c r="T5">
-        <v>7773.5</v>
+        <v>7950.13</v>
       </c>
       <c r="U5">
         <v>0</v>
       </c>
       <c r="V5">
-        <v>57969.3</v>
+        <v>59702.2</v>
       </c>
       <c r="W5">
         <v>0.13</v>
       </c>
       <c r="Y5">
-        <v>1.39</v>
+        <v>5.29</v>
       </c>
       <c r="AA5">
-        <v>57969.3</v>
+        <v>59702.2</v>
       </c>
       <c r="AB5">
-        <v>57969.3</v>
+        <v>59702.2</v>
       </c>
       <c r="AC5">
-        <v>51415.73</v>
+        <v>51113.74</v>
       </c>
       <c r="AD5">
         <v>0.13</v>
@@ -1435,13 +1432,13 @@
         <v>0</v>
       </c>
       <c r="AR5">
-        <v>57969.3</v>
+        <v>59702.2</v>
       </c>
       <c r="AS5">
-        <v>57969.3</v>
+        <v>59702.2</v>
       </c>
       <c r="AT5">
-        <v>51415.73</v>
+        <v>51113.74</v>
       </c>
       <c r="AU5">
         <v>0.13</v>
@@ -1462,13 +1459,13 @@
         <v>0</v>
       </c>
       <c r="BA5">
-        <v>57969.3</v>
+        <v>59702.2</v>
       </c>
       <c r="BB5">
-        <v>57969.3</v>
+        <v>59702.2</v>
       </c>
       <c r="BC5">
-        <v>51415.73</v>
+        <v>51113.74</v>
       </c>
       <c r="BD5">
         <v>0.13</v>
@@ -1489,13 +1486,13 @@
         <v>0</v>
       </c>
       <c r="BJ5">
-        <v>57969.3</v>
+        <v>59702.2</v>
       </c>
       <c r="BK5">
-        <v>57969.3</v>
+        <v>59702.2</v>
       </c>
       <c r="BL5">
-        <v>51415.73</v>
+        <v>51113.74</v>
       </c>
       <c r="BM5">
         <v>0.13</v>
@@ -1519,7 +1516,7 @@
         <v>104.15</v>
       </c>
       <c r="BT5">
-        <v>11.95</v>
+        <v>19.41</v>
       </c>
       <c r="BU5">
         <v>0</v>
@@ -1528,16 +1525,16 @@
         <v>0</v>
       </c>
       <c r="BW5">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="BX5">
-        <v>116.1</v>
+        <v>123.57</v>
       </c>
       <c r="BY5">
         <v>104.15</v>
       </c>
       <c r="BZ5">
-        <v>13.69</v>
+        <v>21.19</v>
       </c>
       <c r="CA5">
         <v>0</v>
@@ -1546,16 +1543,16 @@
         <v>0</v>
       </c>
       <c r="CC5">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="CD5">
-        <v>117.85</v>
+        <v>125.36</v>
       </c>
       <c r="CE5">
         <v>128.35</v>
       </c>
       <c r="CF5">
-        <v>16.93</v>
+        <v>24.87</v>
       </c>
       <c r="CG5">
         <v>0</v>
@@ -1564,16 +1561,16 @@
         <v>0</v>
       </c>
       <c r="CI5">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="CJ5">
-        <v>145.29</v>
+        <v>153.24</v>
       </c>
       <c r="CK5">
-        <v>1430.8196721311</v>
+        <v>1422.1204188482</v>
       </c>
       <c r="CL5">
-        <v>1479.3220338983</v>
+        <v>1474.4698897371</v>
       </c>
     </row>
     <row r="6">
@@ -1620,43 +1617,43 @@
         <v>1</v>
       </c>
       <c r="R6">
-        <v>5940.04</v>
+        <v>3492.26</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
       <c r="T6">
-        <v>5713.69</v>
+        <v>3465.16</v>
       </c>
       <c r="U6">
         <v>0</v>
       </c>
       <c r="V6">
-        <v>-5.17</v>
+        <v>-80.29</v>
       </c>
       <c r="W6">
-        <v>226.36</v>
+        <v>27.15</v>
       </c>
       <c r="AA6">
-        <v>-5.17</v>
+        <v>-80.29</v>
       </c>
       <c r="AB6">
-        <v>-5.17</v>
+        <v>-80.29</v>
       </c>
       <c r="AC6">
         <v>0</v>
       </c>
       <c r="AD6">
-        <v>226.36</v>
+        <v>27.15</v>
       </c>
       <c r="AE6">
-        <v>226.36</v>
+        <v>27.15</v>
       </c>
       <c r="AF6">
         <v>0</v>
       </c>
       <c r="AG6">
-        <v>899.6</v>
+        <v>699.6</v>
       </c>
       <c r="AH6">
         <v>0</v>
@@ -1677,19 +1674,19 @@
         <v>0</v>
       </c>
       <c r="AR6">
-        <v>-5.17</v>
+        <v>-80.29</v>
       </c>
       <c r="AS6">
-        <v>-5.17</v>
+        <v>-80.29</v>
       </c>
       <c r="AT6">
         <v>0</v>
       </c>
       <c r="AU6">
-        <v>226.36</v>
+        <v>27.15</v>
       </c>
       <c r="AV6">
-        <v>226.36</v>
+        <v>27.15</v>
       </c>
       <c r="AW6">
         <v>0</v>
@@ -1704,19 +1701,19 @@
         <v>0</v>
       </c>
       <c r="BA6">
-        <v>-5.17</v>
+        <v>-80.29</v>
       </c>
       <c r="BB6">
-        <v>-5.17</v>
+        <v>-80.29</v>
       </c>
       <c r="BC6">
         <v>0</v>
       </c>
       <c r="BD6">
-        <v>226.36</v>
+        <v>27.15</v>
       </c>
       <c r="BE6">
-        <v>226.36</v>
+        <v>27.15</v>
       </c>
       <c r="BF6">
         <v>0</v>
@@ -1731,19 +1728,19 @@
         <v>0</v>
       </c>
       <c r="BJ6">
-        <v>-5.17</v>
+        <v>-80.29</v>
       </c>
       <c r="BK6">
-        <v>-5.17</v>
+        <v>-80.29</v>
       </c>
       <c r="BL6">
         <v>0</v>
       </c>
       <c r="BM6">
-        <v>226.36</v>
+        <v>27.15</v>
       </c>
       <c r="BN6">
-        <v>226.36</v>
+        <v>27.15</v>
       </c>
       <c r="BO6">
         <v>0</v>
@@ -1758,10 +1755,10 @@
         <v>0</v>
       </c>
       <c r="BS6">
-        <v>8.46</v>
+        <v>31.15</v>
       </c>
       <c r="BT6">
-        <v>4.47</v>
+        <v>5.39</v>
       </c>
       <c r="BU6">
         <v>0</v>
@@ -1773,13 +1770,13 @@
         <v>0</v>
       </c>
       <c r="BX6">
-        <v>12.93</v>
+        <v>36.54</v>
       </c>
       <c r="BY6">
-        <v>43.62</v>
+        <v>34.49</v>
       </c>
       <c r="BZ6">
-        <v>9.4</v>
+        <v>8.53</v>
       </c>
       <c r="CA6">
         <v>0</v>
@@ -1791,13 +1788,13 @@
         <v>0</v>
       </c>
       <c r="CD6">
-        <v>53.02</v>
+        <v>43.02</v>
       </c>
       <c r="CE6">
-        <v>86.31</v>
+        <v>109</v>
       </c>
       <c r="CF6">
-        <v>22.06</v>
+        <v>23.73</v>
       </c>
       <c r="CG6">
         <v>0</v>
@@ -1809,13 +1806,13 @@
         <v>0</v>
       </c>
       <c r="CJ6">
-        <v>108.37</v>
+        <v>132.73</v>
       </c>
       <c r="CK6">
-        <v>1430.8196721311</v>
+        <v>1422.1204188482</v>
       </c>
       <c r="CL6">
-        <v>1479.3220338983</v>
+        <v>1474.4698897371</v>
       </c>
     </row>
     <row r="7">
@@ -1862,13 +1859,13 @@
         <v>1</v>
       </c>
       <c r="R7">
-        <v>5019.82</v>
+        <v>5049.3</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
       <c r="T7">
-        <v>5012.52</v>
+        <v>5041.96</v>
       </c>
       <c r="U7">
         <v>0</v>
@@ -2000,7 +1997,7 @@
         <v>0</v>
       </c>
       <c r="BT7">
-        <v>2.66</v>
+        <v>5.26</v>
       </c>
       <c r="BU7">
         <v>0</v>
@@ -2012,13 +2009,13 @@
         <v>0</v>
       </c>
       <c r="BX7">
-        <v>2.66</v>
+        <v>5.26</v>
       </c>
       <c r="BY7">
         <v>0</v>
       </c>
       <c r="BZ7">
-        <v>2.66</v>
+        <v>5.26</v>
       </c>
       <c r="CA7">
         <v>0</v>
@@ -2030,13 +2027,13 @@
         <v>0</v>
       </c>
       <c r="CD7">
-        <v>2.66</v>
+        <v>5.26</v>
       </c>
       <c r="CE7">
         <v>0</v>
       </c>
       <c r="CF7">
-        <v>2.66</v>
+        <v>5.26</v>
       </c>
       <c r="CG7">
         <v>0</v>
@@ -2048,13 +2045,13 @@
         <v>0</v>
       </c>
       <c r="CJ7">
-        <v>2.66</v>
+        <v>5.26</v>
       </c>
       <c r="CK7">
-        <v>1430.8196721311</v>
+        <v>1422.1204188482</v>
       </c>
       <c r="CL7">
-        <v>1479.3220338983</v>
+        <v>1474.4698897371</v>
       </c>
     </row>
     <row r="8">
@@ -2101,13 +2098,13 @@
         <v>1</v>
       </c>
       <c r="R8">
-        <v>5016.59</v>
+        <v>5061.23</v>
       </c>
       <c r="S8">
         <v>0</v>
       </c>
       <c r="T8">
-        <v>5016.59</v>
+        <v>5061.23</v>
       </c>
       <c r="U8">
         <v>0</v>
@@ -2116,7 +2113,7 @@
         <v>0</v>
       </c>
       <c r="BT8">
-        <v>1.81</v>
+        <v>3.42</v>
       </c>
       <c r="BU8">
         <v>0</v>
@@ -2128,13 +2125,13 @@
         <v>0</v>
       </c>
       <c r="BX8">
-        <v>1.81</v>
+        <v>3.42</v>
       </c>
       <c r="BY8">
         <v>0</v>
       </c>
       <c r="BZ8">
-        <v>1.81</v>
+        <v>3.42</v>
       </c>
       <c r="CA8">
         <v>0</v>
@@ -2146,13 +2143,13 @@
         <v>0</v>
       </c>
       <c r="CD8">
-        <v>1.81</v>
+        <v>3.42</v>
       </c>
       <c r="CE8">
         <v>0</v>
       </c>
       <c r="CF8">
-        <v>1.81</v>
+        <v>3.42</v>
       </c>
       <c r="CG8">
         <v>0</v>
@@ -2164,13 +2161,13 @@
         <v>0</v>
       </c>
       <c r="CJ8">
-        <v>1.81</v>
+        <v>3.42</v>
       </c>
       <c r="CK8">
-        <v>1430.8196721311</v>
+        <v>1422.1204188482</v>
       </c>
       <c r="CL8">
-        <v>1479.3220338983</v>
+        <v>1474.4698897371</v>
       </c>
     </row>
     <row r="9">
@@ -2217,40 +2214,40 @@
         <v>1</v>
       </c>
       <c r="R9">
-        <v>2343.73</v>
+        <v>2648.89</v>
       </c>
       <c r="S9">
-        <v>209.67</v>
+        <v>208.49</v>
       </c>
       <c r="T9">
-        <v>2131.97</v>
+        <v>1739.52</v>
       </c>
       <c r="U9">
         <v>0</v>
       </c>
       <c r="V9">
-        <v>924.08</v>
+        <v>183.71</v>
       </c>
       <c r="W9">
-        <v>1</v>
+        <v>700.31</v>
       </c>
       <c r="Y9">
         <v>0.44</v>
       </c>
       <c r="AA9">
-        <v>924.08</v>
+        <v>183.71</v>
       </c>
       <c r="AB9">
-        <v>924.08</v>
+        <v>183.71</v>
       </c>
       <c r="AC9">
         <v>0</v>
       </c>
       <c r="AD9">
-        <v>1</v>
+        <v>700.31</v>
       </c>
       <c r="AE9">
-        <v>1</v>
+        <v>700.31</v>
       </c>
       <c r="AF9">
         <v>0</v>
@@ -2277,19 +2274,19 @@
         <v>0</v>
       </c>
       <c r="AR9">
-        <v>924.08</v>
+        <v>183.71</v>
       </c>
       <c r="AS9">
-        <v>924.08</v>
+        <v>183.71</v>
       </c>
       <c r="AT9">
         <v>0</v>
       </c>
       <c r="AU9">
-        <v>1</v>
+        <v>700.31</v>
       </c>
       <c r="AV9">
-        <v>1</v>
+        <v>700.31</v>
       </c>
       <c r="AW9">
         <v>0</v>
@@ -2304,19 +2301,19 @@
         <v>0</v>
       </c>
       <c r="BA9">
-        <v>924.08</v>
+        <v>183.71</v>
       </c>
       <c r="BB9">
-        <v>924.08</v>
+        <v>183.71</v>
       </c>
       <c r="BC9">
         <v>0</v>
       </c>
       <c r="BD9">
-        <v>1</v>
+        <v>700.31</v>
       </c>
       <c r="BE9">
-        <v>1</v>
+        <v>700.31</v>
       </c>
       <c r="BF9">
         <v>0</v>
@@ -2331,19 +2328,19 @@
         <v>0</v>
       </c>
       <c r="BJ9">
-        <v>924.08</v>
+        <v>183.71</v>
       </c>
       <c r="BK9">
-        <v>924.08</v>
+        <v>183.71</v>
       </c>
       <c r="BL9">
         <v>0</v>
       </c>
       <c r="BM9">
-        <v>1</v>
+        <v>700.31</v>
       </c>
       <c r="BN9">
-        <v>1</v>
+        <v>700.31</v>
       </c>
       <c r="BO9">
         <v>0</v>
@@ -2358,10 +2355,10 @@
         <v>0</v>
       </c>
       <c r="BS9">
-        <v>38.99</v>
+        <v>50.91</v>
       </c>
       <c r="BT9">
-        <v>7.19</v>
+        <v>5.79</v>
       </c>
       <c r="BU9">
         <v>0</v>
@@ -2373,13 +2370,13 @@
         <v>0</v>
       </c>
       <c r="BX9">
-        <v>46.18</v>
+        <v>56.7</v>
       </c>
       <c r="BY9">
-        <v>107.61</v>
+        <v>115.99</v>
       </c>
       <c r="BZ9">
-        <v>9.47</v>
+        <v>10.38</v>
       </c>
       <c r="CA9">
         <v>0</v>
@@ -2391,13 +2388,13 @@
         <v>0.43</v>
       </c>
       <c r="CD9">
-        <v>117.51</v>
+        <v>126.8</v>
       </c>
       <c r="CE9">
-        <v>171.88</v>
+        <v>184.99</v>
       </c>
       <c r="CF9">
-        <v>11.5</v>
+        <v>11.84</v>
       </c>
       <c r="CG9">
         <v>0</v>
@@ -2409,13 +2406,13 @@
         <v>0.52</v>
       </c>
       <c r="CJ9">
-        <v>183.9</v>
+        <v>197.35</v>
       </c>
       <c r="CK9">
-        <v>1430.8196721311</v>
+        <v>1422.1204188482</v>
       </c>
       <c r="CL9">
-        <v>1479.3220338983</v>
+        <v>1474.4698897371</v>
       </c>
     </row>
     <row r="10">
@@ -2462,19 +2459,19 @@
         <v>1</v>
       </c>
       <c r="R10">
-        <v>20910.05</v>
+        <v>21109.46</v>
       </c>
       <c r="S10">
-        <v>7041.64</v>
+        <v>6755.11</v>
       </c>
       <c r="T10">
-        <v>13796.36</v>
+        <v>13928.57</v>
       </c>
       <c r="U10">
         <v>0</v>
       </c>
       <c r="V10">
-        <v>14997.88</v>
+        <v>514256.26</v>
       </c>
       <c r="W10">
         <v>33.49</v>
@@ -2483,13 +2480,13 @@
         <v>18.22</v>
       </c>
       <c r="Y10">
-        <v>9.87</v>
+        <v>12.48</v>
       </c>
       <c r="AA10">
-        <v>14997.88</v>
+        <v>514256.26</v>
       </c>
       <c r="AB10">
-        <v>14997.88</v>
+        <v>514256.26</v>
       </c>
       <c r="AC10">
         <v>0</v>
@@ -2501,13 +2498,13 @@
         <v>33.49</v>
       </c>
       <c r="AF10">
-        <v>33.49</v>
+        <v>0</v>
       </c>
       <c r="AG10">
         <v>0</v>
       </c>
       <c r="AH10">
-        <v>33.49</v>
+        <v>0</v>
       </c>
       <c r="AI10">
         <v>18.22</v>
@@ -2525,10 +2522,10 @@
         <v>0</v>
       </c>
       <c r="AR10">
-        <v>14997.88</v>
+        <v>514256.26</v>
       </c>
       <c r="AS10">
-        <v>14997.88</v>
+        <v>514256.26</v>
       </c>
       <c r="AT10">
         <v>0</v>
@@ -2540,7 +2537,7 @@
         <v>33.49</v>
       </c>
       <c r="AW10">
-        <v>33.49</v>
+        <v>0</v>
       </c>
       <c r="AX10">
         <v>18.22</v>
@@ -2552,10 +2549,10 @@
         <v>0</v>
       </c>
       <c r="BA10">
-        <v>14997.88</v>
+        <v>514256.26</v>
       </c>
       <c r="BB10">
-        <v>14997.88</v>
+        <v>514256.26</v>
       </c>
       <c r="BC10">
         <v>0</v>
@@ -2567,7 +2564,7 @@
         <v>33.49</v>
       </c>
       <c r="BF10">
-        <v>33.49</v>
+        <v>0</v>
       </c>
       <c r="BG10">
         <v>18.22</v>
@@ -2579,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="BJ10">
-        <v>14997.88</v>
+        <v>514256.26</v>
       </c>
       <c r="BK10">
-        <v>14997.88</v>
+        <v>514256.26</v>
       </c>
       <c r="BL10">
         <v>0</v>
@@ -2594,7 +2591,7 @@
         <v>33.49</v>
       </c>
       <c r="BO10">
-        <v>33.49</v>
+        <v>0</v>
       </c>
       <c r="BP10">
         <v>18.22</v>
@@ -2606,10 +2603,10 @@
         <v>0</v>
       </c>
       <c r="BS10">
-        <v>11.2</v>
+        <v>12.96</v>
       </c>
       <c r="BT10">
-        <v>21.91</v>
+        <v>25.91</v>
       </c>
       <c r="BU10">
         <v>0</v>
@@ -2618,16 +2615,16 @@
         <v>0</v>
       </c>
       <c r="BW10">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="BX10">
-        <v>33.13</v>
+        <v>38.88</v>
       </c>
       <c r="BY10">
-        <v>17.79</v>
+        <v>19.55</v>
       </c>
       <c r="BZ10">
-        <v>39.23</v>
+        <v>41.77</v>
       </c>
       <c r="CA10">
         <v>0</v>
@@ -2639,13 +2636,13 @@
         <v>0.02</v>
       </c>
       <c r="CD10">
-        <v>57.04</v>
+        <v>61.34</v>
       </c>
       <c r="CE10">
-        <v>37.15</v>
+        <v>34.13</v>
       </c>
       <c r="CF10">
-        <v>62.44</v>
+        <v>68.99</v>
       </c>
       <c r="CG10">
         <v>0</v>
@@ -2657,13 +2654,13 @@
         <v>0.06</v>
       </c>
       <c r="CJ10">
-        <v>99.65</v>
+        <v>103.18</v>
       </c>
       <c r="CK10">
-        <v>1430.8196721311</v>
+        <v>1422.1204188482</v>
       </c>
       <c r="CL10">
-        <v>1479.3220338983</v>
+        <v>1474.4698897371</v>
       </c>
     </row>
     <row r="11">
@@ -2710,28 +2707,28 @@
         <v>1</v>
       </c>
       <c r="R11">
-        <v>578.62</v>
+        <v>587.21</v>
       </c>
       <c r="S11">
-        <v>485.06</v>
+        <v>403.6</v>
       </c>
       <c r="T11">
-        <v>87.96</v>
+        <v>89.81</v>
       </c>
       <c r="U11">
         <v>0</v>
       </c>
       <c r="V11">
-        <v>-257.36</v>
+        <v>125162.29</v>
       </c>
       <c r="W11">
         <v>5.79</v>
       </c>
       <c r="AA11">
-        <v>-257.36</v>
+        <v>125162.29</v>
       </c>
       <c r="AB11">
-        <v>-257.36</v>
+        <v>125162.29</v>
       </c>
       <c r="AC11">
         <v>0</v>
@@ -2767,10 +2764,10 @@
         <v>0</v>
       </c>
       <c r="AR11">
-        <v>-257.36</v>
+        <v>125162.29</v>
       </c>
       <c r="AS11">
-        <v>-257.36</v>
+        <v>125162.29</v>
       </c>
       <c r="AT11">
         <v>0</v>
@@ -2794,10 +2791,10 @@
         <v>0</v>
       </c>
       <c r="BA11">
-        <v>-257.36</v>
+        <v>125162.29</v>
       </c>
       <c r="BB11">
-        <v>-257.36</v>
+        <v>125162.29</v>
       </c>
       <c r="BC11">
         <v>0</v>
@@ -2821,10 +2818,10 @@
         <v>0</v>
       </c>
       <c r="BJ11">
-        <v>-257.36</v>
+        <v>125162.29</v>
       </c>
       <c r="BK11">
-        <v>-257.36</v>
+        <v>125162.29</v>
       </c>
       <c r="BL11">
         <v>0</v>
@@ -2851,7 +2848,7 @@
         <v>4.99</v>
       </c>
       <c r="BT11">
-        <v>0.49</v>
+        <v>0.51</v>
       </c>
       <c r="BU11">
         <v>0</v>
@@ -2863,13 +2860,13 @@
         <v>0</v>
       </c>
       <c r="BX11">
-        <v>5.48</v>
+        <v>5.5</v>
       </c>
       <c r="BY11">
         <v>4.99</v>
       </c>
       <c r="BZ11">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="CA11">
         <v>0</v>
@@ -2881,13 +2878,13 @@
         <v>0</v>
       </c>
       <c r="CD11">
-        <v>5.94</v>
+        <v>5.95</v>
       </c>
       <c r="CE11">
         <v>4.99</v>
       </c>
       <c r="CF11">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="CG11">
         <v>0</v>
@@ -2899,13 +2896,13 @@
         <v>0</v>
       </c>
       <c r="CJ11">
-        <v>6.52</v>
+        <v>6.67</v>
       </c>
       <c r="CK11">
-        <v>1430.8196721311</v>
+        <v>1422.1204188482</v>
       </c>
       <c r="CL11">
-        <v>1479.3220338983</v>
+        <v>1474.4698897371</v>
       </c>
     </row>
     <row r="12">
@@ -2996,28 +2993,28 @@
         <v>1</v>
       </c>
       <c r="R13">
-        <v>7411.07</v>
+        <v>7513</v>
       </c>
       <c r="S13">
-        <v>5819.68</v>
+        <v>5872.57</v>
       </c>
       <c r="T13">
-        <v>1563.18</v>
+        <v>1609.89</v>
       </c>
       <c r="U13">
         <v>0</v>
       </c>
       <c r="V13">
-        <v>3661.16</v>
+        <v>5115.47</v>
       </c>
       <c r="Y13">
-        <v>25.68</v>
+        <v>26.94</v>
       </c>
       <c r="AA13">
-        <v>3661.16</v>
+        <v>5115.47</v>
       </c>
       <c r="AB13">
-        <v>3661.16</v>
+        <v>5115.47</v>
       </c>
       <c r="AC13">
         <v>0</v>
@@ -3053,10 +3050,10 @@
         <v>0</v>
       </c>
       <c r="AR13">
-        <v>3661.16</v>
+        <v>5115.47</v>
       </c>
       <c r="AS13">
-        <v>3661.16</v>
+        <v>5115.47</v>
       </c>
       <c r="AT13">
         <v>0</v>
@@ -3080,10 +3077,10 @@
         <v>0</v>
       </c>
       <c r="BA13">
-        <v>3661.16</v>
+        <v>5115.47</v>
       </c>
       <c r="BB13">
-        <v>3661.16</v>
+        <v>5115.47</v>
       </c>
       <c r="BC13">
         <v>0</v>
@@ -3107,10 +3104,10 @@
         <v>0</v>
       </c>
       <c r="BJ13">
-        <v>3661.16</v>
+        <v>5115.47</v>
       </c>
       <c r="BK13">
-        <v>3661.16</v>
+        <v>5115.47</v>
       </c>
       <c r="BL13">
         <v>0</v>
@@ -3137,7 +3134,7 @@
         <v>14.83</v>
       </c>
       <c r="BT13">
-        <v>4.13</v>
+        <v>5.67</v>
       </c>
       <c r="BU13">
         <v>0</v>
@@ -3146,16 +3143,16 @@
         <v>0</v>
       </c>
       <c r="BW13">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="BX13">
-        <v>19.01</v>
+        <v>20.52</v>
       </c>
       <c r="BY13">
         <v>15.58</v>
       </c>
       <c r="BZ13">
-        <v>7.1</v>
+        <v>8.69</v>
       </c>
       <c r="CA13">
         <v>0</v>
@@ -3167,13 +3164,13 @@
         <v>0.05</v>
       </c>
       <c r="CD13">
-        <v>22.73</v>
+        <v>24.32</v>
       </c>
       <c r="CE13">
         <v>39.72</v>
       </c>
       <c r="CF13">
-        <v>11.32</v>
+        <v>13.68</v>
       </c>
       <c r="CG13">
         <v>0</v>
@@ -3185,13 +3182,13 @@
         <v>0.16</v>
       </c>
       <c r="CJ13">
-        <v>51.2</v>
+        <v>53.56</v>
       </c>
       <c r="CK13">
-        <v>1430.8196721311</v>
+        <v>1422.1204188482</v>
       </c>
       <c r="CL13">
-        <v>1479.3220338983</v>
+        <v>1474.4698897371</v>
       </c>
     </row>
     <row r="14">
@@ -3238,13 +3235,13 @@
         <v>1</v>
       </c>
       <c r="R14">
-        <v>4938.75</v>
+        <v>4876.16</v>
       </c>
       <c r="S14">
-        <v>1919.67</v>
+        <v>1854.84</v>
       </c>
       <c r="T14">
-        <v>3002.8</v>
+        <v>3005.06</v>
       </c>
       <c r="U14">
         <v>0</v>
@@ -3379,7 +3376,7 @@
         <v>14.74</v>
       </c>
       <c r="BT14">
-        <v>0.48</v>
+        <v>0.98</v>
       </c>
       <c r="BU14">
         <v>0</v>
@@ -3391,13 +3388,13 @@
         <v>0</v>
       </c>
       <c r="BX14">
-        <v>15.22</v>
+        <v>15.72</v>
       </c>
       <c r="BY14">
         <v>14.74</v>
       </c>
       <c r="BZ14">
-        <v>3.9</v>
+        <v>1.48</v>
       </c>
       <c r="CA14">
         <v>0</v>
@@ -3409,13 +3406,13 @@
         <v>0</v>
       </c>
       <c r="CD14">
-        <v>18.64</v>
+        <v>16.22</v>
       </c>
       <c r="CE14">
         <v>14.74</v>
       </c>
       <c r="CF14">
-        <v>17.53</v>
+        <v>18.03</v>
       </c>
       <c r="CG14">
         <v>0</v>
@@ -3427,13 +3424,13 @@
         <v>0</v>
       </c>
       <c r="CJ14">
-        <v>32.27</v>
+        <v>32.77</v>
       </c>
       <c r="CK14">
-        <v>1430.8196721311</v>
+        <v>1422.1204188482</v>
       </c>
       <c r="CL14">
-        <v>1479.3220338983</v>
+        <v>1474.4698897371</v>
       </c>
     </row>
     <row r="15">
@@ -3480,40 +3477,37 @@
         <v>1</v>
       </c>
       <c r="R15">
-        <v>6714.57</v>
+        <v>7072.48</v>
       </c>
       <c r="S15">
-        <v>3637.44</v>
+        <v>3872.92</v>
       </c>
       <c r="T15">
-        <v>3068.04</v>
+        <v>2691.46</v>
       </c>
       <c r="U15">
         <v>0</v>
       </c>
-      <c r="V15">
-        <v>4671.33</v>
-      </c>
       <c r="W15">
-        <v>0.03</v>
+        <v>500.03</v>
       </c>
       <c r="Y15">
-        <v>5.82</v>
+        <v>8.09</v>
       </c>
       <c r="AA15">
-        <v>4671.33</v>
+        <v>0</v>
       </c>
       <c r="AB15">
-        <v>4671.33</v>
+        <v>0</v>
       </c>
       <c r="AC15">
-        <v>4230.15</v>
+        <v>0</v>
       </c>
       <c r="AD15">
-        <v>0.03</v>
+        <v>500.03</v>
       </c>
       <c r="AE15">
-        <v>0.03</v>
+        <v>500.03</v>
       </c>
       <c r="AF15">
         <v>0</v>
@@ -3540,19 +3534,19 @@
         <v>0</v>
       </c>
       <c r="AR15">
-        <v>4671.33</v>
+        <v>0</v>
       </c>
       <c r="AS15">
-        <v>4671.33</v>
+        <v>0</v>
       </c>
       <c r="AT15">
-        <v>4230.15</v>
+        <v>0</v>
       </c>
       <c r="AU15">
-        <v>0.03</v>
+        <v>500.03</v>
       </c>
       <c r="AV15">
-        <v>0.03</v>
+        <v>500.03</v>
       </c>
       <c r="AW15">
         <v>0</v>
@@ -3567,19 +3561,19 @@
         <v>0</v>
       </c>
       <c r="BA15">
-        <v>4671.33</v>
+        <v>0</v>
       </c>
       <c r="BB15">
-        <v>4671.33</v>
+        <v>0</v>
       </c>
       <c r="BC15">
-        <v>4230.15</v>
+        <v>0</v>
       </c>
       <c r="BD15">
-        <v>0.03</v>
+        <v>500.03</v>
       </c>
       <c r="BE15">
-        <v>0.03</v>
+        <v>500.03</v>
       </c>
       <c r="BF15">
         <v>0</v>
@@ -3594,19 +3588,19 @@
         <v>0</v>
       </c>
       <c r="BJ15">
-        <v>4671.33</v>
+        <v>0</v>
       </c>
       <c r="BK15">
-        <v>4671.33</v>
+        <v>0</v>
       </c>
       <c r="BL15">
-        <v>4230.15</v>
+        <v>0</v>
       </c>
       <c r="BM15">
-        <v>0.03</v>
+        <v>500.03</v>
       </c>
       <c r="BN15">
-        <v>0.03</v>
+        <v>500.03</v>
       </c>
       <c r="BO15">
         <v>0</v>
@@ -3621,10 +3615,10 @@
         <v>0</v>
       </c>
       <c r="BS15">
-        <v>27.63</v>
+        <v>18.12</v>
       </c>
       <c r="BT15">
-        <v>4.44</v>
+        <v>5.85</v>
       </c>
       <c r="BU15">
         <v>0</v>
@@ -3636,13 +3630,13 @@
         <v>0.02</v>
       </c>
       <c r="BX15">
-        <v>32.09</v>
+        <v>23.99</v>
       </c>
       <c r="BY15">
-        <v>30.84</v>
+        <v>31.41</v>
       </c>
       <c r="BZ15">
-        <v>7.15</v>
+        <v>8.61</v>
       </c>
       <c r="CA15">
         <v>0</v>
@@ -3654,13 +3648,13 @@
         <v>0.03</v>
       </c>
       <c r="CD15">
-        <v>38.02</v>
+        <v>40.05</v>
       </c>
       <c r="CE15">
-        <v>39.43</v>
+        <v>41.55</v>
       </c>
       <c r="CF15">
-        <v>8.96</v>
+        <v>11.11</v>
       </c>
       <c r="CG15">
         <v>0</v>
@@ -3669,16 +3663,16 @@
         <v>0</v>
       </c>
       <c r="CI15">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="CJ15">
-        <v>48.42</v>
+        <v>52.7</v>
       </c>
       <c r="CK15">
-        <v>1430.8196721311</v>
+        <v>1422.1204188482</v>
       </c>
       <c r="CL15">
-        <v>1479.3220338983</v>
+        <v>1474.4698897371</v>
       </c>
     </row>
     <row r="16">
@@ -3725,13 +3719,13 @@
         <v>1</v>
       </c>
       <c r="R16">
-        <v>173479</v>
+        <v>173693.16</v>
       </c>
       <c r="S16">
-        <v>11037.17</v>
+        <v>10037.69</v>
       </c>
       <c r="T16">
-        <v>162404.87</v>
+        <v>163618.32</v>
       </c>
       <c r="U16">
         <v>0</v>
@@ -3866,7 +3860,7 @@
         <v>59.9</v>
       </c>
       <c r="BT16">
-        <v>207.05</v>
+        <v>245.21</v>
       </c>
       <c r="BU16">
         <v>0</v>
@@ -3878,13 +3872,13 @@
         <v>0</v>
       </c>
       <c r="BX16">
-        <v>266.95</v>
+        <v>305.11</v>
       </c>
       <c r="BY16">
         <v>59.9</v>
       </c>
       <c r="BZ16">
-        <v>207.05</v>
+        <v>270.06</v>
       </c>
       <c r="CA16">
         <v>0</v>
@@ -3896,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="CD16">
-        <v>266.95</v>
+        <v>329.96</v>
       </c>
       <c r="CE16">
         <v>267</v>
       </c>
       <c r="CF16">
-        <v>207.05</v>
+        <v>270.06</v>
       </c>
       <c r="CG16">
         <v>0</v>
@@ -3914,13 +3908,13 @@
         <v>0</v>
       </c>
       <c r="CJ16">
-        <v>474.05</v>
+        <v>537.06</v>
       </c>
       <c r="CK16">
-        <v>1430.8196721311</v>
+        <v>1422.1204188482</v>
       </c>
       <c r="CL16">
-        <v>1479.3220338983</v>
+        <v>1474.4698897371</v>
       </c>
     </row>
     <row r="17">
@@ -3967,13 +3961,13 @@
         <v>1</v>
       </c>
       <c r="R17">
-        <v>3006.34</v>
+        <v>3031</v>
       </c>
       <c r="S17">
         <v>0</v>
       </c>
       <c r="T17">
-        <v>2706.35</v>
+        <v>2731</v>
       </c>
       <c r="U17">
         <v>0</v>
@@ -4105,7 +4099,7 @@
         <v>0</v>
       </c>
       <c r="BT17">
-        <v>1.29</v>
+        <v>2.86</v>
       </c>
       <c r="BU17">
         <v>0</v>
@@ -4117,13 +4111,13 @@
         <v>0</v>
       </c>
       <c r="BX17">
-        <v>1.29</v>
+        <v>2.86</v>
       </c>
       <c r="BY17">
         <v>0</v>
       </c>
       <c r="BZ17">
-        <v>1.29</v>
+        <v>2.86</v>
       </c>
       <c r="CA17">
         <v>0</v>
@@ -4135,13 +4129,13 @@
         <v>0</v>
       </c>
       <c r="CD17">
-        <v>1.29</v>
+        <v>2.86</v>
       </c>
       <c r="CE17">
         <v>0</v>
       </c>
       <c r="CF17">
-        <v>1.29</v>
+        <v>2.86</v>
       </c>
       <c r="CG17">
         <v>0</v>
@@ -4153,13 +4147,13 @@
         <v>0</v>
       </c>
       <c r="CJ17">
-        <v>1.29</v>
+        <v>2.86</v>
       </c>
       <c r="CK17">
-        <v>1430.8196721311</v>
+        <v>1422.1204188482</v>
       </c>
       <c r="CL17">
-        <v>1479.3220338983</v>
+        <v>1474.4698897371</v>
       </c>
     </row>
     <row r="18">
@@ -4206,40 +4200,40 @@
         <v>1</v>
       </c>
       <c r="R18">
-        <v>3040.41</v>
+        <v>3287.19</v>
       </c>
       <c r="S18">
-        <v>2392.6</v>
+        <v>2919.89</v>
       </c>
       <c r="T18">
-        <v>625.22</v>
+        <v>330.35</v>
       </c>
       <c r="U18">
         <v>0</v>
       </c>
       <c r="V18">
-        <v>10887.16</v>
+        <v>30736.12</v>
       </c>
       <c r="W18">
-        <v>12.9</v>
+        <v>10.61</v>
       </c>
       <c r="Y18">
-        <v>2.1</v>
+        <v>4.73</v>
       </c>
       <c r="AA18">
-        <v>10887.16</v>
+        <v>30736.12</v>
       </c>
       <c r="AB18">
-        <v>10887.16</v>
+        <v>30736.12</v>
       </c>
       <c r="AC18">
-        <v>10887.16</v>
+        <v>30307.45</v>
       </c>
       <c r="AD18">
-        <v>12.9</v>
+        <v>10.61</v>
       </c>
       <c r="AE18">
-        <v>12.9</v>
+        <v>10.61</v>
       </c>
       <c r="AF18">
         <v>0</v>
@@ -4266,19 +4260,19 @@
         <v>0</v>
       </c>
       <c r="AR18">
-        <v>10887.16</v>
+        <v>30736.12</v>
       </c>
       <c r="AS18">
-        <v>10887.16</v>
+        <v>30736.12</v>
       </c>
       <c r="AT18">
-        <v>10887.16</v>
+        <v>30307.45</v>
       </c>
       <c r="AU18">
-        <v>12.9</v>
+        <v>10.61</v>
       </c>
       <c r="AV18">
-        <v>12.9</v>
+        <v>10.61</v>
       </c>
       <c r="AW18">
         <v>0</v>
@@ -4293,19 +4287,19 @@
         <v>0</v>
       </c>
       <c r="BA18">
-        <v>10887.16</v>
+        <v>30736.12</v>
       </c>
       <c r="BB18">
-        <v>10887.16</v>
+        <v>30736.12</v>
       </c>
       <c r="BC18">
-        <v>10887.16</v>
+        <v>30307.45</v>
       </c>
       <c r="BD18">
-        <v>12.9</v>
+        <v>10.61</v>
       </c>
       <c r="BE18">
-        <v>12.9</v>
+        <v>10.61</v>
       </c>
       <c r="BF18">
         <v>0</v>
@@ -4320,19 +4314,19 @@
         <v>0</v>
       </c>
       <c r="BJ18">
-        <v>10887.16</v>
+        <v>30736.12</v>
       </c>
       <c r="BK18">
-        <v>10887.16</v>
+        <v>30736.12</v>
       </c>
       <c r="BL18">
-        <v>10887.16</v>
+        <v>30307.45</v>
       </c>
       <c r="BM18">
-        <v>12.9</v>
+        <v>10.61</v>
       </c>
       <c r="BN18">
-        <v>12.9</v>
+        <v>10.61</v>
       </c>
       <c r="BO18">
         <v>0</v>
@@ -4347,10 +4341,10 @@
         <v>0</v>
       </c>
       <c r="BS18">
-        <v>4.59</v>
+        <v>7.57</v>
       </c>
       <c r="BT18">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="BU18">
         <v>0</v>
@@ -4359,16 +4353,16 @@
         <v>0</v>
       </c>
       <c r="BW18">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="BX18">
-        <v>6.39</v>
+        <v>9.32</v>
       </c>
       <c r="BY18">
-        <v>13.35</v>
+        <v>16.33</v>
       </c>
       <c r="BZ18">
-        <v>2.75</v>
+        <v>3.15</v>
       </c>
       <c r="CA18">
         <v>0</v>
@@ -4377,16 +4371,16 @@
         <v>0</v>
       </c>
       <c r="CC18">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="CD18">
-        <v>16.1</v>
+        <v>19.49</v>
       </c>
       <c r="CE18">
-        <v>13.35</v>
+        <v>16.33</v>
       </c>
       <c r="CF18">
-        <v>2.75</v>
+        <v>3.15</v>
       </c>
       <c r="CG18">
         <v>0</v>
@@ -4395,16 +4389,16 @@
         <v>0</v>
       </c>
       <c r="CI18">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="CJ18">
-        <v>16.1</v>
+        <v>19.49</v>
       </c>
       <c r="CK18">
-        <v>1430.8196721311</v>
+        <v>1422.1204188482</v>
       </c>
       <c r="CL18">
-        <v>1479.3220338983</v>
+        <v>1474.4698897371</v>
       </c>
     </row>
     <row r="19">
@@ -4596,13 +4590,13 @@
         <v>1</v>
       </c>
       <c r="R21">
-        <v>601.15</v>
+        <v>606.69</v>
       </c>
       <c r="S21">
         <v>0</v>
       </c>
       <c r="T21">
-        <v>601.15</v>
+        <v>606.7</v>
       </c>
       <c r="U21">
         <v>0</v>
@@ -4611,7 +4605,7 @@
         <v>0</v>
       </c>
       <c r="BT21">
-        <v>0.26</v>
+        <v>0.69</v>
       </c>
       <c r="BU21">
         <v>0</v>
@@ -4623,13 +4617,13 @@
         <v>0</v>
       </c>
       <c r="BX21">
-        <v>0.26</v>
+        <v>0.69</v>
       </c>
       <c r="BY21">
         <v>0</v>
       </c>
       <c r="BZ21">
-        <v>0.26</v>
+        <v>0.69</v>
       </c>
       <c r="CA21">
         <v>0</v>
@@ -4641,13 +4635,13 @@
         <v>0</v>
       </c>
       <c r="CD21">
-        <v>0.26</v>
+        <v>0.69</v>
       </c>
       <c r="CE21">
         <v>0</v>
       </c>
       <c r="CF21">
-        <v>0.26</v>
+        <v>0.69</v>
       </c>
       <c r="CG21">
         <v>0</v>
@@ -4659,13 +4653,13 @@
         <v>0</v>
       </c>
       <c r="CJ21">
-        <v>0.26</v>
+        <v>0.69</v>
       </c>
       <c r="CK21">
-        <v>1430.8196721311</v>
+        <v>1422.1204188482</v>
       </c>
       <c r="CL21">
-        <v>1479.3220338983</v>
+        <v>1474.4698897371</v>
       </c>
     </row>
     <row r="22">
@@ -4712,13 +4706,13 @@
         <v>1</v>
       </c>
       <c r="R22">
-        <v>799.79</v>
+        <v>831.48</v>
       </c>
       <c r="S22">
         <v>0</v>
       </c>
       <c r="T22">
-        <v>799.79</v>
+        <v>831.48</v>
       </c>
       <c r="U22">
         <v>0</v>
@@ -4727,7 +4721,7 @@
         <v>0.73</v>
       </c>
       <c r="BT22">
-        <v>1.54</v>
+        <v>2.86</v>
       </c>
       <c r="BU22">
         <v>0</v>
@@ -4739,13 +4733,13 @@
         <v>0</v>
       </c>
       <c r="BX22">
-        <v>2.27</v>
+        <v>3.59</v>
       </c>
       <c r="BY22">
         <v>0.73</v>
       </c>
       <c r="BZ22">
-        <v>1.54</v>
+        <v>2.86</v>
       </c>
       <c r="CA22">
         <v>0</v>
@@ -4757,13 +4751,13 @@
         <v>0</v>
       </c>
       <c r="CD22">
-        <v>2.27</v>
+        <v>3.59</v>
       </c>
       <c r="CE22">
         <v>0.73</v>
       </c>
       <c r="CF22">
-        <v>1.54</v>
+        <v>2.86</v>
       </c>
       <c r="CG22">
         <v>0</v>
@@ -4775,13 +4769,13 @@
         <v>0</v>
       </c>
       <c r="CJ22">
-        <v>2.27</v>
+        <v>3.59</v>
       </c>
       <c r="CK22">
-        <v>1430.8196721311</v>
+        <v>1422.1204188482</v>
       </c>
       <c r="CL22">
-        <v>1479.3220338983</v>
+        <v>1474.4698897371</v>
       </c>
     </row>
     <row r="23">
@@ -4828,22 +4822,148 @@
         <v>1</v>
       </c>
       <c r="R23">
-        <v>28069.7</v>
+        <v>27557.5</v>
       </c>
       <c r="S23">
         <v>0</v>
       </c>
       <c r="T23">
-        <v>28069.69</v>
+        <v>27556.61</v>
       </c>
       <c r="U23">
         <v>0</v>
       </c>
+      <c r="V23">
+        <v>-17.83</v>
+      </c>
+      <c r="W23">
+        <v>0.91</v>
+      </c>
+      <c r="AA23">
+        <v>-17.83</v>
+      </c>
+      <c r="AB23">
+        <v>-17.83</v>
+      </c>
+      <c r="AC23">
+        <v>0</v>
+      </c>
+      <c r="AD23">
+        <v>0.91</v>
+      </c>
+      <c r="AE23">
+        <v>0.91</v>
+      </c>
+      <c r="AF23">
+        <v>0</v>
+      </c>
+      <c r="AG23">
+        <v>0</v>
+      </c>
+      <c r="AH23">
+        <v>0</v>
+      </c>
+      <c r="AI23">
+        <v>0</v>
+      </c>
+      <c r="AJ23">
+        <v>0</v>
+      </c>
+      <c r="AK23">
+        <v>0</v>
+      </c>
+      <c r="AL23">
+        <v>0</v>
+      </c>
+      <c r="AM23">
+        <v>0</v>
+      </c>
+      <c r="AR23">
+        <v>-17.83</v>
+      </c>
+      <c r="AS23">
+        <v>-17.83</v>
+      </c>
+      <c r="AT23">
+        <v>0</v>
+      </c>
+      <c r="AU23">
+        <v>0.91</v>
+      </c>
+      <c r="AV23">
+        <v>0.91</v>
+      </c>
+      <c r="AW23">
+        <v>0</v>
+      </c>
+      <c r="AX23">
+        <v>0</v>
+      </c>
+      <c r="AY23">
+        <v>0</v>
+      </c>
+      <c r="AZ23">
+        <v>0</v>
+      </c>
+      <c r="BA23">
+        <v>-17.83</v>
+      </c>
+      <c r="BB23">
+        <v>-17.83</v>
+      </c>
+      <c r="BC23">
+        <v>0</v>
+      </c>
+      <c r="BD23">
+        <v>0.91</v>
+      </c>
+      <c r="BE23">
+        <v>0.91</v>
+      </c>
+      <c r="BF23">
+        <v>0</v>
+      </c>
+      <c r="BG23">
+        <v>0</v>
+      </c>
+      <c r="BH23">
+        <v>0</v>
+      </c>
+      <c r="BI23">
+        <v>0</v>
+      </c>
+      <c r="BJ23">
+        <v>-17.83</v>
+      </c>
+      <c r="BK23">
+        <v>-17.83</v>
+      </c>
+      <c r="BL23">
+        <v>0</v>
+      </c>
+      <c r="BM23">
+        <v>0.91</v>
+      </c>
+      <c r="BN23">
+        <v>0.91</v>
+      </c>
+      <c r="BO23">
+        <v>0</v>
+      </c>
+      <c r="BP23">
+        <v>0</v>
+      </c>
+      <c r="BQ23">
+        <v>0</v>
+      </c>
+      <c r="BR23">
+        <v>0</v>
+      </c>
       <c r="BS23">
-        <v>0</v>
+        <v>10.39</v>
       </c>
       <c r="BT23">
-        <v>12.81</v>
+        <v>23.54</v>
       </c>
       <c r="BU23">
         <v>0</v>
@@ -4855,13 +4975,13 @@
         <v>0</v>
       </c>
       <c r="BX23">
-        <v>12.81</v>
+        <v>33.93</v>
       </c>
       <c r="BY23">
-        <v>0</v>
+        <v>10.39</v>
       </c>
       <c r="BZ23">
-        <v>12.81</v>
+        <v>23.54</v>
       </c>
       <c r="CA23">
         <v>0</v>
@@ -4873,13 +4993,13 @@
         <v>0</v>
       </c>
       <c r="CD23">
-        <v>12.81</v>
+        <v>33.93</v>
       </c>
       <c r="CE23">
-        <v>0</v>
+        <v>10.39</v>
       </c>
       <c r="CF23">
-        <v>12.81</v>
+        <v>23.54</v>
       </c>
       <c r="CG23">
         <v>0</v>
@@ -4891,13 +5011,13 @@
         <v>0</v>
       </c>
       <c r="CJ23">
-        <v>12.81</v>
+        <v>33.93</v>
       </c>
       <c r="CK23">
-        <v>1430.8196721311</v>
+        <v>1422.1204188482</v>
       </c>
       <c r="CL23">
-        <v>1479.3220338983</v>
+        <v>1474.4698897371</v>
       </c>
     </row>
     <row r="24">
@@ -4988,28 +5108,31 @@
         <v>1</v>
       </c>
       <c r="R25">
-        <v>7990.57</v>
+        <v>7517.89</v>
       </c>
       <c r="S25">
-        <v>2742.43</v>
+        <v>3440.3</v>
       </c>
       <c r="T25">
-        <v>5248.15</v>
+        <v>4067.84</v>
       </c>
       <c r="U25">
         <v>0</v>
       </c>
       <c r="V25">
-        <v>3.85</v>
+        <v>6553.43</v>
+      </c>
+      <c r="Y25">
+        <v>5.12</v>
       </c>
       <c r="AA25">
-        <v>3.85</v>
+        <v>6553.43</v>
       </c>
       <c r="AB25">
-        <v>3.85</v>
+        <v>6553.43</v>
       </c>
       <c r="AC25">
-        <v>3.85</v>
+        <v>6553.43</v>
       </c>
       <c r="AD25">
         <v>0</v>
@@ -5042,13 +5165,13 @@
         <v>0</v>
       </c>
       <c r="AR25">
-        <v>3.85</v>
+        <v>6553.43</v>
       </c>
       <c r="AS25">
-        <v>3.85</v>
+        <v>6553.43</v>
       </c>
       <c r="AT25">
-        <v>3.85</v>
+        <v>6553.43</v>
       </c>
       <c r="AU25">
         <v>0</v>
@@ -5069,13 +5192,13 @@
         <v>0</v>
       </c>
       <c r="BA25">
-        <v>3.85</v>
+        <v>6553.43</v>
       </c>
       <c r="BB25">
-        <v>3.85</v>
+        <v>6553.43</v>
       </c>
       <c r="BC25">
-        <v>3.85</v>
+        <v>6553.43</v>
       </c>
       <c r="BD25">
         <v>0</v>
@@ -5096,13 +5219,13 @@
         <v>0</v>
       </c>
       <c r="BJ25">
-        <v>3.85</v>
+        <v>6553.43</v>
       </c>
       <c r="BK25">
-        <v>3.85</v>
+        <v>6553.43</v>
       </c>
       <c r="BL25">
-        <v>3.85</v>
+        <v>6553.43</v>
       </c>
       <c r="BM25">
         <v>0</v>
@@ -5123,10 +5246,10 @@
         <v>0</v>
       </c>
       <c r="BS25">
-        <v>16.21</v>
+        <v>20.36</v>
       </c>
       <c r="BT25">
-        <v>8.93</v>
+        <v>16.1</v>
       </c>
       <c r="BU25">
         <v>0</v>
@@ -5135,16 +5258,16 @@
         <v>0</v>
       </c>
       <c r="BW25">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="BX25">
-        <v>25.14</v>
+        <v>36.47</v>
       </c>
       <c r="BY25">
-        <v>16.21</v>
+        <v>20.36</v>
       </c>
       <c r="BZ25">
-        <v>8.93</v>
+        <v>16.1</v>
       </c>
       <c r="CA25">
         <v>0</v>
@@ -5153,16 +5276,16 @@
         <v>0</v>
       </c>
       <c r="CC25">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="CD25">
-        <v>25.14</v>
+        <v>36.47</v>
       </c>
       <c r="CE25">
-        <v>16.21</v>
+        <v>20.36</v>
       </c>
       <c r="CF25">
-        <v>8.93</v>
+        <v>16.1</v>
       </c>
       <c r="CG25">
         <v>0</v>
@@ -5171,16 +5294,16 @@
         <v>0</v>
       </c>
       <c r="CI25">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="CJ25">
-        <v>25.14</v>
+        <v>36.47</v>
       </c>
       <c r="CK25">
-        <v>1430.8196721311</v>
+        <v>1422.1204188482</v>
       </c>
       <c r="CL25">
-        <v>1479.3220338983</v>
+        <v>1474.4698897371</v>
       </c>
     </row>
     <row r="26">
@@ -5227,13 +5350,13 @@
         <v>1</v>
       </c>
       <c r="R26">
-        <v>5004.22</v>
+        <v>5013.12</v>
       </c>
       <c r="S26">
         <v>0</v>
       </c>
       <c r="T26">
-        <v>5004.23</v>
+        <v>5013.12</v>
       </c>
       <c r="U26">
         <v>0</v>
@@ -5242,7 +5365,7 @@
         <v>0</v>
       </c>
       <c r="BT26">
-        <v>0.81</v>
+        <v>2.02</v>
       </c>
       <c r="BU26">
         <v>0</v>
@@ -5254,13 +5377,13 @@
         <v>0</v>
       </c>
       <c r="BX26">
-        <v>0.81</v>
+        <v>2.02</v>
       </c>
       <c r="BY26">
         <v>0</v>
       </c>
       <c r="BZ26">
-        <v>0.81</v>
+        <v>2.02</v>
       </c>
       <c r="CA26">
         <v>0</v>
@@ -5272,13 +5395,13 @@
         <v>0</v>
       </c>
       <c r="CD26">
-        <v>0.81</v>
+        <v>2.02</v>
       </c>
       <c r="CE26">
         <v>0</v>
       </c>
       <c r="CF26">
-        <v>0.81</v>
+        <v>2.02</v>
       </c>
       <c r="CG26">
         <v>0</v>
@@ -5290,13 +5413,13 @@
         <v>0</v>
       </c>
       <c r="CJ26">
-        <v>0.81</v>
+        <v>2.02</v>
       </c>
       <c r="CK26">
-        <v>1430.8196721311</v>
+        <v>1422.1204188482</v>
       </c>
       <c r="CL26">
-        <v>1479.3220338983</v>
+        <v>1474.4698897371</v>
       </c>
     </row>
     <row r="27">
@@ -5343,13 +5466,13 @@
         <v>1</v>
       </c>
       <c r="R27">
-        <v>5012.29</v>
+        <v>5058.79</v>
       </c>
       <c r="S27">
         <v>0</v>
       </c>
       <c r="T27">
-        <v>5011.3</v>
+        <v>5057.8</v>
       </c>
       <c r="U27">
         <v>0</v>
@@ -5481,7 +5604,7 @@
         <v>0</v>
       </c>
       <c r="BT27">
-        <v>3.09</v>
+        <v>6.95</v>
       </c>
       <c r="BU27">
         <v>0</v>
@@ -5493,13 +5616,13 @@
         <v>0</v>
       </c>
       <c r="BX27">
-        <v>3.09</v>
+        <v>6.95</v>
       </c>
       <c r="BY27">
         <v>0</v>
       </c>
       <c r="BZ27">
-        <v>3.09</v>
+        <v>6.95</v>
       </c>
       <c r="CA27">
         <v>0</v>
@@ -5511,13 +5634,13 @@
         <v>0</v>
       </c>
       <c r="CD27">
-        <v>3.09</v>
+        <v>6.95</v>
       </c>
       <c r="CE27">
         <v>0</v>
       </c>
       <c r="CF27">
-        <v>3.09</v>
+        <v>6.95</v>
       </c>
       <c r="CG27">
         <v>0</v>
@@ -5529,13 +5652,13 @@
         <v>0</v>
       </c>
       <c r="CJ27">
-        <v>3.09</v>
+        <v>6.95</v>
       </c>
       <c r="CK27">
-        <v>1430.8196721311</v>
+        <v>1422.1204188482</v>
       </c>
       <c r="CL27">
-        <v>1479.3220338983</v>
+        <v>1474.4698897371</v>
       </c>
     </row>
     <row r="28">
@@ -5717,10 +5840,10 @@
         <v>0</v>
       </c>
       <c r="CK28">
-        <v>1430.8196721311</v>
+        <v>1422.1204188482</v>
       </c>
       <c r="CL28">
-        <v>1479.3220338983</v>
+        <v>1474.4698897371</v>
       </c>
     </row>
     <row r="29">
@@ -5767,37 +5890,37 @@
         <v>1</v>
       </c>
       <c r="R29">
-        <v>52277.49</v>
+        <v>68174.15</v>
       </c>
       <c r="S29">
-        <v>8787.39</v>
+        <v>11169.32</v>
       </c>
       <c r="T29">
-        <v>43162.47</v>
+        <v>56956.95</v>
       </c>
       <c r="U29">
         <v>0</v>
       </c>
       <c r="V29">
-        <v>-2961.79</v>
-      </c>
-      <c r="W29">
-        <v>329.71</v>
+        <v>59554.3</v>
+      </c>
+      <c r="Y29">
+        <v>5.99</v>
       </c>
       <c r="AA29">
-        <v>-2961.79</v>
+        <v>59554.3</v>
       </c>
       <c r="AB29">
-        <v>-2961.79</v>
+        <v>59554.3</v>
       </c>
       <c r="AC29">
         <v>0</v>
       </c>
       <c r="AD29">
-        <v>329.71</v>
+        <v>0</v>
       </c>
       <c r="AE29">
-        <v>329.71</v>
+        <v>0</v>
       </c>
       <c r="AF29">
         <v>0</v>
@@ -5824,19 +5947,19 @@
         <v>0</v>
       </c>
       <c r="AR29">
-        <v>-2961.79</v>
+        <v>59554.3</v>
       </c>
       <c r="AS29">
-        <v>-2961.79</v>
+        <v>59554.3</v>
       </c>
       <c r="AT29">
         <v>0</v>
       </c>
       <c r="AU29">
-        <v>329.71</v>
+        <v>0</v>
       </c>
       <c r="AV29">
-        <v>329.71</v>
+        <v>0</v>
       </c>
       <c r="AW29">
         <v>0</v>
@@ -5851,19 +5974,19 @@
         <v>0</v>
       </c>
       <c r="BA29">
-        <v>-2961.79</v>
+        <v>59554.3</v>
       </c>
       <c r="BB29">
-        <v>-2961.79</v>
+        <v>59554.3</v>
       </c>
       <c r="BC29">
         <v>0</v>
       </c>
       <c r="BD29">
-        <v>329.71</v>
+        <v>0</v>
       </c>
       <c r="BE29">
-        <v>329.71</v>
+        <v>0</v>
       </c>
       <c r="BF29">
         <v>0</v>
@@ -5878,19 +6001,19 @@
         <v>0</v>
       </c>
       <c r="BJ29">
-        <v>-2961.79</v>
+        <v>59554.3</v>
       </c>
       <c r="BK29">
-        <v>-2961.79</v>
+        <v>59554.3</v>
       </c>
       <c r="BL29">
         <v>0</v>
       </c>
       <c r="BM29">
-        <v>329.71</v>
+        <v>0</v>
       </c>
       <c r="BN29">
-        <v>329.71</v>
+        <v>0</v>
       </c>
       <c r="BO29">
         <v>0</v>
@@ -5905,10 +6028,10 @@
         <v>0</v>
       </c>
       <c r="BS29">
-        <v>52.41</v>
+        <v>68.27</v>
       </c>
       <c r="BT29">
-        <v>1.96</v>
+        <v>27.27</v>
       </c>
       <c r="BU29">
         <v>0</v>
@@ -5917,16 +6040,16 @@
         <v>0</v>
       </c>
       <c r="BW29">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="BX29">
-        <v>54.37</v>
+        <v>95.55</v>
       </c>
       <c r="BY29">
-        <v>52.41</v>
+        <v>68.27</v>
       </c>
       <c r="BZ29">
-        <v>1.96</v>
+        <v>27.27</v>
       </c>
       <c r="CA29">
         <v>0</v>
@@ -5935,16 +6058,16 @@
         <v>0</v>
       </c>
       <c r="CC29">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="CD29">
-        <v>54.37</v>
+        <v>95.55</v>
       </c>
       <c r="CE29">
-        <v>52.41</v>
+        <v>68.27</v>
       </c>
       <c r="CF29">
-        <v>1.96</v>
+        <v>27.27</v>
       </c>
       <c r="CG29">
         <v>0</v>
@@ -5953,21 +6076,103 @@
         <v>0</v>
       </c>
       <c r="CI29">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="CJ29">
-        <v>54.37</v>
+        <v>95.55</v>
       </c>
       <c r="CK29">
-        <v>1430.8196721311</v>
+        <v>1422.1204188482</v>
       </c>
       <c r="CL29">
-        <v>1479.3220338983</v>
+        <v>1474.4698897371</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>1557739</v>
+      </c>
+      <c r="D30" t="str">
+        <v>5000991</v>
+      </c>
+      <c r="E30" t="str">
+        <v>BONFANTI DIEGO ALEJANDRO</v>
+      </c>
+      <c r="F30" s="1">
+        <v>46097</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30" t="str">
+        <v>IFA 5767</v>
+      </c>
+      <c r="I30" t="str">
+        <v>Vicien/DV - Marketing - IFA</v>
+      </c>
+      <c r="J30" t="str">
+        <v>IFA</v>
+      </c>
+      <c r="N30" t="str">
+        <v>Internacional</v>
+      </c>
+      <c r="P30" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q30">
+        <v>0</v>
+      </c>
+      <c r="R30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>1567825</v>
+      </c>
+      <c r="B31" t="str">
+        <v>1607966</v>
+      </c>
+      <c r="C31" t="str">
+        <v>892025</v>
+      </c>
+      <c r="E31" t="str">
+        <v>GATTO LUCAS GONZALO</v>
+      </c>
+      <c r="F31" s="1">
+        <v>46111</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31" t="str">
+        <v>IFA 5767</v>
+      </c>
+      <c r="I31" t="str">
+        <v>Vicien/DV - Marketing - IFA</v>
+      </c>
+      <c r="J31" t="str">
+        <v>IFA</v>
+      </c>
+      <c r="K31" t="str">
+        <v>IFA 4</v>
+      </c>
+      <c r="N31" t="str">
+        <v>Argentina</v>
+      </c>
+      <c r="P31" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q31">
+        <v>0</v>
+      </c>
+      <c r="R31">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:CL29"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:CL31"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/cluster.xlsx
+++ b/data/cluster.xlsx
@@ -376,7 +376,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CL31"/>
+  <dimension ref="A1:CL32"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -832,7 +832,7 @@
         <v>0</v>
       </c>
       <c r="BS2">
-        <v>80.42</v>
+        <v>55.14</v>
       </c>
       <c r="BT2">
         <v>0</v>
@@ -847,7 +847,7 @@
         <v>0</v>
       </c>
       <c r="BX2">
-        <v>80.42</v>
+        <v>55.14</v>
       </c>
       <c r="BY2">
         <v>265.34</v>
@@ -886,10 +886,10 @@
         <v>383.89</v>
       </c>
       <c r="CK2">
-        <v>1422.1204188482</v>
+        <v>1433.0420969023</v>
       </c>
       <c r="CL2">
-        <v>1474.4698897371</v>
+        <v>1486.4063272368</v>
       </c>
     </row>
     <row r="3">
@@ -939,46 +939,43 @@
         <v>1</v>
       </c>
       <c r="R3">
-        <v>11673.15</v>
+        <v>7170.67</v>
       </c>
       <c r="S3">
-        <v>4922.05</v>
+        <v>5402.52</v>
       </c>
       <c r="T3">
-        <v>6739.38</v>
+        <v>1750.89</v>
       </c>
       <c r="U3">
         <v>0</v>
       </c>
       <c r="V3">
-        <v>189.24</v>
-      </c>
-      <c r="W3">
-        <v>0.13</v>
+        <v>7962.02</v>
       </c>
       <c r="Y3">
-        <v>11.44</v>
+        <v>11.71</v>
       </c>
       <c r="AA3">
-        <v>189.24</v>
+        <v>7962.02</v>
       </c>
       <c r="AB3">
-        <v>189.24</v>
+        <v>7962.02</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>7203.58</v>
       </c>
       <c r="AD3">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="AE3">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="AF3">
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>5150.58</v>
+        <v>0</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -999,19 +996,19 @@
         <v>0</v>
       </c>
       <c r="AR3">
-        <v>189.24</v>
+        <v>7962.02</v>
       </c>
       <c r="AS3">
-        <v>189.24</v>
+        <v>7962.02</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>7203.58</v>
       </c>
       <c r="AU3">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="AV3">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="AW3">
         <v>0</v>
@@ -1026,19 +1023,19 @@
         <v>0</v>
       </c>
       <c r="BA3">
-        <v>189.24</v>
+        <v>7962.02</v>
       </c>
       <c r="BB3">
-        <v>189.24</v>
+        <v>7962.02</v>
       </c>
       <c r="BC3">
-        <v>0</v>
+        <v>7203.58</v>
       </c>
       <c r="BD3">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="BE3">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="BF3">
         <v>0</v>
@@ -1053,19 +1050,19 @@
         <v>0</v>
       </c>
       <c r="BJ3">
-        <v>189.24</v>
+        <v>7962.02</v>
       </c>
       <c r="BK3">
-        <v>189.24</v>
+        <v>7962.02</v>
       </c>
       <c r="BL3">
-        <v>0</v>
+        <v>7203.58</v>
       </c>
       <c r="BM3">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="BN3">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="BO3">
         <v>0</v>
@@ -1080,10 +1077,10 @@
         <v>0</v>
       </c>
       <c r="BS3">
-        <v>66.18</v>
+        <v>67.34</v>
       </c>
       <c r="BT3">
-        <v>8.72</v>
+        <v>10.66</v>
       </c>
       <c r="BU3">
         <v>0</v>
@@ -1095,13 +1092,13 @@
         <v>0.01</v>
       </c>
       <c r="BX3">
-        <v>74.91</v>
+        <v>78.01</v>
       </c>
       <c r="BY3">
-        <v>70.25</v>
+        <v>73.37</v>
       </c>
       <c r="BZ3">
-        <v>13.63</v>
+        <v>16.39</v>
       </c>
       <c r="CA3">
         <v>0</v>
@@ -1113,13 +1110,13 @@
         <v>0.02</v>
       </c>
       <c r="CD3">
-        <v>83.9</v>
+        <v>89.78</v>
       </c>
       <c r="CE3">
-        <v>90.79</v>
+        <v>93.91</v>
       </c>
       <c r="CF3">
-        <v>20.41</v>
+        <v>24.58</v>
       </c>
       <c r="CG3">
         <v>0</v>
@@ -1131,13 +1128,13 @@
         <v>0.03</v>
       </c>
       <c r="CJ3">
-        <v>111.23</v>
+        <v>118.52</v>
       </c>
       <c r="CK3">
-        <v>1422.1204188482</v>
+        <v>1433.0420969023</v>
       </c>
       <c r="CL3">
-        <v>1474.4698897371</v>
+        <v>1486.4063272368</v>
       </c>
     </row>
     <row r="4">
@@ -1322,10 +1319,10 @@
         <v>0</v>
       </c>
       <c r="CK4">
-        <v>1422.1204188482</v>
+        <v>1433.0420969023</v>
       </c>
       <c r="CL4">
-        <v>1474.4698897371</v>
+        <v>1486.4063272368</v>
       </c>
     </row>
     <row r="5">
@@ -1372,46 +1369,46 @@
         <v>1</v>
       </c>
       <c r="R5">
-        <v>14733.16</v>
+        <v>17745.62</v>
       </c>
       <c r="S5">
-        <v>6735.59</v>
+        <v>7823.03</v>
       </c>
       <c r="T5">
-        <v>7950.13</v>
+        <v>9905.59</v>
       </c>
       <c r="U5">
         <v>0</v>
       </c>
       <c r="V5">
-        <v>59702.2</v>
+        <v>16231.69</v>
       </c>
       <c r="W5">
-        <v>0.13</v>
+        <v>0.03</v>
       </c>
       <c r="Y5">
-        <v>5.29</v>
+        <v>5.62</v>
       </c>
       <c r="AA5">
-        <v>59702.2</v>
+        <v>16231.69</v>
       </c>
       <c r="AB5">
-        <v>59702.2</v>
+        <v>16231.69</v>
       </c>
       <c r="AC5">
-        <v>51113.74</v>
+        <v>6890.79</v>
       </c>
       <c r="AD5">
-        <v>0.13</v>
+        <v>0.03</v>
       </c>
       <c r="AE5">
-        <v>0.13</v>
+        <v>0.03</v>
       </c>
       <c r="AF5">
         <v>0</v>
       </c>
       <c r="AG5">
-        <v>5006.73</v>
+        <v>6324.92</v>
       </c>
       <c r="AH5">
         <v>0</v>
@@ -1432,19 +1429,19 @@
         <v>0</v>
       </c>
       <c r="AR5">
-        <v>59702.2</v>
+        <v>16231.69</v>
       </c>
       <c r="AS5">
-        <v>59702.2</v>
+        <v>16231.69</v>
       </c>
       <c r="AT5">
-        <v>51113.74</v>
+        <v>6890.79</v>
       </c>
       <c r="AU5">
-        <v>0.13</v>
+        <v>0.03</v>
       </c>
       <c r="AV5">
-        <v>0.13</v>
+        <v>0.03</v>
       </c>
       <c r="AW5">
         <v>0</v>
@@ -1459,19 +1456,19 @@
         <v>0</v>
       </c>
       <c r="BA5">
-        <v>59702.2</v>
+        <v>16231.69</v>
       </c>
       <c r="BB5">
-        <v>59702.2</v>
+        <v>16231.69</v>
       </c>
       <c r="BC5">
-        <v>51113.74</v>
+        <v>6890.79</v>
       </c>
       <c r="BD5">
-        <v>0.13</v>
+        <v>0.03</v>
       </c>
       <c r="BE5">
-        <v>0.13</v>
+        <v>0.03</v>
       </c>
       <c r="BF5">
         <v>0</v>
@@ -1486,19 +1483,19 @@
         <v>0</v>
       </c>
       <c r="BJ5">
-        <v>59702.2</v>
+        <v>16231.69</v>
       </c>
       <c r="BK5">
-        <v>59702.2</v>
+        <v>16231.69</v>
       </c>
       <c r="BL5">
-        <v>51113.74</v>
+        <v>6890.79</v>
       </c>
       <c r="BM5">
-        <v>0.13</v>
+        <v>0.03</v>
       </c>
       <c r="BN5">
-        <v>0.13</v>
+        <v>0.03</v>
       </c>
       <c r="BO5">
         <v>0</v>
@@ -1513,10 +1510,10 @@
         <v>0</v>
       </c>
       <c r="BS5">
-        <v>104.15</v>
+        <v>82.03</v>
       </c>
       <c r="BT5">
-        <v>19.41</v>
+        <v>26.71</v>
       </c>
       <c r="BU5">
         <v>0</v>
@@ -1528,13 +1525,13 @@
         <v>0.01</v>
       </c>
       <c r="BX5">
-        <v>123.57</v>
+        <v>108.75</v>
       </c>
       <c r="BY5">
-        <v>104.15</v>
+        <v>125.78</v>
       </c>
       <c r="BZ5">
-        <v>21.19</v>
+        <v>32.26</v>
       </c>
       <c r="CA5">
         <v>0</v>
@@ -1546,13 +1543,13 @@
         <v>0.02</v>
       </c>
       <c r="CD5">
-        <v>125.36</v>
+        <v>158.06</v>
       </c>
       <c r="CE5">
-        <v>128.35</v>
+        <v>149.98</v>
       </c>
       <c r="CF5">
-        <v>24.87</v>
+        <v>36.47</v>
       </c>
       <c r="CG5">
         <v>0</v>
@@ -1564,13 +1561,13 @@
         <v>0.02</v>
       </c>
       <c r="CJ5">
-        <v>153.24</v>
+        <v>186.47</v>
       </c>
       <c r="CK5">
-        <v>1422.1204188482</v>
+        <v>1433.0420969023</v>
       </c>
       <c r="CL5">
-        <v>1474.4698897371</v>
+        <v>1486.4063272368</v>
       </c>
     </row>
     <row r="6">
@@ -1617,46 +1614,43 @@
         <v>1</v>
       </c>
       <c r="R6">
-        <v>3492.26</v>
+        <v>8993.79</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
       <c r="T6">
-        <v>3465.16</v>
+        <v>5073.71</v>
       </c>
       <c r="U6">
         <v>0</v>
       </c>
-      <c r="V6">
-        <v>-80.29</v>
-      </c>
       <c r="W6">
-        <v>27.15</v>
+        <v>3920.08</v>
       </c>
       <c r="AA6">
-        <v>-80.29</v>
+        <v>0</v>
       </c>
       <c r="AB6">
-        <v>-80.29</v>
+        <v>0</v>
       </c>
       <c r="AC6">
         <v>0</v>
       </c>
       <c r="AD6">
-        <v>27.15</v>
+        <v>3920.08</v>
       </c>
       <c r="AE6">
-        <v>27.15</v>
+        <v>3920.08</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>3920.08</v>
       </c>
       <c r="AG6">
-        <v>699.6</v>
+        <v>672.45</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>3920.08</v>
       </c>
       <c r="AI6">
         <v>0</v>
@@ -1674,22 +1668,22 @@
         <v>0</v>
       </c>
       <c r="AR6">
-        <v>-80.29</v>
+        <v>0</v>
       </c>
       <c r="AS6">
-        <v>-80.29</v>
+        <v>0</v>
       </c>
       <c r="AT6">
         <v>0</v>
       </c>
       <c r="AU6">
-        <v>27.15</v>
+        <v>3920.08</v>
       </c>
       <c r="AV6">
-        <v>27.15</v>
+        <v>3920.08</v>
       </c>
       <c r="AW6">
-        <v>0</v>
+        <v>3920.08</v>
       </c>
       <c r="AX6">
         <v>0</v>
@@ -1701,22 +1695,22 @@
         <v>0</v>
       </c>
       <c r="BA6">
-        <v>-80.29</v>
+        <v>0</v>
       </c>
       <c r="BB6">
-        <v>-80.29</v>
+        <v>0</v>
       </c>
       <c r="BC6">
         <v>0</v>
       </c>
       <c r="BD6">
-        <v>27.15</v>
+        <v>3920.08</v>
       </c>
       <c r="BE6">
-        <v>27.15</v>
+        <v>3920.08</v>
       </c>
       <c r="BF6">
-        <v>0</v>
+        <v>3920.08</v>
       </c>
       <c r="BG6">
         <v>0</v>
@@ -1728,22 +1722,22 @@
         <v>0</v>
       </c>
       <c r="BJ6">
-        <v>-80.29</v>
+        <v>0</v>
       </c>
       <c r="BK6">
-        <v>-80.29</v>
+        <v>0</v>
       </c>
       <c r="BL6">
         <v>0</v>
       </c>
       <c r="BM6">
-        <v>27.15</v>
+        <v>3920.08</v>
       </c>
       <c r="BN6">
-        <v>27.15</v>
+        <v>3920.08</v>
       </c>
       <c r="BO6">
-        <v>0</v>
+        <v>3920.08</v>
       </c>
       <c r="BP6">
         <v>0</v>
@@ -1758,7 +1752,7 @@
         <v>31.15</v>
       </c>
       <c r="BT6">
-        <v>5.39</v>
+        <v>6.24</v>
       </c>
       <c r="BU6">
         <v>0</v>
@@ -1770,13 +1764,13 @@
         <v>0</v>
       </c>
       <c r="BX6">
-        <v>36.54</v>
+        <v>37.39</v>
       </c>
       <c r="BY6">
         <v>34.49</v>
       </c>
       <c r="BZ6">
-        <v>8.53</v>
+        <v>9.19</v>
       </c>
       <c r="CA6">
         <v>0</v>
@@ -1788,13 +1782,13 @@
         <v>0</v>
       </c>
       <c r="CD6">
-        <v>43.02</v>
+        <v>43.68</v>
       </c>
       <c r="CE6">
-        <v>109</v>
+        <v>89.38</v>
       </c>
       <c r="CF6">
-        <v>23.73</v>
+        <v>25.48</v>
       </c>
       <c r="CG6">
         <v>0</v>
@@ -1806,13 +1800,13 @@
         <v>0</v>
       </c>
       <c r="CJ6">
-        <v>132.73</v>
+        <v>114.86</v>
       </c>
       <c r="CK6">
-        <v>1422.1204188482</v>
+        <v>1433.0420969023</v>
       </c>
       <c r="CL6">
-        <v>1474.4698897371</v>
+        <v>1486.4063272368</v>
       </c>
     </row>
     <row r="7">
@@ -1859,13 +1853,13 @@
         <v>1</v>
       </c>
       <c r="R7">
-        <v>5049.3</v>
+        <v>5092.37</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
       <c r="T7">
-        <v>5041.96</v>
+        <v>5085.09</v>
       </c>
       <c r="U7">
         <v>0</v>
@@ -1997,7 +1991,7 @@
         <v>0</v>
       </c>
       <c r="BT7">
-        <v>5.26</v>
+        <v>8.5</v>
       </c>
       <c r="BU7">
         <v>0</v>
@@ -2009,13 +2003,13 @@
         <v>0</v>
       </c>
       <c r="BX7">
-        <v>5.26</v>
+        <v>8.5</v>
       </c>
       <c r="BY7">
         <v>0</v>
       </c>
       <c r="BZ7">
-        <v>5.26</v>
+        <v>8.5</v>
       </c>
       <c r="CA7">
         <v>0</v>
@@ -2027,13 +2021,13 @@
         <v>0</v>
       </c>
       <c r="CD7">
-        <v>5.26</v>
+        <v>8.5</v>
       </c>
       <c r="CE7">
         <v>0</v>
       </c>
       <c r="CF7">
-        <v>5.26</v>
+        <v>8.5</v>
       </c>
       <c r="CG7">
         <v>0</v>
@@ -2045,13 +2039,13 @@
         <v>0</v>
       </c>
       <c r="CJ7">
-        <v>5.26</v>
+        <v>8.5</v>
       </c>
       <c r="CK7">
-        <v>1422.1204188482</v>
+        <v>1433.0420969023</v>
       </c>
       <c r="CL7">
-        <v>1474.4698897371</v>
+        <v>1486.4063272368</v>
       </c>
     </row>
     <row r="8">
@@ -2098,13 +2092,13 @@
         <v>1</v>
       </c>
       <c r="R8">
-        <v>5061.23</v>
+        <v>5075.04</v>
       </c>
       <c r="S8">
         <v>0</v>
       </c>
       <c r="T8">
-        <v>5061.23</v>
+        <v>5075.04</v>
       </c>
       <c r="U8">
         <v>0</v>
@@ -2113,7 +2107,7 @@
         <v>0</v>
       </c>
       <c r="BT8">
-        <v>3.42</v>
+        <v>5.45</v>
       </c>
       <c r="BU8">
         <v>0</v>
@@ -2125,13 +2119,13 @@
         <v>0</v>
       </c>
       <c r="BX8">
-        <v>3.42</v>
+        <v>5.45</v>
       </c>
       <c r="BY8">
         <v>0</v>
       </c>
       <c r="BZ8">
-        <v>3.42</v>
+        <v>5.45</v>
       </c>
       <c r="CA8">
         <v>0</v>
@@ -2143,13 +2137,13 @@
         <v>0</v>
       </c>
       <c r="CD8">
-        <v>3.42</v>
+        <v>5.45</v>
       </c>
       <c r="CE8">
         <v>0</v>
       </c>
       <c r="CF8">
-        <v>3.42</v>
+        <v>5.45</v>
       </c>
       <c r="CG8">
         <v>0</v>
@@ -2161,13 +2155,13 @@
         <v>0</v>
       </c>
       <c r="CJ8">
-        <v>3.42</v>
+        <v>5.45</v>
       </c>
       <c r="CK8">
-        <v>1422.1204188482</v>
+        <v>1433.0420969023</v>
       </c>
       <c r="CL8">
-        <v>1474.4698897371</v>
+        <v>1486.4063272368</v>
       </c>
     </row>
     <row r="9">
@@ -2214,49 +2208,49 @@
         <v>1</v>
       </c>
       <c r="R9">
-        <v>2648.89</v>
+        <v>3807.65</v>
       </c>
       <c r="S9">
-        <v>208.49</v>
+        <v>201.95</v>
       </c>
       <c r="T9">
-        <v>1739.52</v>
+        <v>866.42</v>
       </c>
       <c r="U9">
         <v>0</v>
       </c>
       <c r="V9">
-        <v>183.71</v>
+        <v>54103.73</v>
       </c>
       <c r="W9">
-        <v>700.31</v>
+        <v>2701.08</v>
       </c>
       <c r="Y9">
         <v>0.44</v>
       </c>
       <c r="AA9">
-        <v>183.71</v>
+        <v>54103.73</v>
       </c>
       <c r="AB9">
-        <v>183.71</v>
+        <v>54103.73</v>
       </c>
       <c r="AC9">
         <v>0</v>
       </c>
       <c r="AD9">
-        <v>700.31</v>
+        <v>2701.08</v>
       </c>
       <c r="AE9">
-        <v>700.31</v>
+        <v>2701.08</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>2100.32</v>
       </c>
       <c r="AG9">
-        <v>5226.24</v>
+        <v>5126.24</v>
       </c>
       <c r="AH9">
-        <v>0</v>
+        <v>2100.32</v>
       </c>
       <c r="AI9">
         <v>0</v>
@@ -2274,22 +2268,22 @@
         <v>0</v>
       </c>
       <c r="AR9">
-        <v>183.71</v>
+        <v>54103.73</v>
       </c>
       <c r="AS9">
-        <v>183.71</v>
+        <v>54103.73</v>
       </c>
       <c r="AT9">
         <v>0</v>
       </c>
       <c r="AU9">
-        <v>700.31</v>
+        <v>2701.08</v>
       </c>
       <c r="AV9">
-        <v>700.31</v>
+        <v>2701.08</v>
       </c>
       <c r="AW9">
-        <v>0</v>
+        <v>2100.32</v>
       </c>
       <c r="AX9">
         <v>0</v>
@@ -2301,22 +2295,22 @@
         <v>0</v>
       </c>
       <c r="BA9">
-        <v>183.71</v>
+        <v>54103.73</v>
       </c>
       <c r="BB9">
-        <v>183.71</v>
+        <v>54103.73</v>
       </c>
       <c r="BC9">
         <v>0</v>
       </c>
       <c r="BD9">
-        <v>700.31</v>
+        <v>2701.08</v>
       </c>
       <c r="BE9">
-        <v>700.31</v>
+        <v>2701.08</v>
       </c>
       <c r="BF9">
-        <v>0</v>
+        <v>2100.32</v>
       </c>
       <c r="BG9">
         <v>0</v>
@@ -2328,22 +2322,22 @@
         <v>0</v>
       </c>
       <c r="BJ9">
-        <v>183.71</v>
+        <v>54103.73</v>
       </c>
       <c r="BK9">
-        <v>183.71</v>
+        <v>54103.73</v>
       </c>
       <c r="BL9">
         <v>0</v>
       </c>
       <c r="BM9">
-        <v>700.31</v>
+        <v>2701.08</v>
       </c>
       <c r="BN9">
-        <v>700.31</v>
+        <v>2701.08</v>
       </c>
       <c r="BO9">
-        <v>0</v>
+        <v>2100.32</v>
       </c>
       <c r="BP9">
         <v>0</v>
@@ -2355,10 +2349,10 @@
         <v>0</v>
       </c>
       <c r="BS9">
-        <v>50.91</v>
+        <v>57.25</v>
       </c>
       <c r="BT9">
-        <v>5.79</v>
+        <v>4.8</v>
       </c>
       <c r="BU9">
         <v>0</v>
@@ -2370,13 +2364,13 @@
         <v>0</v>
       </c>
       <c r="BX9">
-        <v>56.7</v>
+        <v>62.05</v>
       </c>
       <c r="BY9">
-        <v>115.99</v>
+        <v>106.61</v>
       </c>
       <c r="BZ9">
-        <v>10.38</v>
+        <v>11.68</v>
       </c>
       <c r="CA9">
         <v>0</v>
@@ -2385,16 +2379,16 @@
         <v>0</v>
       </c>
       <c r="CC9">
-        <v>0.43</v>
+        <v>0</v>
       </c>
       <c r="CD9">
-        <v>126.8</v>
+        <v>118.29</v>
       </c>
       <c r="CE9">
-        <v>184.99</v>
+        <v>202.85</v>
       </c>
       <c r="CF9">
-        <v>11.84</v>
+        <v>12.39</v>
       </c>
       <c r="CG9">
         <v>0</v>
@@ -2406,13 +2400,13 @@
         <v>0.52</v>
       </c>
       <c r="CJ9">
-        <v>197.35</v>
+        <v>215.76</v>
       </c>
       <c r="CK9">
-        <v>1422.1204188482</v>
+        <v>1433.0420969023</v>
       </c>
       <c r="CL9">
-        <v>1474.4698897371</v>
+        <v>1486.4063272368</v>
       </c>
     </row>
     <row r="10">
@@ -2459,19 +2453,19 @@
         <v>1</v>
       </c>
       <c r="R10">
-        <v>21109.46</v>
+        <v>21264.69</v>
       </c>
       <c r="S10">
-        <v>6755.11</v>
+        <v>7168.42</v>
       </c>
       <c r="T10">
-        <v>13928.57</v>
+        <v>14027.34</v>
       </c>
       <c r="U10">
         <v>0</v>
       </c>
       <c r="V10">
-        <v>514256.26</v>
+        <v>6534.83</v>
       </c>
       <c r="W10">
         <v>33.49</v>
@@ -2480,13 +2474,13 @@
         <v>18.22</v>
       </c>
       <c r="Y10">
-        <v>12.48</v>
+        <v>12.65</v>
       </c>
       <c r="AA10">
-        <v>514256.26</v>
+        <v>6534.83</v>
       </c>
       <c r="AB10">
-        <v>514256.26</v>
+        <v>6534.83</v>
       </c>
       <c r="AC10">
         <v>0</v>
@@ -2522,10 +2516,10 @@
         <v>0</v>
       </c>
       <c r="AR10">
-        <v>514256.26</v>
+        <v>6534.83</v>
       </c>
       <c r="AS10">
-        <v>514256.26</v>
+        <v>6534.83</v>
       </c>
       <c r="AT10">
         <v>0</v>
@@ -2549,10 +2543,10 @@
         <v>0</v>
       </c>
       <c r="BA10">
-        <v>514256.26</v>
+        <v>6534.83</v>
       </c>
       <c r="BB10">
-        <v>514256.26</v>
+        <v>6534.83</v>
       </c>
       <c r="BC10">
         <v>0</v>
@@ -2576,10 +2570,10 @@
         <v>0</v>
       </c>
       <c r="BJ10">
-        <v>514256.26</v>
+        <v>6534.83</v>
       </c>
       <c r="BK10">
-        <v>514256.26</v>
+        <v>6534.83</v>
       </c>
       <c r="BL10">
         <v>0</v>
@@ -2603,10 +2597,10 @@
         <v>0</v>
       </c>
       <c r="BS10">
-        <v>12.96</v>
+        <v>3.52</v>
       </c>
       <c r="BT10">
-        <v>25.91</v>
+        <v>30.17</v>
       </c>
       <c r="BU10">
         <v>0</v>
@@ -2615,16 +2609,16 @@
         <v>0</v>
       </c>
       <c r="BW10">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="BX10">
-        <v>38.88</v>
+        <v>33.69</v>
       </c>
       <c r="BY10">
-        <v>19.55</v>
+        <v>20.79</v>
       </c>
       <c r="BZ10">
-        <v>41.77</v>
+        <v>46.14</v>
       </c>
       <c r="CA10">
         <v>0</v>
@@ -2636,13 +2630,13 @@
         <v>0.02</v>
       </c>
       <c r="CD10">
-        <v>61.34</v>
+        <v>66.95</v>
       </c>
       <c r="CE10">
-        <v>34.13</v>
+        <v>34.46</v>
       </c>
       <c r="CF10">
-        <v>68.99</v>
+        <v>76.65</v>
       </c>
       <c r="CG10">
         <v>0</v>
@@ -2654,13 +2648,13 @@
         <v>0.06</v>
       </c>
       <c r="CJ10">
-        <v>103.18</v>
+        <v>111.17</v>
       </c>
       <c r="CK10">
-        <v>1422.1204188482</v>
+        <v>1433.0420969023</v>
       </c>
       <c r="CL10">
-        <v>1474.4698897371</v>
+        <v>1486.4063272368</v>
       </c>
     </row>
     <row r="11">
@@ -2707,46 +2701,46 @@
         <v>1</v>
       </c>
       <c r="R11">
-        <v>587.21</v>
+        <v>10594.06</v>
       </c>
       <c r="S11">
-        <v>403.6</v>
+        <v>409.21</v>
       </c>
       <c r="T11">
-        <v>89.81</v>
+        <v>177.9</v>
       </c>
       <c r="U11">
         <v>0</v>
       </c>
       <c r="V11">
-        <v>125162.29</v>
+        <v>430.2</v>
       </c>
       <c r="W11">
-        <v>5.79</v>
+        <v>10006.65</v>
       </c>
       <c r="AA11">
-        <v>125162.29</v>
+        <v>430.2</v>
       </c>
       <c r="AB11">
-        <v>125162.29</v>
+        <v>430.2</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>430.2</v>
       </c>
       <c r="AD11">
-        <v>5.79</v>
+        <v>10006.65</v>
       </c>
       <c r="AE11">
-        <v>5.79</v>
+        <v>6.65</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>0.86</v>
       </c>
       <c r="AG11">
         <v>399.74</v>
       </c>
       <c r="AH11">
-        <v>0</v>
+        <v>0.86</v>
       </c>
       <c r="AI11">
         <v>0</v>
@@ -2764,22 +2758,22 @@
         <v>0</v>
       </c>
       <c r="AR11">
-        <v>125162.29</v>
+        <v>430.2</v>
       </c>
       <c r="AS11">
-        <v>125162.29</v>
+        <v>430.2</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>430.2</v>
       </c>
       <c r="AU11">
-        <v>5.79</v>
+        <v>10006.65</v>
       </c>
       <c r="AV11">
-        <v>5.79</v>
+        <v>6.65</v>
       </c>
       <c r="AW11">
-        <v>0</v>
+        <v>0.86</v>
       </c>
       <c r="AX11">
         <v>0</v>
@@ -2791,22 +2785,22 @@
         <v>0</v>
       </c>
       <c r="BA11">
-        <v>125162.29</v>
+        <v>430.2</v>
       </c>
       <c r="BB11">
-        <v>125162.29</v>
+        <v>430.2</v>
       </c>
       <c r="BC11">
-        <v>0</v>
+        <v>430.2</v>
       </c>
       <c r="BD11">
-        <v>5.79</v>
+        <v>10006.65</v>
       </c>
       <c r="BE11">
-        <v>5.79</v>
+        <v>6.65</v>
       </c>
       <c r="BF11">
-        <v>0</v>
+        <v>0.86</v>
       </c>
       <c r="BG11">
         <v>0</v>
@@ -2818,22 +2812,22 @@
         <v>0</v>
       </c>
       <c r="BJ11">
-        <v>125162.29</v>
+        <v>430.2</v>
       </c>
       <c r="BK11">
-        <v>125162.29</v>
+        <v>430.2</v>
       </c>
       <c r="BL11">
-        <v>0</v>
+        <v>430.2</v>
       </c>
       <c r="BM11">
-        <v>5.79</v>
+        <v>10006.65</v>
       </c>
       <c r="BN11">
-        <v>5.79</v>
+        <v>6.65</v>
       </c>
       <c r="BO11">
-        <v>0</v>
+        <v>0.86</v>
       </c>
       <c r="BP11">
         <v>0</v>
@@ -2845,10 +2839,10 @@
         <v>0</v>
       </c>
       <c r="BS11">
-        <v>4.99</v>
+        <v>33.63</v>
       </c>
       <c r="BT11">
-        <v>0.51</v>
+        <v>0.53</v>
       </c>
       <c r="BU11">
         <v>0</v>
@@ -2860,13 +2854,13 @@
         <v>0</v>
       </c>
       <c r="BX11">
-        <v>5.5</v>
+        <v>34.16</v>
       </c>
       <c r="BY11">
-        <v>4.99</v>
+        <v>33.63</v>
       </c>
       <c r="BZ11">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="CA11">
         <v>0</v>
@@ -2878,13 +2872,13 @@
         <v>0</v>
       </c>
       <c r="CD11">
-        <v>5.95</v>
+        <v>34.63</v>
       </c>
       <c r="CE11">
-        <v>4.99</v>
+        <v>33.63</v>
       </c>
       <c r="CF11">
-        <v>1.68</v>
+        <v>1.86</v>
       </c>
       <c r="CG11">
         <v>0</v>
@@ -2896,13 +2890,13 @@
         <v>0</v>
       </c>
       <c r="CJ11">
-        <v>6.67</v>
+        <v>35.49</v>
       </c>
       <c r="CK11">
-        <v>1422.1204188482</v>
+        <v>1433.0420969023</v>
       </c>
       <c r="CL11">
-        <v>1474.4698897371</v>
+        <v>1486.4063272368</v>
       </c>
     </row>
     <row r="12">
@@ -2993,28 +2987,28 @@
         <v>1</v>
       </c>
       <c r="R13">
-        <v>7513</v>
+        <v>7597.93</v>
       </c>
       <c r="S13">
-        <v>5872.57</v>
+        <v>5942.11</v>
       </c>
       <c r="T13">
-        <v>1609.89</v>
+        <v>1623.11</v>
       </c>
       <c r="U13">
         <v>0</v>
       </c>
       <c r="V13">
-        <v>5115.47</v>
+        <v>5982.97</v>
       </c>
       <c r="Y13">
-        <v>26.94</v>
+        <v>28.55</v>
       </c>
       <c r="AA13">
-        <v>5115.47</v>
+        <v>5982.97</v>
       </c>
       <c r="AB13">
-        <v>5115.47</v>
+        <v>5982.97</v>
       </c>
       <c r="AC13">
         <v>0</v>
@@ -3050,10 +3044,10 @@
         <v>0</v>
       </c>
       <c r="AR13">
-        <v>5115.47</v>
+        <v>5982.97</v>
       </c>
       <c r="AS13">
-        <v>5115.47</v>
+        <v>5982.97</v>
       </c>
       <c r="AT13">
         <v>0</v>
@@ -3077,10 +3071,10 @@
         <v>0</v>
       </c>
       <c r="BA13">
-        <v>5115.47</v>
+        <v>5982.97</v>
       </c>
       <c r="BB13">
-        <v>5115.47</v>
+        <v>5982.97</v>
       </c>
       <c r="BC13">
         <v>0</v>
@@ -3104,10 +3098,10 @@
         <v>0</v>
       </c>
       <c r="BJ13">
-        <v>5115.47</v>
+        <v>5982.97</v>
       </c>
       <c r="BK13">
-        <v>5115.47</v>
+        <v>5982.97</v>
       </c>
       <c r="BL13">
         <v>0</v>
@@ -3134,7 +3128,7 @@
         <v>14.83</v>
       </c>
       <c r="BT13">
-        <v>5.67</v>
+        <v>7.7</v>
       </c>
       <c r="BU13">
         <v>0</v>
@@ -3143,16 +3137,16 @@
         <v>0</v>
       </c>
       <c r="BW13">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="BX13">
-        <v>20.52</v>
+        <v>22.53</v>
       </c>
       <c r="BY13">
         <v>15.58</v>
       </c>
       <c r="BZ13">
-        <v>8.69</v>
+        <v>10.86</v>
       </c>
       <c r="CA13">
         <v>0</v>
@@ -3164,13 +3158,13 @@
         <v>0.05</v>
       </c>
       <c r="CD13">
-        <v>24.32</v>
+        <v>26.49</v>
       </c>
       <c r="CE13">
         <v>39.72</v>
       </c>
       <c r="CF13">
-        <v>13.68</v>
+        <v>16.74</v>
       </c>
       <c r="CG13">
         <v>0</v>
@@ -3182,13 +3176,13 @@
         <v>0.16</v>
       </c>
       <c r="CJ13">
-        <v>53.56</v>
+        <v>56.62</v>
       </c>
       <c r="CK13">
-        <v>1422.1204188482</v>
+        <v>1433.0420969023</v>
       </c>
       <c r="CL13">
-        <v>1474.4698897371</v>
+        <v>1486.4063272368</v>
       </c>
     </row>
     <row r="14">
@@ -3235,13 +3229,13 @@
         <v>1</v>
       </c>
       <c r="R14">
-        <v>4876.16</v>
+        <v>5059.5</v>
       </c>
       <c r="S14">
-        <v>1854.84</v>
+        <v>2036.05</v>
       </c>
       <c r="T14">
-        <v>3005.06</v>
+        <v>3007.15</v>
       </c>
       <c r="U14">
         <v>0</v>
@@ -3376,7 +3370,7 @@
         <v>14.74</v>
       </c>
       <c r="BT14">
-        <v>0.98</v>
+        <v>1.56</v>
       </c>
       <c r="BU14">
         <v>0</v>
@@ -3388,13 +3382,13 @@
         <v>0</v>
       </c>
       <c r="BX14">
-        <v>15.72</v>
+        <v>16.3</v>
       </c>
       <c r="BY14">
         <v>14.74</v>
       </c>
       <c r="BZ14">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="CA14">
         <v>0</v>
@@ -3406,13 +3400,13 @@
         <v>0</v>
       </c>
       <c r="CD14">
-        <v>16.22</v>
+        <v>16.3</v>
       </c>
       <c r="CE14">
         <v>14.74</v>
       </c>
       <c r="CF14">
-        <v>18.03</v>
+        <v>18.61</v>
       </c>
       <c r="CG14">
         <v>0</v>
@@ -3424,13 +3418,13 @@
         <v>0</v>
       </c>
       <c r="CJ14">
-        <v>32.77</v>
+        <v>33.35</v>
       </c>
       <c r="CK14">
-        <v>1422.1204188482</v>
+        <v>1433.0420969023</v>
       </c>
       <c r="CL14">
-        <v>1474.4698897371</v>
+        <v>1486.4063272368</v>
       </c>
     </row>
     <row r="15">
@@ -3477,43 +3471,43 @@
         <v>1</v>
       </c>
       <c r="R15">
-        <v>7072.48</v>
+        <v>7107.63</v>
       </c>
       <c r="S15">
-        <v>3872.92</v>
+        <v>3881.69</v>
       </c>
       <c r="T15">
-        <v>2691.46</v>
+        <v>3217.4</v>
       </c>
       <c r="U15">
         <v>0</v>
       </c>
-      <c r="W15">
-        <v>500.03</v>
+      <c r="V15">
+        <v>433.3</v>
       </c>
       <c r="Y15">
-        <v>8.09</v>
+        <v>8.25</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>433.3</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>433.3</v>
       </c>
       <c r="AC15">
         <v>0</v>
       </c>
       <c r="AD15">
-        <v>500.03</v>
+        <v>0</v>
       </c>
       <c r="AE15">
-        <v>500.03</v>
+        <v>0</v>
       </c>
       <c r="AF15">
         <v>0</v>
       </c>
       <c r="AG15">
-        <v>2444.93</v>
+        <v>0</v>
       </c>
       <c r="AH15">
         <v>0</v>
@@ -3534,19 +3528,19 @@
         <v>0</v>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>433.3</v>
       </c>
       <c r="AS15">
-        <v>0</v>
+        <v>433.3</v>
       </c>
       <c r="AT15">
         <v>0</v>
       </c>
       <c r="AU15">
-        <v>500.03</v>
+        <v>0</v>
       </c>
       <c r="AV15">
-        <v>500.03</v>
+        <v>0</v>
       </c>
       <c r="AW15">
         <v>0</v>
@@ -3561,19 +3555,19 @@
         <v>0</v>
       </c>
       <c r="BA15">
-        <v>0</v>
+        <v>433.3</v>
       </c>
       <c r="BB15">
-        <v>0</v>
+        <v>433.3</v>
       </c>
       <c r="BC15">
         <v>0</v>
       </c>
       <c r="BD15">
-        <v>500.03</v>
+        <v>0</v>
       </c>
       <c r="BE15">
-        <v>500.03</v>
+        <v>0</v>
       </c>
       <c r="BF15">
         <v>0</v>
@@ -3588,19 +3582,19 @@
         <v>0</v>
       </c>
       <c r="BJ15">
-        <v>0</v>
+        <v>433.3</v>
       </c>
       <c r="BK15">
-        <v>0</v>
+        <v>433.3</v>
       </c>
       <c r="BL15">
         <v>0</v>
       </c>
       <c r="BM15">
-        <v>500.03</v>
+        <v>0</v>
       </c>
       <c r="BN15">
-        <v>500.03</v>
+        <v>0</v>
       </c>
       <c r="BO15">
         <v>0</v>
@@ -3618,7 +3612,7 @@
         <v>18.12</v>
       </c>
       <c r="BT15">
-        <v>5.85</v>
+        <v>7.35</v>
       </c>
       <c r="BU15">
         <v>0</v>
@@ -3627,16 +3621,16 @@
         <v>0</v>
       </c>
       <c r="BW15">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="BX15">
-        <v>23.99</v>
+        <v>25.48</v>
       </c>
       <c r="BY15">
         <v>31.41</v>
       </c>
       <c r="BZ15">
-        <v>8.61</v>
+        <v>10.59</v>
       </c>
       <c r="CA15">
         <v>0</v>
@@ -3648,13 +3642,13 @@
         <v>0.03</v>
       </c>
       <c r="CD15">
-        <v>40.05</v>
+        <v>42.03</v>
       </c>
       <c r="CE15">
         <v>41.55</v>
       </c>
       <c r="CF15">
-        <v>11.11</v>
+        <v>13.9</v>
       </c>
       <c r="CG15">
         <v>0</v>
@@ -3666,13 +3660,13 @@
         <v>0.04</v>
       </c>
       <c r="CJ15">
-        <v>52.7</v>
+        <v>55.49</v>
       </c>
       <c r="CK15">
-        <v>1422.1204188482</v>
+        <v>1433.0420969023</v>
       </c>
       <c r="CL15">
-        <v>1474.4698897371</v>
+        <v>1486.4063272368</v>
       </c>
     </row>
     <row r="16">
@@ -3719,37 +3713,37 @@
         <v>1</v>
       </c>
       <c r="R16">
-        <v>173693.16</v>
+        <v>174442.56</v>
       </c>
       <c r="S16">
-        <v>10037.69</v>
+        <v>14583.8</v>
       </c>
       <c r="T16">
-        <v>163618.32</v>
+        <v>159795.9</v>
       </c>
       <c r="U16">
         <v>0</v>
       </c>
       <c r="V16">
-        <v>43302.99</v>
+        <v>30481.69</v>
       </c>
       <c r="W16">
-        <v>6.7</v>
+        <v>41.57</v>
       </c>
       <c r="AA16">
-        <v>43302.99</v>
+        <v>30481.69</v>
       </c>
       <c r="AB16">
-        <v>43302.99</v>
+        <v>30481.69</v>
       </c>
       <c r="AC16">
         <v>0</v>
       </c>
       <c r="AD16">
-        <v>6.7</v>
+        <v>41.57</v>
       </c>
       <c r="AE16">
-        <v>6.7</v>
+        <v>41.57</v>
       </c>
       <c r="AF16">
         <v>0</v>
@@ -3776,19 +3770,19 @@
         <v>0</v>
       </c>
       <c r="AR16">
-        <v>43302.99</v>
+        <v>30481.69</v>
       </c>
       <c r="AS16">
-        <v>43302.99</v>
+        <v>30481.69</v>
       </c>
       <c r="AT16">
         <v>0</v>
       </c>
       <c r="AU16">
-        <v>6.7</v>
+        <v>41.57</v>
       </c>
       <c r="AV16">
-        <v>6.7</v>
+        <v>41.57</v>
       </c>
       <c r="AW16">
         <v>0</v>
@@ -3803,19 +3797,19 @@
         <v>0</v>
       </c>
       <c r="BA16">
-        <v>43302.99</v>
+        <v>30481.69</v>
       </c>
       <c r="BB16">
-        <v>43302.99</v>
+        <v>30481.69</v>
       </c>
       <c r="BC16">
         <v>0</v>
       </c>
       <c r="BD16">
-        <v>6.7</v>
+        <v>41.57</v>
       </c>
       <c r="BE16">
-        <v>6.7</v>
+        <v>41.57</v>
       </c>
       <c r="BF16">
         <v>0</v>
@@ -3830,19 +3824,19 @@
         <v>0</v>
       </c>
       <c r="BJ16">
-        <v>43302.99</v>
+        <v>30481.69</v>
       </c>
       <c r="BK16">
-        <v>43302.99</v>
+        <v>30481.69</v>
       </c>
       <c r="BL16">
         <v>0</v>
       </c>
       <c r="BM16">
-        <v>6.7</v>
+        <v>41.57</v>
       </c>
       <c r="BN16">
-        <v>6.7</v>
+        <v>41.57</v>
       </c>
       <c r="BO16">
         <v>0</v>
@@ -3857,10 +3851,10 @@
         <v>0</v>
       </c>
       <c r="BS16">
-        <v>59.9</v>
+        <v>59.51</v>
       </c>
       <c r="BT16">
-        <v>245.21</v>
+        <v>263.66</v>
       </c>
       <c r="BU16">
         <v>0</v>
@@ -3872,13 +3866,13 @@
         <v>0</v>
       </c>
       <c r="BX16">
-        <v>305.11</v>
+        <v>323.17</v>
       </c>
       <c r="BY16">
-        <v>59.9</v>
+        <v>89.51</v>
       </c>
       <c r="BZ16">
-        <v>270.06</v>
+        <v>368.37</v>
       </c>
       <c r="CA16">
         <v>0</v>
@@ -3890,13 +3884,13 @@
         <v>0</v>
       </c>
       <c r="CD16">
-        <v>329.96</v>
+        <v>457.88</v>
       </c>
       <c r="CE16">
-        <v>267</v>
+        <v>296.61</v>
       </c>
       <c r="CF16">
-        <v>270.06</v>
+        <v>368.37</v>
       </c>
       <c r="CG16">
         <v>0</v>
@@ -3908,13 +3902,13 @@
         <v>0</v>
       </c>
       <c r="CJ16">
-        <v>537.06</v>
+        <v>664.98</v>
       </c>
       <c r="CK16">
-        <v>1422.1204188482</v>
+        <v>1433.0420969023</v>
       </c>
       <c r="CL16">
-        <v>1474.4698897371</v>
+        <v>1486.4063272368</v>
       </c>
     </row>
     <row r="17">
@@ -3961,22 +3955,22 @@
         <v>1</v>
       </c>
       <c r="R17">
-        <v>3031</v>
+        <v>4058.61</v>
       </c>
       <c r="S17">
         <v>0</v>
       </c>
       <c r="T17">
-        <v>2731</v>
+        <v>3814.37</v>
       </c>
       <c r="U17">
         <v>0</v>
       </c>
-      <c r="W17">
-        <v>300</v>
+      <c r="V17">
+        <v>350000</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>350000</v>
       </c>
       <c r="AB17">
         <v>0</v>
@@ -3985,19 +3979,19 @@
         <v>0</v>
       </c>
       <c r="AD17">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AE17">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AF17">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AG17">
         <v>0</v>
       </c>
       <c r="AH17">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AI17">
         <v>0</v>
@@ -4015,7 +4009,7 @@
         <v>0</v>
       </c>
       <c r="AR17">
-        <v>0</v>
+        <v>350000</v>
       </c>
       <c r="AS17">
         <v>0</v>
@@ -4024,13 +4018,13 @@
         <v>0</v>
       </c>
       <c r="AU17">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AV17">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AW17">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AX17">
         <v>0</v>
@@ -4042,7 +4036,7 @@
         <v>0</v>
       </c>
       <c r="BA17">
-        <v>0</v>
+        <v>350000</v>
       </c>
       <c r="BB17">
         <v>0</v>
@@ -4051,13 +4045,13 @@
         <v>0</v>
       </c>
       <c r="BD17">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="BE17">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="BF17">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="BG17">
         <v>0</v>
@@ -4069,7 +4063,7 @@
         <v>0</v>
       </c>
       <c r="BJ17">
-        <v>0</v>
+        <v>350000</v>
       </c>
       <c r="BK17">
         <v>0</v>
@@ -4078,13 +4072,13 @@
         <v>0</v>
       </c>
       <c r="BM17">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="BN17">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="BO17">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="BP17">
         <v>0</v>
@@ -4099,7 +4093,7 @@
         <v>0</v>
       </c>
       <c r="BT17">
-        <v>2.86</v>
+        <v>5.18</v>
       </c>
       <c r="BU17">
         <v>0</v>
@@ -4111,13 +4105,13 @@
         <v>0</v>
       </c>
       <c r="BX17">
-        <v>2.86</v>
+        <v>5.18</v>
       </c>
       <c r="BY17">
         <v>0</v>
       </c>
       <c r="BZ17">
-        <v>2.86</v>
+        <v>5.18</v>
       </c>
       <c r="CA17">
         <v>0</v>
@@ -4129,13 +4123,13 @@
         <v>0</v>
       </c>
       <c r="CD17">
-        <v>2.86</v>
+        <v>5.18</v>
       </c>
       <c r="CE17">
         <v>0</v>
       </c>
       <c r="CF17">
-        <v>2.86</v>
+        <v>5.18</v>
       </c>
       <c r="CG17">
         <v>0</v>
@@ -4147,13 +4141,13 @@
         <v>0</v>
       </c>
       <c r="CJ17">
-        <v>2.86</v>
+        <v>5.18</v>
       </c>
       <c r="CK17">
-        <v>1422.1204188482</v>
+        <v>1433.0420969023</v>
       </c>
       <c r="CL17">
-        <v>1474.4698897371</v>
+        <v>1486.4063272368</v>
       </c>
     </row>
     <row r="18">
@@ -4200,34 +4194,34 @@
         <v>1</v>
       </c>
       <c r="R18">
-        <v>3287.19</v>
+        <v>4430.07</v>
       </c>
       <c r="S18">
-        <v>2919.89</v>
+        <v>3906.26</v>
       </c>
       <c r="T18">
-        <v>330.35</v>
+        <v>508.3</v>
       </c>
       <c r="U18">
         <v>0</v>
       </c>
       <c r="V18">
-        <v>30736.12</v>
+        <v>-0.42</v>
       </c>
       <c r="W18">
         <v>10.61</v>
       </c>
       <c r="Y18">
-        <v>4.73</v>
+        <v>4.9</v>
       </c>
       <c r="AA18">
-        <v>30736.12</v>
+        <v>-0.42</v>
       </c>
       <c r="AB18">
-        <v>30736.12</v>
+        <v>-0.42</v>
       </c>
       <c r="AC18">
-        <v>30307.45</v>
+        <v>0</v>
       </c>
       <c r="AD18">
         <v>10.61</v>
@@ -4260,13 +4254,13 @@
         <v>0</v>
       </c>
       <c r="AR18">
-        <v>30736.12</v>
+        <v>-0.42</v>
       </c>
       <c r="AS18">
-        <v>30736.12</v>
+        <v>-0.42</v>
       </c>
       <c r="AT18">
-        <v>30307.45</v>
+        <v>0</v>
       </c>
       <c r="AU18">
         <v>10.61</v>
@@ -4287,13 +4281,13 @@
         <v>0</v>
       </c>
       <c r="BA18">
-        <v>30736.12</v>
+        <v>-0.42</v>
       </c>
       <c r="BB18">
-        <v>30736.12</v>
+        <v>-0.42</v>
       </c>
       <c r="BC18">
-        <v>30307.45</v>
+        <v>0</v>
       </c>
       <c r="BD18">
         <v>10.61</v>
@@ -4314,13 +4308,13 @@
         <v>0</v>
       </c>
       <c r="BJ18">
-        <v>30736.12</v>
+        <v>-0.42</v>
       </c>
       <c r="BK18">
-        <v>30736.12</v>
+        <v>-0.42</v>
       </c>
       <c r="BL18">
-        <v>30307.45</v>
+        <v>0</v>
       </c>
       <c r="BM18">
         <v>10.61</v>
@@ -4341,10 +4335,10 @@
         <v>0</v>
       </c>
       <c r="BS18">
-        <v>7.57</v>
+        <v>10.31</v>
       </c>
       <c r="BT18">
-        <v>1.74</v>
+        <v>1.51</v>
       </c>
       <c r="BU18">
         <v>0</v>
@@ -4356,13 +4350,13 @@
         <v>0.01</v>
       </c>
       <c r="BX18">
-        <v>9.32</v>
+        <v>11.83</v>
       </c>
       <c r="BY18">
-        <v>16.33</v>
+        <v>18.58</v>
       </c>
       <c r="BZ18">
-        <v>3.15</v>
+        <v>3.37</v>
       </c>
       <c r="CA18">
         <v>0</v>
@@ -4374,13 +4368,13 @@
         <v>0.01</v>
       </c>
       <c r="CD18">
-        <v>19.49</v>
+        <v>21.96</v>
       </c>
       <c r="CE18">
-        <v>16.33</v>
+        <v>22.45</v>
       </c>
       <c r="CF18">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="CG18">
         <v>0</v>
@@ -4392,13 +4386,13 @@
         <v>0.01</v>
       </c>
       <c r="CJ18">
-        <v>19.49</v>
+        <v>25.96</v>
       </c>
       <c r="CK18">
-        <v>1422.1204188482</v>
+        <v>1433.0420969023</v>
       </c>
       <c r="CL18">
-        <v>1474.4698897371</v>
+        <v>1486.4063272368</v>
       </c>
     </row>
     <row r="19">
@@ -4448,10 +4442,10 @@
         <v>0</v>
       </c>
       <c r="BS19">
-        <v>0.91</v>
+        <v>0.08</v>
       </c>
       <c r="BT19">
-        <v>1.7</v>
+        <v>1.18</v>
       </c>
       <c r="BU19">
         <v>0</v>
@@ -4463,7 +4457,7 @@
         <v>0</v>
       </c>
       <c r="BX19">
-        <v>2.61</v>
+        <v>1.26</v>
       </c>
       <c r="BY19">
         <v>0.91</v>
@@ -4590,22 +4584,148 @@
         <v>1</v>
       </c>
       <c r="R21">
-        <v>606.69</v>
+        <v>1598.62</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>583.45</v>
       </c>
       <c r="T21">
-        <v>606.7</v>
+        <v>1015.16</v>
       </c>
       <c r="U21">
         <v>0</v>
       </c>
+      <c r="V21">
+        <v>-1552.44</v>
+      </c>
+      <c r="W21">
+        <v>1.09</v>
+      </c>
+      <c r="AA21">
+        <v>-1552.44</v>
+      </c>
+      <c r="AB21">
+        <v>-1552.44</v>
+      </c>
+      <c r="AC21">
+        <v>0</v>
+      </c>
+      <c r="AD21">
+        <v>1.09</v>
+      </c>
+      <c r="AE21">
+        <v>1.09</v>
+      </c>
+      <c r="AF21">
+        <v>1.09</v>
+      </c>
+      <c r="AG21">
+        <v>0</v>
+      </c>
+      <c r="AH21">
+        <v>1.09</v>
+      </c>
+      <c r="AI21">
+        <v>0</v>
+      </c>
+      <c r="AJ21">
+        <v>0</v>
+      </c>
+      <c r="AK21">
+        <v>0</v>
+      </c>
+      <c r="AL21">
+        <v>0</v>
+      </c>
+      <c r="AM21">
+        <v>0</v>
+      </c>
+      <c r="AR21">
+        <v>-1552.44</v>
+      </c>
+      <c r="AS21">
+        <v>-1552.44</v>
+      </c>
+      <c r="AT21">
+        <v>0</v>
+      </c>
+      <c r="AU21">
+        <v>1.09</v>
+      </c>
+      <c r="AV21">
+        <v>1.09</v>
+      </c>
+      <c r="AW21">
+        <v>1.09</v>
+      </c>
+      <c r="AX21">
+        <v>0</v>
+      </c>
+      <c r="AY21">
+        <v>0</v>
+      </c>
+      <c r="AZ21">
+        <v>0</v>
+      </c>
+      <c r="BA21">
+        <v>-1552.44</v>
+      </c>
+      <c r="BB21">
+        <v>-1552.44</v>
+      </c>
+      <c r="BC21">
+        <v>0</v>
+      </c>
+      <c r="BD21">
+        <v>1.09</v>
+      </c>
+      <c r="BE21">
+        <v>1.09</v>
+      </c>
+      <c r="BF21">
+        <v>1.09</v>
+      </c>
+      <c r="BG21">
+        <v>0</v>
+      </c>
+      <c r="BH21">
+        <v>0</v>
+      </c>
+      <c r="BI21">
+        <v>0</v>
+      </c>
+      <c r="BJ21">
+        <v>-1552.44</v>
+      </c>
+      <c r="BK21">
+        <v>-1552.44</v>
+      </c>
+      <c r="BL21">
+        <v>0</v>
+      </c>
+      <c r="BM21">
+        <v>1.09</v>
+      </c>
+      <c r="BN21">
+        <v>1.09</v>
+      </c>
+      <c r="BO21">
+        <v>1.09</v>
+      </c>
+      <c r="BP21">
+        <v>0</v>
+      </c>
+      <c r="BQ21">
+        <v>0</v>
+      </c>
+      <c r="BR21">
+        <v>0</v>
+      </c>
       <c r="BS21">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="BT21">
-        <v>0.69</v>
+        <v>1.25</v>
       </c>
       <c r="BU21">
         <v>0</v>
@@ -4617,13 +4737,13 @@
         <v>0</v>
       </c>
       <c r="BX21">
-        <v>0.69</v>
+        <v>4.82</v>
       </c>
       <c r="BY21">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="BZ21">
-        <v>0.69</v>
+        <v>1.25</v>
       </c>
       <c r="CA21">
         <v>0</v>
@@ -4635,13 +4755,13 @@
         <v>0</v>
       </c>
       <c r="CD21">
-        <v>0.69</v>
+        <v>4.82</v>
       </c>
       <c r="CE21">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="CF21">
-        <v>0.69</v>
+        <v>1.25</v>
       </c>
       <c r="CG21">
         <v>0</v>
@@ -4653,13 +4773,13 @@
         <v>0</v>
       </c>
       <c r="CJ21">
-        <v>0.69</v>
+        <v>4.82</v>
       </c>
       <c r="CK21">
-        <v>1422.1204188482</v>
+        <v>1433.0420969023</v>
       </c>
       <c r="CL21">
-        <v>1474.4698897371</v>
+        <v>1486.4063272368</v>
       </c>
     </row>
     <row r="22">
@@ -4706,22 +4826,22 @@
         <v>1</v>
       </c>
       <c r="R22">
-        <v>831.48</v>
+        <v>842.3</v>
       </c>
       <c r="S22">
         <v>0</v>
       </c>
       <c r="T22">
-        <v>831.48</v>
+        <v>842.3</v>
       </c>
       <c r="U22">
         <v>0</v>
       </c>
       <c r="BS22">
-        <v>0.73</v>
+        <v>0.4</v>
       </c>
       <c r="BT22">
-        <v>2.86</v>
+        <v>4.33</v>
       </c>
       <c r="BU22">
         <v>0</v>
@@ -4733,13 +4853,13 @@
         <v>0</v>
       </c>
       <c r="BX22">
-        <v>3.59</v>
+        <v>4.73</v>
       </c>
       <c r="BY22">
         <v>0.73</v>
       </c>
       <c r="BZ22">
-        <v>2.86</v>
+        <v>4.57</v>
       </c>
       <c r="CA22">
         <v>0</v>
@@ -4751,13 +4871,13 @@
         <v>0</v>
       </c>
       <c r="CD22">
-        <v>3.59</v>
+        <v>5.3</v>
       </c>
       <c r="CE22">
         <v>0.73</v>
       </c>
       <c r="CF22">
-        <v>2.86</v>
+        <v>4.57</v>
       </c>
       <c r="CG22">
         <v>0</v>
@@ -4769,13 +4889,13 @@
         <v>0</v>
       </c>
       <c r="CJ22">
-        <v>3.59</v>
+        <v>5.3</v>
       </c>
       <c r="CK22">
-        <v>1422.1204188482</v>
+        <v>1433.0420969023</v>
       </c>
       <c r="CL22">
-        <v>1474.4698897371</v>
+        <v>1486.4063272368</v>
       </c>
     </row>
     <row r="23">
@@ -4822,37 +4942,37 @@
         <v>1</v>
       </c>
       <c r="R23">
-        <v>27557.5</v>
+        <v>27094.87</v>
       </c>
       <c r="S23">
         <v>0</v>
       </c>
       <c r="T23">
-        <v>27556.61</v>
+        <v>27094.65</v>
       </c>
       <c r="U23">
         <v>0</v>
       </c>
       <c r="V23">
-        <v>-17.83</v>
+        <v>-0.62</v>
       </c>
       <c r="W23">
-        <v>0.91</v>
+        <v>0.22</v>
       </c>
       <c r="AA23">
-        <v>-17.83</v>
+        <v>-0.62</v>
       </c>
       <c r="AB23">
-        <v>-17.83</v>
+        <v>-0.62</v>
       </c>
       <c r="AC23">
         <v>0</v>
       </c>
       <c r="AD23">
-        <v>0.91</v>
+        <v>0.22</v>
       </c>
       <c r="AE23">
-        <v>0.91</v>
+        <v>0.22</v>
       </c>
       <c r="AF23">
         <v>0</v>
@@ -4879,19 +4999,19 @@
         <v>0</v>
       </c>
       <c r="AR23">
-        <v>-17.83</v>
+        <v>-0.62</v>
       </c>
       <c r="AS23">
-        <v>-17.83</v>
+        <v>-0.62</v>
       </c>
       <c r="AT23">
         <v>0</v>
       </c>
       <c r="AU23">
-        <v>0.91</v>
+        <v>0.22</v>
       </c>
       <c r="AV23">
-        <v>0.91</v>
+        <v>0.22</v>
       </c>
       <c r="AW23">
         <v>0</v>
@@ -4906,19 +5026,19 @@
         <v>0</v>
       </c>
       <c r="BA23">
-        <v>-17.83</v>
+        <v>-0.62</v>
       </c>
       <c r="BB23">
-        <v>-17.83</v>
+        <v>-0.62</v>
       </c>
       <c r="BC23">
         <v>0</v>
       </c>
       <c r="BD23">
-        <v>0.91</v>
+        <v>0.22</v>
       </c>
       <c r="BE23">
-        <v>0.91</v>
+        <v>0.22</v>
       </c>
       <c r="BF23">
         <v>0</v>
@@ -4933,19 +5053,19 @@
         <v>0</v>
       </c>
       <c r="BJ23">
-        <v>-17.83</v>
+        <v>-0.62</v>
       </c>
       <c r="BK23">
-        <v>-17.83</v>
+        <v>-0.62</v>
       </c>
       <c r="BL23">
         <v>0</v>
       </c>
       <c r="BM23">
-        <v>0.91</v>
+        <v>0.22</v>
       </c>
       <c r="BN23">
-        <v>0.91</v>
+        <v>0.22</v>
       </c>
       <c r="BO23">
         <v>0</v>
@@ -4960,10 +5080,10 @@
         <v>0</v>
       </c>
       <c r="BS23">
-        <v>10.39</v>
+        <v>19.34</v>
       </c>
       <c r="BT23">
-        <v>23.54</v>
+        <v>37.04</v>
       </c>
       <c r="BU23">
         <v>0</v>
@@ -4975,13 +5095,13 @@
         <v>0</v>
       </c>
       <c r="BX23">
-        <v>33.93</v>
+        <v>56.38</v>
       </c>
       <c r="BY23">
-        <v>10.39</v>
+        <v>19.34</v>
       </c>
       <c r="BZ23">
-        <v>23.54</v>
+        <v>37.04</v>
       </c>
       <c r="CA23">
         <v>0</v>
@@ -4993,13 +5113,13 @@
         <v>0</v>
       </c>
       <c r="CD23">
-        <v>33.93</v>
+        <v>56.38</v>
       </c>
       <c r="CE23">
-        <v>10.39</v>
+        <v>19.34</v>
       </c>
       <c r="CF23">
-        <v>23.54</v>
+        <v>37.04</v>
       </c>
       <c r="CG23">
         <v>0</v>
@@ -5011,13 +5131,13 @@
         <v>0</v>
       </c>
       <c r="CJ23">
-        <v>33.93</v>
+        <v>56.38</v>
       </c>
       <c r="CK23">
-        <v>1422.1204188482</v>
+        <v>1433.0420969023</v>
       </c>
       <c r="CL23">
-        <v>1474.4698897371</v>
+        <v>1486.4063272368</v>
       </c>
     </row>
     <row r="24">
@@ -5054,14 +5174,209 @@
       <c r="N24" t="str">
         <v>Argentina</v>
       </c>
+      <c r="O24" s="1">
+        <v>46128</v>
+      </c>
       <c r="P24" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>10892.47</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <v>7019.46</v>
+      </c>
+      <c r="U24">
+        <v>0</v>
+      </c>
+      <c r="W24">
+        <v>3873</v>
+      </c>
+      <c r="AA24">
+        <v>0</v>
+      </c>
+      <c r="AB24">
+        <v>0</v>
+      </c>
+      <c r="AC24">
+        <v>0</v>
+      </c>
+      <c r="AD24">
+        <v>3873</v>
+      </c>
+      <c r="AE24">
+        <v>3873</v>
+      </c>
+      <c r="AF24">
+        <v>3873</v>
+      </c>
+      <c r="AG24">
+        <v>0</v>
+      </c>
+      <c r="AH24">
+        <v>3873</v>
+      </c>
+      <c r="AI24">
+        <v>0</v>
+      </c>
+      <c r="AJ24">
+        <v>0</v>
+      </c>
+      <c r="AK24">
+        <v>0</v>
+      </c>
+      <c r="AL24">
+        <v>0</v>
+      </c>
+      <c r="AM24">
+        <v>0</v>
+      </c>
+      <c r="AR24">
+        <v>0</v>
+      </c>
+      <c r="AS24">
+        <v>0</v>
+      </c>
+      <c r="AT24">
+        <v>0</v>
+      </c>
+      <c r="AU24">
+        <v>3873</v>
+      </c>
+      <c r="AV24">
+        <v>3873</v>
+      </c>
+      <c r="AW24">
+        <v>3873</v>
+      </c>
+      <c r="AX24">
+        <v>0</v>
+      </c>
+      <c r="AY24">
+        <v>0</v>
+      </c>
+      <c r="AZ24">
+        <v>0</v>
+      </c>
+      <c r="BA24">
+        <v>0</v>
+      </c>
+      <c r="BB24">
+        <v>0</v>
+      </c>
+      <c r="BC24">
+        <v>0</v>
+      </c>
+      <c r="BD24">
+        <v>3873</v>
+      </c>
+      <c r="BE24">
+        <v>3873</v>
+      </c>
+      <c r="BF24">
+        <v>3873</v>
+      </c>
+      <c r="BG24">
+        <v>0</v>
+      </c>
+      <c r="BH24">
+        <v>0</v>
+      </c>
+      <c r="BI24">
+        <v>0</v>
+      </c>
+      <c r="BJ24">
+        <v>0</v>
+      </c>
+      <c r="BK24">
+        <v>0</v>
+      </c>
+      <c r="BL24">
+        <v>0</v>
+      </c>
+      <c r="BM24">
+        <v>3873</v>
+      </c>
+      <c r="BN24">
+        <v>3873</v>
+      </c>
+      <c r="BO24">
+        <v>3873</v>
+      </c>
+      <c r="BP24">
+        <v>0</v>
+      </c>
+      <c r="BQ24">
+        <v>0</v>
+      </c>
+      <c r="BR24">
+        <v>0</v>
+      </c>
+      <c r="BS24">
+        <v>0.12</v>
+      </c>
+      <c r="BT24">
+        <v>5.34</v>
+      </c>
+      <c r="BU24">
+        <v>0</v>
+      </c>
+      <c r="BV24">
+        <v>0</v>
+      </c>
+      <c r="BW24">
+        <v>0</v>
+      </c>
+      <c r="BX24">
+        <v>5.46</v>
+      </c>
+      <c r="BY24">
+        <v>0.12</v>
+      </c>
+      <c r="BZ24">
+        <v>5.34</v>
+      </c>
+      <c r="CA24">
+        <v>0</v>
+      </c>
+      <c r="CB24">
+        <v>0</v>
+      </c>
+      <c r="CC24">
+        <v>0</v>
+      </c>
+      <c r="CD24">
+        <v>5.46</v>
+      </c>
+      <c r="CE24">
+        <v>0.12</v>
+      </c>
+      <c r="CF24">
+        <v>5.34</v>
+      </c>
+      <c r="CG24">
+        <v>0</v>
+      </c>
+      <c r="CH24">
+        <v>0</v>
+      </c>
+      <c r="CI24">
+        <v>0</v>
+      </c>
+      <c r="CJ24">
+        <v>5.46</v>
+      </c>
+      <c r="CK24">
+        <v>1433.0420969023</v>
+      </c>
+      <c r="CL24">
+        <v>1486.4063272368</v>
       </c>
     </row>
     <row r="25">
@@ -5108,148 +5423,25 @@
         <v>1</v>
       </c>
       <c r="R25">
-        <v>7517.89</v>
+        <v>7393.26</v>
       </c>
       <c r="S25">
-        <v>3440.3</v>
+        <v>4578.08</v>
       </c>
       <c r="T25">
-        <v>4067.84</v>
+        <v>2810.03</v>
       </c>
       <c r="U25">
         <v>0</v>
-      </c>
-      <c r="V25">
-        <v>6553.43</v>
       </c>
       <c r="Y25">
         <v>5.12</v>
       </c>
-      <c r="AA25">
-        <v>6553.43</v>
-      </c>
-      <c r="AB25">
-        <v>6553.43</v>
-      </c>
-      <c r="AC25">
-        <v>6553.43</v>
-      </c>
-      <c r="AD25">
-        <v>0</v>
-      </c>
-      <c r="AE25">
-        <v>0</v>
-      </c>
-      <c r="AF25">
-        <v>0</v>
-      </c>
-      <c r="AG25">
-        <v>0</v>
-      </c>
-      <c r="AH25">
-        <v>0</v>
-      </c>
-      <c r="AI25">
-        <v>0</v>
-      </c>
-      <c r="AJ25">
-        <v>0</v>
-      </c>
-      <c r="AK25">
-        <v>0</v>
-      </c>
-      <c r="AL25">
-        <v>0</v>
-      </c>
-      <c r="AM25">
-        <v>0</v>
-      </c>
-      <c r="AR25">
-        <v>6553.43</v>
-      </c>
-      <c r="AS25">
-        <v>6553.43</v>
-      </c>
-      <c r="AT25">
-        <v>6553.43</v>
-      </c>
-      <c r="AU25">
-        <v>0</v>
-      </c>
-      <c r="AV25">
-        <v>0</v>
-      </c>
-      <c r="AW25">
-        <v>0</v>
-      </c>
-      <c r="AX25">
-        <v>0</v>
-      </c>
-      <c r="AY25">
-        <v>0</v>
-      </c>
-      <c r="AZ25">
-        <v>0</v>
-      </c>
-      <c r="BA25">
-        <v>6553.43</v>
-      </c>
-      <c r="BB25">
-        <v>6553.43</v>
-      </c>
-      <c r="BC25">
-        <v>6553.43</v>
-      </c>
-      <c r="BD25">
-        <v>0</v>
-      </c>
-      <c r="BE25">
-        <v>0</v>
-      </c>
-      <c r="BF25">
-        <v>0</v>
-      </c>
-      <c r="BG25">
-        <v>0</v>
-      </c>
-      <c r="BH25">
-        <v>0</v>
-      </c>
-      <c r="BI25">
-        <v>0</v>
-      </c>
-      <c r="BJ25">
-        <v>6553.43</v>
-      </c>
-      <c r="BK25">
-        <v>6553.43</v>
-      </c>
-      <c r="BL25">
-        <v>6553.43</v>
-      </c>
-      <c r="BM25">
-        <v>0</v>
-      </c>
-      <c r="BN25">
-        <v>0</v>
-      </c>
-      <c r="BO25">
-        <v>0</v>
-      </c>
-      <c r="BP25">
-        <v>0</v>
-      </c>
-      <c r="BQ25">
-        <v>0</v>
-      </c>
-      <c r="BR25">
-        <v>0</v>
-      </c>
       <c r="BS25">
-        <v>20.36</v>
+        <v>26.6</v>
       </c>
       <c r="BT25">
-        <v>16.1</v>
+        <v>23.37</v>
       </c>
       <c r="BU25">
         <v>0</v>
@@ -5261,13 +5453,13 @@
         <v>0.01</v>
       </c>
       <c r="BX25">
-        <v>36.47</v>
+        <v>49.98</v>
       </c>
       <c r="BY25">
-        <v>20.36</v>
+        <v>26.6</v>
       </c>
       <c r="BZ25">
-        <v>16.1</v>
+        <v>23.37</v>
       </c>
       <c r="CA25">
         <v>0</v>
@@ -5279,13 +5471,13 @@
         <v>0.01</v>
       </c>
       <c r="CD25">
-        <v>36.47</v>
+        <v>49.98</v>
       </c>
       <c r="CE25">
-        <v>20.36</v>
+        <v>26.6</v>
       </c>
       <c r="CF25">
-        <v>16.1</v>
+        <v>23.37</v>
       </c>
       <c r="CG25">
         <v>0</v>
@@ -5297,13 +5489,13 @@
         <v>0.01</v>
       </c>
       <c r="CJ25">
-        <v>36.47</v>
+        <v>49.98</v>
       </c>
       <c r="CK25">
-        <v>1422.1204188482</v>
+        <v>1433.0420969023</v>
       </c>
       <c r="CL25">
-        <v>1474.4698897371</v>
+        <v>1486.4063272368</v>
       </c>
     </row>
     <row r="26">
@@ -5350,13 +5542,13 @@
         <v>1</v>
       </c>
       <c r="R26">
-        <v>5013.12</v>
+        <v>5024.53</v>
       </c>
       <c r="S26">
         <v>0</v>
       </c>
       <c r="T26">
-        <v>5013.12</v>
+        <v>5024.53</v>
       </c>
       <c r="U26">
         <v>0</v>
@@ -5365,7 +5557,7 @@
         <v>0</v>
       </c>
       <c r="BT26">
-        <v>2.02</v>
+        <v>3.47</v>
       </c>
       <c r="BU26">
         <v>0</v>
@@ -5377,13 +5569,13 @@
         <v>0</v>
       </c>
       <c r="BX26">
-        <v>2.02</v>
+        <v>3.47</v>
       </c>
       <c r="BY26">
         <v>0</v>
       </c>
       <c r="BZ26">
-        <v>2.02</v>
+        <v>3.47</v>
       </c>
       <c r="CA26">
         <v>0</v>
@@ -5395,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="CD26">
-        <v>2.02</v>
+        <v>3.47</v>
       </c>
       <c r="CE26">
         <v>0</v>
       </c>
       <c r="CF26">
-        <v>2.02</v>
+        <v>3.47</v>
       </c>
       <c r="CG26">
         <v>0</v>
@@ -5413,13 +5605,13 @@
         <v>0</v>
       </c>
       <c r="CJ26">
-        <v>2.02</v>
+        <v>3.47</v>
       </c>
       <c r="CK26">
-        <v>1422.1204188482</v>
+        <v>1433.0420969023</v>
       </c>
       <c r="CL26">
-        <v>1474.4698897371</v>
+        <v>1486.4063272368</v>
       </c>
     </row>
     <row r="27">
@@ -5466,13 +5658,13 @@
         <v>1</v>
       </c>
       <c r="R27">
-        <v>5058.79</v>
+        <v>5128.24</v>
       </c>
       <c r="S27">
         <v>0</v>
       </c>
       <c r="T27">
-        <v>5057.8</v>
+        <v>5127.25</v>
       </c>
       <c r="U27">
         <v>0</v>
@@ -5604,7 +5796,7 @@
         <v>0</v>
       </c>
       <c r="BT27">
-        <v>6.95</v>
+        <v>11.84</v>
       </c>
       <c r="BU27">
         <v>0</v>
@@ -5616,13 +5808,13 @@
         <v>0</v>
       </c>
       <c r="BX27">
-        <v>6.95</v>
+        <v>11.84</v>
       </c>
       <c r="BY27">
         <v>0</v>
       </c>
       <c r="BZ27">
-        <v>6.95</v>
+        <v>11.84</v>
       </c>
       <c r="CA27">
         <v>0</v>
@@ -5634,13 +5826,13 @@
         <v>0</v>
       </c>
       <c r="CD27">
-        <v>6.95</v>
+        <v>11.84</v>
       </c>
       <c r="CE27">
         <v>0</v>
       </c>
       <c r="CF27">
-        <v>6.95</v>
+        <v>11.84</v>
       </c>
       <c r="CG27">
         <v>0</v>
@@ -5652,13 +5844,13 @@
         <v>0</v>
       </c>
       <c r="CJ27">
-        <v>6.95</v>
+        <v>11.84</v>
       </c>
       <c r="CK27">
-        <v>1422.1204188482</v>
+        <v>1433.0420969023</v>
       </c>
       <c r="CL27">
-        <v>1474.4698897371</v>
+        <v>1486.4063272368</v>
       </c>
     </row>
     <row r="28">
@@ -5840,10 +6032,10 @@
         <v>0</v>
       </c>
       <c r="CK28">
-        <v>1422.1204188482</v>
+        <v>1433.0420969023</v>
       </c>
       <c r="CL28">
-        <v>1474.4698897371</v>
+        <v>1486.4063272368</v>
       </c>
     </row>
     <row r="29">
@@ -5890,28 +6082,28 @@
         <v>1</v>
       </c>
       <c r="R29">
-        <v>68174.15</v>
+        <v>68872.26</v>
       </c>
       <c r="S29">
-        <v>11169.32</v>
+        <v>11904.55</v>
       </c>
       <c r="T29">
-        <v>56956.95</v>
+        <v>56920.93</v>
       </c>
       <c r="U29">
         <v>0</v>
       </c>
       <c r="V29">
-        <v>59554.3</v>
+        <v>58427.33</v>
       </c>
       <c r="Y29">
         <v>5.99</v>
       </c>
       <c r="AA29">
-        <v>59554.3</v>
+        <v>58427.33</v>
       </c>
       <c r="AB29">
-        <v>59554.3</v>
+        <v>58427.33</v>
       </c>
       <c r="AC29">
         <v>0</v>
@@ -5947,10 +6139,10 @@
         <v>0</v>
       </c>
       <c r="AR29">
-        <v>59554.3</v>
+        <v>58427.33</v>
       </c>
       <c r="AS29">
-        <v>59554.3</v>
+        <v>58427.33</v>
       </c>
       <c r="AT29">
         <v>0</v>
@@ -5974,10 +6166,10 @@
         <v>0</v>
       </c>
       <c r="BA29">
-        <v>59554.3</v>
+        <v>58427.33</v>
       </c>
       <c r="BB29">
-        <v>59554.3</v>
+        <v>58427.33</v>
       </c>
       <c r="BC29">
         <v>0</v>
@@ -6001,10 +6193,10 @@
         <v>0</v>
       </c>
       <c r="BJ29">
-        <v>59554.3</v>
+        <v>58427.33</v>
       </c>
       <c r="BK29">
-        <v>59554.3</v>
+        <v>58427.33</v>
       </c>
       <c r="BL29">
         <v>0</v>
@@ -6028,10 +6220,10 @@
         <v>0</v>
       </c>
       <c r="BS29">
-        <v>68.27</v>
+        <v>70.87</v>
       </c>
       <c r="BT29">
-        <v>27.27</v>
+        <v>61.62</v>
       </c>
       <c r="BU29">
         <v>0</v>
@@ -6043,13 +6235,13 @@
         <v>0.01</v>
       </c>
       <c r="BX29">
-        <v>95.55</v>
+        <v>132.5</v>
       </c>
       <c r="BY29">
-        <v>68.27</v>
+        <v>70.87</v>
       </c>
       <c r="BZ29">
-        <v>27.27</v>
+        <v>61.62</v>
       </c>
       <c r="CA29">
         <v>0</v>
@@ -6061,13 +6253,13 @@
         <v>0.01</v>
       </c>
       <c r="CD29">
-        <v>95.55</v>
+        <v>132.5</v>
       </c>
       <c r="CE29">
-        <v>68.27</v>
+        <v>70.87</v>
       </c>
       <c r="CF29">
-        <v>27.27</v>
+        <v>61.62</v>
       </c>
       <c r="CG29">
         <v>0</v>
@@ -6079,13 +6271,13 @@
         <v>0.01</v>
       </c>
       <c r="CJ29">
-        <v>95.55</v>
+        <v>132.5</v>
       </c>
       <c r="CK29">
-        <v>1422.1204188482</v>
+        <v>1433.0420969023</v>
       </c>
       <c r="CL29">
-        <v>1474.4698897371</v>
+        <v>1486.4063272368</v>
       </c>
     </row>
     <row r="30">
@@ -6160,19 +6352,252 @@
       <c r="N31" t="str">
         <v>Argentina</v>
       </c>
+      <c r="O31" s="1">
+        <v>46118</v>
+      </c>
       <c r="P31" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R31">
+        <v>36.58</v>
+      </c>
+      <c r="S31">
+        <v>29.34</v>
+      </c>
+      <c r="T31">
+        <v>0</v>
+      </c>
+      <c r="U31">
+        <v>0</v>
+      </c>
+      <c r="W31">
+        <v>7.24</v>
+      </c>
+      <c r="AA31">
+        <v>0</v>
+      </c>
+      <c r="AB31">
+        <v>0</v>
+      </c>
+      <c r="AC31">
+        <v>0</v>
+      </c>
+      <c r="AD31">
+        <v>7.24</v>
+      </c>
+      <c r="AE31">
+        <v>7.24</v>
+      </c>
+      <c r="AF31">
+        <v>7.24</v>
+      </c>
+      <c r="AG31">
+        <v>0</v>
+      </c>
+      <c r="AH31">
+        <v>7.24</v>
+      </c>
+      <c r="AI31">
+        <v>0</v>
+      </c>
+      <c r="AJ31">
+        <v>0</v>
+      </c>
+      <c r="AK31">
+        <v>0</v>
+      </c>
+      <c r="AL31">
+        <v>0</v>
+      </c>
+      <c r="AM31">
+        <v>0</v>
+      </c>
+      <c r="AR31">
+        <v>0</v>
+      </c>
+      <c r="AS31">
+        <v>0</v>
+      </c>
+      <c r="AT31">
+        <v>0</v>
+      </c>
+      <c r="AU31">
+        <v>7.24</v>
+      </c>
+      <c r="AV31">
+        <v>7.24</v>
+      </c>
+      <c r="AW31">
+        <v>7.24</v>
+      </c>
+      <c r="AX31">
+        <v>0</v>
+      </c>
+      <c r="AY31">
+        <v>0</v>
+      </c>
+      <c r="AZ31">
+        <v>0</v>
+      </c>
+      <c r="BA31">
+        <v>0</v>
+      </c>
+      <c r="BB31">
+        <v>0</v>
+      </c>
+      <c r="BC31">
+        <v>0</v>
+      </c>
+      <c r="BD31">
+        <v>7.24</v>
+      </c>
+      <c r="BE31">
+        <v>7.24</v>
+      </c>
+      <c r="BF31">
+        <v>7.24</v>
+      </c>
+      <c r="BG31">
+        <v>0</v>
+      </c>
+      <c r="BH31">
+        <v>0</v>
+      </c>
+      <c r="BI31">
+        <v>0</v>
+      </c>
+      <c r="BJ31">
+        <v>0</v>
+      </c>
+      <c r="BK31">
+        <v>0</v>
+      </c>
+      <c r="BL31">
+        <v>0</v>
+      </c>
+      <c r="BM31">
+        <v>7.24</v>
+      </c>
+      <c r="BN31">
+        <v>7.24</v>
+      </c>
+      <c r="BO31">
+        <v>7.24</v>
+      </c>
+      <c r="BP31">
+        <v>0</v>
+      </c>
+      <c r="BQ31">
+        <v>0</v>
+      </c>
+      <c r="BR31">
+        <v>0</v>
+      </c>
+      <c r="BS31">
+        <v>29.74</v>
+      </c>
+      <c r="BT31">
+        <v>0</v>
+      </c>
+      <c r="BU31">
+        <v>0</v>
+      </c>
+      <c r="BV31">
+        <v>0</v>
+      </c>
+      <c r="BW31">
+        <v>0</v>
+      </c>
+      <c r="BX31">
+        <v>29.74</v>
+      </c>
+      <c r="BY31">
+        <v>29.74</v>
+      </c>
+      <c r="BZ31">
+        <v>0</v>
+      </c>
+      <c r="CA31">
+        <v>0</v>
+      </c>
+      <c r="CB31">
+        <v>0</v>
+      </c>
+      <c r="CC31">
+        <v>0</v>
+      </c>
+      <c r="CD31">
+        <v>29.74</v>
+      </c>
+      <c r="CE31">
+        <v>29.74</v>
+      </c>
+      <c r="CF31">
+        <v>0</v>
+      </c>
+      <c r="CG31">
+        <v>0</v>
+      </c>
+      <c r="CH31">
+        <v>0</v>
+      </c>
+      <c r="CI31">
+        <v>0</v>
+      </c>
+      <c r="CJ31">
+        <v>29.74</v>
+      </c>
+      <c r="CK31">
+        <v>1433.0420969023</v>
+      </c>
+      <c r="CL31">
+        <v>1486.4063272368</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>1574965</v>
+      </c>
+      <c r="D32" t="str">
+        <v>5001104</v>
+      </c>
+      <c r="E32" t="str">
+        <v>DEGANO GREGORIO MARTIN</v>
+      </c>
+      <c r="F32" s="1">
+        <v>46119</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32" t="str">
+        <v>IFA 5767</v>
+      </c>
+      <c r="I32" t="str">
+        <v>Vicien/DV - Marketing - IFA</v>
+      </c>
+      <c r="J32" t="str">
+        <v>IFA</v>
+      </c>
+      <c r="N32" t="str">
+        <v>Internacional</v>
+      </c>
+      <c r="P32" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q32">
+        <v>0</v>
+      </c>
+      <c r="R32">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:CL31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:CL32"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/cluster.xlsx
+++ b/data/cluster.xlsx
@@ -376,7 +376,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CL32"/>
+  <dimension ref="A1:CL36"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -832,7 +832,7 @@
         <v>0</v>
       </c>
       <c r="BS2">
-        <v>55.14</v>
+        <v>0.25</v>
       </c>
       <c r="BT2">
         <v>0</v>
@@ -847,10 +847,10 @@
         <v>0</v>
       </c>
       <c r="BX2">
-        <v>55.14</v>
+        <v>0.25</v>
       </c>
       <c r="BY2">
-        <v>265.34</v>
+        <v>264.07</v>
       </c>
       <c r="BZ2">
         <v>0.77</v>
@@ -865,10 +865,10 @@
         <v>0</v>
       </c>
       <c r="CD2">
-        <v>266.11</v>
+        <v>264.84</v>
       </c>
       <c r="CE2">
-        <v>383.12</v>
+        <v>378.09</v>
       </c>
       <c r="CF2">
         <v>0.77</v>
@@ -883,13 +883,13 @@
         <v>0</v>
       </c>
       <c r="CJ2">
-        <v>383.89</v>
+        <v>378.86</v>
       </c>
       <c r="CK2">
-        <v>1433.0420969023</v>
+        <v>1425.46875</v>
       </c>
       <c r="CL2">
-        <v>1486.4063272368</v>
+        <v>1479.5653584171</v>
       </c>
     </row>
     <row r="3">
@@ -939,43 +939,46 @@
         <v>1</v>
       </c>
       <c r="R3">
-        <v>7170.67</v>
+        <v>7293.95</v>
       </c>
       <c r="S3">
-        <v>5402.52</v>
+        <v>5457.47</v>
       </c>
       <c r="T3">
-        <v>1750.89</v>
+        <v>1809.46</v>
       </c>
       <c r="U3">
         <v>0</v>
       </c>
       <c r="V3">
-        <v>7962.02</v>
+        <v>9283.96</v>
+      </c>
+      <c r="W3">
+        <v>8.72</v>
       </c>
       <c r="Y3">
-        <v>11.71</v>
+        <v>11.81</v>
       </c>
       <c r="AA3">
-        <v>7962.02</v>
+        <v>9283.96</v>
       </c>
       <c r="AB3">
-        <v>7962.02</v>
+        <v>9283.96</v>
       </c>
       <c r="AC3">
-        <v>7203.58</v>
+        <v>6476.01</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>8.72</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>8.72</v>
       </c>
       <c r="AF3">
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>5150.58</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -996,19 +999,19 @@
         <v>0</v>
       </c>
       <c r="AR3">
-        <v>7962.02</v>
+        <v>9283.96</v>
       </c>
       <c r="AS3">
-        <v>7962.02</v>
+        <v>9283.96</v>
       </c>
       <c r="AT3">
-        <v>7203.58</v>
+        <v>6476.01</v>
       </c>
       <c r="AU3">
-        <v>0</v>
+        <v>8.72</v>
       </c>
       <c r="AV3">
-        <v>0</v>
+        <v>8.72</v>
       </c>
       <c r="AW3">
         <v>0</v>
@@ -1023,19 +1026,19 @@
         <v>0</v>
       </c>
       <c r="BA3">
-        <v>7962.02</v>
+        <v>9283.96</v>
       </c>
       <c r="BB3">
-        <v>7962.02</v>
+        <v>9283.96</v>
       </c>
       <c r="BC3">
-        <v>7203.58</v>
+        <v>6476.01</v>
       </c>
       <c r="BD3">
-        <v>0</v>
+        <v>8.72</v>
       </c>
       <c r="BE3">
-        <v>0</v>
+        <v>8.72</v>
       </c>
       <c r="BF3">
         <v>0</v>
@@ -1050,19 +1053,19 @@
         <v>0</v>
       </c>
       <c r="BJ3">
-        <v>7962.02</v>
+        <v>9283.96</v>
       </c>
       <c r="BK3">
-        <v>7962.02</v>
+        <v>9283.96</v>
       </c>
       <c r="BL3">
-        <v>7203.58</v>
+        <v>6476.01</v>
       </c>
       <c r="BM3">
-        <v>0</v>
+        <v>8.72</v>
       </c>
       <c r="BN3">
-        <v>0</v>
+        <v>8.72</v>
       </c>
       <c r="BO3">
         <v>0</v>
@@ -1080,7 +1083,7 @@
         <v>67.34</v>
       </c>
       <c r="BT3">
-        <v>10.66</v>
+        <v>11.31</v>
       </c>
       <c r="BU3">
         <v>0</v>
@@ -1089,16 +1092,16 @@
         <v>0</v>
       </c>
       <c r="BW3">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="BX3">
-        <v>78.01</v>
+        <v>78.69</v>
       </c>
       <c r="BY3">
         <v>73.37</v>
       </c>
       <c r="BZ3">
-        <v>16.39</v>
+        <v>17.84</v>
       </c>
       <c r="CA3">
         <v>0</v>
@@ -1107,16 +1110,16 @@
         <v>0</v>
       </c>
       <c r="CC3">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="CD3">
-        <v>89.78</v>
+        <v>91.26</v>
       </c>
       <c r="CE3">
         <v>93.91</v>
       </c>
       <c r="CF3">
-        <v>24.58</v>
+        <v>26.83</v>
       </c>
       <c r="CG3">
         <v>0</v>
@@ -1125,33 +1128,33 @@
         <v>0</v>
       </c>
       <c r="CI3">
-        <v>0.03</v>
+        <v>0.07</v>
       </c>
       <c r="CJ3">
-        <v>118.52</v>
+        <v>120.81</v>
       </c>
       <c r="CK3">
-        <v>1433.0420969023</v>
+        <v>1425.46875</v>
       </c>
       <c r="CL3">
-        <v>1486.4063272368</v>
+        <v>1479.5653584171</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>70167</v>
+        <v>62857</v>
       </c>
       <c r="B4" t="str">
-        <v>36123</v>
+        <v>294941</v>
       </c>
       <c r="C4" t="str">
-        <v>67490</v>
+        <v>60133</v>
       </c>
       <c r="E4" t="str">
-        <v>JAIME TOMAS VALENTIN</v>
+        <v>DELFIN SANTIAGO JAVIER</v>
       </c>
       <c r="F4" s="1">
-        <v>43782</v>
+        <v>43754</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1166,180 +1169,111 @@
         <v>IFA</v>
       </c>
       <c r="K4" t="str">
-        <v>IFA 1</v>
+        <v>IFA 4</v>
       </c>
       <c r="N4" t="str">
         <v>Argentina</v>
       </c>
       <c r="O4" s="1">
-        <v>43789</v>
+        <v>43909</v>
       </c>
       <c r="P4" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R4">
-        <v>-4.61</v>
+        <v>64930.66</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>3237.7</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>61671.65</v>
       </c>
       <c r="U4">
         <v>0</v>
       </c>
-      <c r="V4">
-        <v>859.63</v>
-      </c>
-      <c r="W4">
-        <v>-5.21</v>
-      </c>
-      <c r="AA4">
-        <v>859.63</v>
-      </c>
-      <c r="AB4">
-        <v>859.63</v>
-      </c>
-      <c r="AC4">
-        <v>133.1</v>
-      </c>
-      <c r="AD4">
-        <v>-5.21</v>
-      </c>
-      <c r="AE4">
-        <v>-5.21</v>
-      </c>
-      <c r="AF4">
-        <v>0</v>
-      </c>
-      <c r="AG4">
-        <v>0</v>
-      </c>
-      <c r="AH4">
-        <v>-5.21</v>
-      </c>
-      <c r="AI4">
-        <v>0</v>
-      </c>
-      <c r="AJ4">
-        <v>0</v>
-      </c>
-      <c r="AK4">
-        <v>0</v>
-      </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
-        <v>0</v>
-      </c>
-      <c r="AR4">
-        <v>859.63</v>
-      </c>
-      <c r="AS4">
-        <v>859.63</v>
-      </c>
-      <c r="AT4">
-        <v>133.1</v>
-      </c>
-      <c r="AU4">
-        <v>-5.21</v>
-      </c>
-      <c r="AV4">
-        <v>-5.21</v>
-      </c>
-      <c r="AW4">
-        <v>0</v>
-      </c>
-      <c r="AX4">
-        <v>0</v>
-      </c>
-      <c r="AY4">
-        <v>0</v>
-      </c>
-      <c r="AZ4">
-        <v>0</v>
-      </c>
-      <c r="BA4">
-        <v>859.63</v>
-      </c>
-      <c r="BB4">
-        <v>859.63</v>
-      </c>
-      <c r="BC4">
-        <v>133.1</v>
-      </c>
-      <c r="BD4">
-        <v>-5.21</v>
-      </c>
-      <c r="BE4">
-        <v>-5.21</v>
-      </c>
-      <c r="BF4">
-        <v>0</v>
-      </c>
-      <c r="BG4">
-        <v>0</v>
-      </c>
-      <c r="BH4">
-        <v>0</v>
-      </c>
-      <c r="BI4">
-        <v>0</v>
-      </c>
-      <c r="BJ4">
-        <v>859.63</v>
-      </c>
-      <c r="BK4">
-        <v>859.63</v>
-      </c>
-      <c r="BL4">
-        <v>133.1</v>
-      </c>
-      <c r="BM4">
-        <v>-5.21</v>
-      </c>
-      <c r="BN4">
-        <v>-5.21</v>
-      </c>
-      <c r="BO4">
-        <v>0</v>
-      </c>
-      <c r="BP4">
-        <v>0</v>
-      </c>
-      <c r="BQ4">
-        <v>0</v>
-      </c>
-      <c r="BR4">
-        <v>0</v>
+      <c r="Y4">
+        <v>21.37</v>
+      </c>
+      <c r="BS4">
+        <v>49.32</v>
+      </c>
+      <c r="BT4">
+        <v>46.61</v>
+      </c>
+      <c r="BU4">
+        <v>0</v>
+      </c>
+      <c r="BV4">
+        <v>0</v>
+      </c>
+      <c r="BW4">
+        <v>0</v>
+      </c>
+      <c r="BX4">
+        <v>95.93</v>
+      </c>
+      <c r="BY4">
+        <v>54.19</v>
+      </c>
+      <c r="BZ4">
+        <v>47.79</v>
+      </c>
+      <c r="CA4">
+        <v>0</v>
+      </c>
+      <c r="CB4">
+        <v>0</v>
+      </c>
+      <c r="CC4">
+        <v>0</v>
+      </c>
+      <c r="CD4">
+        <v>101.98</v>
+      </c>
+      <c r="CE4">
+        <v>498.34</v>
+      </c>
+      <c r="CF4">
+        <v>54.67</v>
+      </c>
+      <c r="CG4">
+        <v>0</v>
+      </c>
+      <c r="CH4">
+        <v>0</v>
+      </c>
+      <c r="CI4">
+        <v>0.01</v>
+      </c>
+      <c r="CJ4">
+        <v>553.02</v>
       </c>
       <c r="CK4">
-        <v>1433.0420969023</v>
+        <v>1425.46875</v>
       </c>
       <c r="CL4">
-        <v>1486.4063272368</v>
+        <v>1479.5653584171</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>74679</v>
+        <v>70167</v>
       </c>
       <c r="B5" t="str">
-        <v>304685</v>
+        <v>36123</v>
       </c>
       <c r="C5" t="str">
-        <v>71908</v>
+        <v>67490</v>
       </c>
       <c r="E5" t="str">
-        <v>TOSO GUIDO</v>
+        <v>JAIME TOMAS VALENTIN</v>
       </c>
       <c r="F5" s="1">
-        <v>43826</v>
+        <v>43782</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1354,64 +1288,61 @@
         <v>IFA</v>
       </c>
       <c r="K5" t="str">
-        <v>IFA 3</v>
+        <v>IFA 1</v>
       </c>
       <c r="N5" t="str">
         <v>Argentina</v>
       </c>
       <c r="O5" s="1">
-        <v>45794</v>
+        <v>43789</v>
       </c>
       <c r="P5" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R5">
-        <v>17745.62</v>
+        <v>-4.61</v>
       </c>
       <c r="S5">
-        <v>7823.03</v>
+        <v>0</v>
       </c>
       <c r="T5">
-        <v>9905.59</v>
+        <v>0</v>
       </c>
       <c r="U5">
         <v>0</v>
       </c>
       <c r="V5">
-        <v>16231.69</v>
+        <v>859.63</v>
       </c>
       <c r="W5">
-        <v>0.03</v>
-      </c>
-      <c r="Y5">
-        <v>5.62</v>
+        <v>-5.21</v>
       </c>
       <c r="AA5">
-        <v>16231.69</v>
+        <v>859.63</v>
       </c>
       <c r="AB5">
-        <v>16231.69</v>
+        <v>859.63</v>
       </c>
       <c r="AC5">
-        <v>6890.79</v>
+        <v>133.1</v>
       </c>
       <c r="AD5">
-        <v>0.03</v>
+        <v>-5.21</v>
       </c>
       <c r="AE5">
-        <v>0.03</v>
+        <v>-5.21</v>
       </c>
       <c r="AF5">
         <v>0</v>
       </c>
       <c r="AG5">
-        <v>6324.92</v>
+        <v>0</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>-5.21</v>
       </c>
       <c r="AI5">
         <v>0</v>
@@ -1429,19 +1360,19 @@
         <v>0</v>
       </c>
       <c r="AR5">
-        <v>16231.69</v>
+        <v>859.63</v>
       </c>
       <c r="AS5">
-        <v>16231.69</v>
+        <v>859.63</v>
       </c>
       <c r="AT5">
-        <v>6890.79</v>
+        <v>133.1</v>
       </c>
       <c r="AU5">
-        <v>0.03</v>
+        <v>-5.21</v>
       </c>
       <c r="AV5">
-        <v>0.03</v>
+        <v>-5.21</v>
       </c>
       <c r="AW5">
         <v>0</v>
@@ -1456,19 +1387,19 @@
         <v>0</v>
       </c>
       <c r="BA5">
-        <v>16231.69</v>
+        <v>859.63</v>
       </c>
       <c r="BB5">
-        <v>16231.69</v>
+        <v>859.63</v>
       </c>
       <c r="BC5">
-        <v>6890.79</v>
+        <v>133.1</v>
       </c>
       <c r="BD5">
-        <v>0.03</v>
+        <v>-5.21</v>
       </c>
       <c r="BE5">
-        <v>0.03</v>
+        <v>-5.21</v>
       </c>
       <c r="BF5">
         <v>0</v>
@@ -1483,19 +1414,19 @@
         <v>0</v>
       </c>
       <c r="BJ5">
-        <v>16231.69</v>
+        <v>859.63</v>
       </c>
       <c r="BK5">
-        <v>16231.69</v>
+        <v>859.63</v>
       </c>
       <c r="BL5">
-        <v>6890.79</v>
+        <v>133.1</v>
       </c>
       <c r="BM5">
-        <v>0.03</v>
+        <v>-5.21</v>
       </c>
       <c r="BN5">
-        <v>0.03</v>
+        <v>-5.21</v>
       </c>
       <c r="BO5">
         <v>0</v>
@@ -1509,82 +1440,28 @@
       <c r="BR5">
         <v>0</v>
       </c>
-      <c r="BS5">
-        <v>82.03</v>
-      </c>
-      <c r="BT5">
-        <v>26.71</v>
-      </c>
-      <c r="BU5">
-        <v>0</v>
-      </c>
-      <c r="BV5">
-        <v>0</v>
-      </c>
-      <c r="BW5">
-        <v>0.01</v>
-      </c>
-      <c r="BX5">
-        <v>108.75</v>
-      </c>
-      <c r="BY5">
-        <v>125.78</v>
-      </c>
-      <c r="BZ5">
-        <v>32.26</v>
-      </c>
-      <c r="CA5">
-        <v>0</v>
-      </c>
-      <c r="CB5">
-        <v>0</v>
-      </c>
-      <c r="CC5">
-        <v>0.02</v>
-      </c>
-      <c r="CD5">
-        <v>158.06</v>
-      </c>
-      <c r="CE5">
-        <v>149.98</v>
-      </c>
-      <c r="CF5">
-        <v>36.47</v>
-      </c>
-      <c r="CG5">
-        <v>0</v>
-      </c>
-      <c r="CH5">
-        <v>0</v>
-      </c>
-      <c r="CI5">
-        <v>0.02</v>
-      </c>
-      <c r="CJ5">
-        <v>186.47</v>
-      </c>
       <c r="CK5">
-        <v>1433.0420969023</v>
+        <v>1425.46875</v>
       </c>
       <c r="CL5">
-        <v>1486.4063272368</v>
+        <v>1479.5653584171</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>76054</v>
+        <v>74679</v>
       </c>
       <c r="B6" t="str">
-        <v>305892</v>
+        <v>304685</v>
       </c>
       <c r="C6" t="str">
-        <v>73283</v>
+        <v>71908</v>
       </c>
       <c r="E6" t="str">
-        <v>MIRANDA LUCIA</v>
+        <v>TOSO GUIDO</v>
       </c>
       <c r="F6" s="1">
-        <v>43829</v>
+        <v>43826</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1599,13 +1476,13 @@
         <v>IFA</v>
       </c>
       <c r="K6" t="str">
-        <v>IFA 4</v>
+        <v>IFA 3</v>
       </c>
       <c r="N6" t="str">
         <v>Argentina</v>
       </c>
       <c r="O6" s="1">
-        <v>43840</v>
+        <v>45794</v>
       </c>
       <c r="P6" t="str">
         <v>1</v>
@@ -1614,43 +1491,49 @@
         <v>1</v>
       </c>
       <c r="R6">
-        <v>8993.79</v>
+        <v>18012.98</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>7980.63</v>
       </c>
       <c r="T6">
-        <v>5073.71</v>
+        <v>10011</v>
       </c>
       <c r="U6">
         <v>0</v>
       </c>
+      <c r="V6">
+        <v>20031.99</v>
+      </c>
       <c r="W6">
-        <v>3920.08</v>
+        <v>0.03</v>
+      </c>
+      <c r="Y6">
+        <v>7.26</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>20031.99</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>20031.99</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>5807.29</v>
       </c>
       <c r="AD6">
-        <v>3920.08</v>
+        <v>0.03</v>
       </c>
       <c r="AE6">
-        <v>3920.08</v>
+        <v>0.03</v>
       </c>
       <c r="AF6">
-        <v>3920.08</v>
+        <v>0</v>
       </c>
       <c r="AG6">
-        <v>672.45</v>
+        <v>6324.92</v>
       </c>
       <c r="AH6">
-        <v>3920.08</v>
+        <v>0</v>
       </c>
       <c r="AI6">
         <v>0</v>
@@ -1668,22 +1551,22 @@
         <v>0</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>20031.99</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>20031.99</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>5807.29</v>
       </c>
       <c r="AU6">
-        <v>3920.08</v>
+        <v>0.03</v>
       </c>
       <c r="AV6">
-        <v>3920.08</v>
+        <v>0.03</v>
       </c>
       <c r="AW6">
-        <v>3920.08</v>
+        <v>0</v>
       </c>
       <c r="AX6">
         <v>0</v>
@@ -1695,22 +1578,22 @@
         <v>0</v>
       </c>
       <c r="BA6">
-        <v>0</v>
+        <v>20031.99</v>
       </c>
       <c r="BB6">
-        <v>0</v>
+        <v>20031.99</v>
       </c>
       <c r="BC6">
-        <v>0</v>
+        <v>5807.29</v>
       </c>
       <c r="BD6">
-        <v>3920.08</v>
+        <v>0.03</v>
       </c>
       <c r="BE6">
-        <v>3920.08</v>
+        <v>0.03</v>
       </c>
       <c r="BF6">
-        <v>3920.08</v>
+        <v>0</v>
       </c>
       <c r="BG6">
         <v>0</v>
@@ -1722,22 +1605,22 @@
         <v>0</v>
       </c>
       <c r="BJ6">
-        <v>0</v>
+        <v>20031.99</v>
       </c>
       <c r="BK6">
-        <v>0</v>
+        <v>20031.99</v>
       </c>
       <c r="BL6">
-        <v>0</v>
+        <v>5807.29</v>
       </c>
       <c r="BM6">
-        <v>3920.08</v>
+        <v>0.03</v>
       </c>
       <c r="BN6">
-        <v>3920.08</v>
+        <v>0.03</v>
       </c>
       <c r="BO6">
-        <v>3920.08</v>
+        <v>0</v>
       </c>
       <c r="BP6">
         <v>0</v>
@@ -1749,10 +1632,10 @@
         <v>0</v>
       </c>
       <c r="BS6">
-        <v>31.15</v>
+        <v>82.03</v>
       </c>
       <c r="BT6">
-        <v>6.24</v>
+        <v>33.41</v>
       </c>
       <c r="BU6">
         <v>0</v>
@@ -1761,16 +1644,16 @@
         <v>0</v>
       </c>
       <c r="BW6">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="BX6">
-        <v>37.39</v>
+        <v>115.46</v>
       </c>
       <c r="BY6">
-        <v>34.49</v>
+        <v>125.78</v>
       </c>
       <c r="BZ6">
-        <v>9.19</v>
+        <v>43.03</v>
       </c>
       <c r="CA6">
         <v>0</v>
@@ -1779,16 +1662,16 @@
         <v>0</v>
       </c>
       <c r="CC6">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="CD6">
-        <v>43.68</v>
+        <v>168.83</v>
       </c>
       <c r="CE6">
-        <v>89.38</v>
+        <v>140.4</v>
       </c>
       <c r="CF6">
-        <v>25.48</v>
+        <v>47.53</v>
       </c>
       <c r="CG6">
         <v>0</v>
@@ -1797,33 +1680,33 @@
         <v>0</v>
       </c>
       <c r="CI6">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="CJ6">
-        <v>114.86</v>
+        <v>187.96</v>
       </c>
       <c r="CK6">
-        <v>1433.0420969023</v>
+        <v>1425.46875</v>
       </c>
       <c r="CL6">
-        <v>1486.4063272368</v>
+        <v>1479.5653584171</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>317096</v>
+        <v>76054</v>
       </c>
       <c r="B7" t="str">
-        <v>506385</v>
+        <v>305892</v>
       </c>
       <c r="C7" t="str">
-        <v>280147</v>
+        <v>73283</v>
       </c>
       <c r="E7" t="str">
-        <v>GONZALEZ BRISIGHELLI VICTORIA GRACIELA</v>
+        <v>MIRANDA LUCIA</v>
       </c>
       <c r="F7" s="1">
-        <v>44991</v>
+        <v>43829</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1844,7 +1727,7 @@
         <v>Argentina</v>
       </c>
       <c r="O7" s="1">
-        <v>45278</v>
+        <v>43840</v>
       </c>
       <c r="P7" t="str">
         <v>1</v>
@@ -1853,31 +1736,34 @@
         <v>1</v>
       </c>
       <c r="R7">
-        <v>5092.37</v>
+        <v>9492.34</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1374.13</v>
       </c>
       <c r="T7">
-        <v>5085.09</v>
+        <v>0</v>
       </c>
       <c r="U7">
         <v>0</v>
       </c>
       <c r="V7">
-        <v>10441.78</v>
+        <v>29527.39</v>
+      </c>
+      <c r="W7">
+        <v>8097.49</v>
       </c>
       <c r="AA7">
-        <v>10441.78</v>
+        <v>29527.39</v>
       </c>
       <c r="AB7">
-        <v>10441.78</v>
+        <v>29527.39</v>
       </c>
       <c r="AC7">
-        <v>10441.78</v>
+        <v>29527.39</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>8097.49</v>
       </c>
       <c r="AE7">
         <v>0</v>
@@ -1886,7 +1772,7 @@
         <v>0</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>672.45</v>
       </c>
       <c r="AH7">
         <v>0</v>
@@ -1907,16 +1793,16 @@
         <v>0</v>
       </c>
       <c r="AR7">
-        <v>10441.78</v>
+        <v>29527.39</v>
       </c>
       <c r="AS7">
-        <v>10441.78</v>
+        <v>29527.39</v>
       </c>
       <c r="AT7">
-        <v>10441.78</v>
+        <v>29527.39</v>
       </c>
       <c r="AU7">
-        <v>0</v>
+        <v>8097.49</v>
       </c>
       <c r="AV7">
         <v>0</v>
@@ -1934,16 +1820,16 @@
         <v>0</v>
       </c>
       <c r="BA7">
-        <v>10441.78</v>
+        <v>29527.39</v>
       </c>
       <c r="BB7">
-        <v>10441.78</v>
+        <v>29527.39</v>
       </c>
       <c r="BC7">
-        <v>10441.78</v>
+        <v>29527.39</v>
       </c>
       <c r="BD7">
-        <v>0</v>
+        <v>8097.49</v>
       </c>
       <c r="BE7">
         <v>0</v>
@@ -1961,16 +1847,16 @@
         <v>0</v>
       </c>
       <c r="BJ7">
-        <v>10441.78</v>
+        <v>29527.39</v>
       </c>
       <c r="BK7">
-        <v>10441.78</v>
+        <v>29527.39</v>
       </c>
       <c r="BL7">
-        <v>10441.78</v>
+        <v>29527.39</v>
       </c>
       <c r="BM7">
-        <v>0</v>
+        <v>8097.49</v>
       </c>
       <c r="BN7">
         <v>0</v>
@@ -1988,10 +1874,10 @@
         <v>0</v>
       </c>
       <c r="BS7">
-        <v>0</v>
+        <v>29.53</v>
       </c>
       <c r="BT7">
-        <v>8.5</v>
+        <v>8.55</v>
       </c>
       <c r="BU7">
         <v>0</v>
@@ -2003,13 +1889,13 @@
         <v>0</v>
       </c>
       <c r="BX7">
-        <v>8.5</v>
+        <v>38.08</v>
       </c>
       <c r="BY7">
-        <v>0</v>
+        <v>41.33</v>
       </c>
       <c r="BZ7">
-        <v>8.5</v>
+        <v>12.38</v>
       </c>
       <c r="CA7">
         <v>0</v>
@@ -2021,13 +1907,13 @@
         <v>0</v>
       </c>
       <c r="CD7">
-        <v>8.5</v>
+        <v>53.71</v>
       </c>
       <c r="CE7">
-        <v>0</v>
+        <v>96.23</v>
       </c>
       <c r="CF7">
-        <v>8.5</v>
+        <v>28.06</v>
       </c>
       <c r="CG7">
         <v>0</v>
@@ -2039,30 +1925,30 @@
         <v>0</v>
       </c>
       <c r="CJ7">
-        <v>8.5</v>
+        <v>124.29</v>
       </c>
       <c r="CK7">
-        <v>1433.0420969023</v>
+        <v>1425.46875</v>
       </c>
       <c r="CL7">
-        <v>1486.4063272368</v>
+        <v>1479.5653584171</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>469465</v>
+        <v>174303</v>
       </c>
       <c r="B8" t="str">
-        <v>643364</v>
+        <v>369323</v>
       </c>
       <c r="C8" t="str">
-        <v>374621</v>
+        <v>140935</v>
       </c>
       <c r="E8" t="str">
-        <v>PACIOS NOELIA BELEN</v>
+        <v>XANTHOPOULOS IGNACIO ANDRES</v>
       </c>
       <c r="F8" s="1">
-        <v>45162</v>
+        <v>44214</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -2077,13 +1963,13 @@
         <v>IFA</v>
       </c>
       <c r="K8" t="str">
-        <v>IFA 4</v>
+        <v>RETAIL 2</v>
       </c>
       <c r="N8" t="str">
         <v>Argentina</v>
       </c>
       <c r="O8" s="1">
-        <v>46062</v>
+        <v>44215</v>
       </c>
       <c r="P8" t="str">
         <v>1</v>
@@ -2092,22 +1978,28 @@
         <v>1</v>
       </c>
       <c r="R8">
-        <v>5075.04</v>
+        <v>36282.14</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1964.28</v>
       </c>
       <c r="T8">
-        <v>5075.04</v>
+        <v>34316.56</v>
       </c>
       <c r="U8">
         <v>0</v>
       </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="Y8">
+        <v>1.32</v>
+      </c>
       <c r="BS8">
         <v>0</v>
       </c>
       <c r="BT8">
-        <v>5.45</v>
+        <v>4.04</v>
       </c>
       <c r="BU8">
         <v>0</v>
@@ -2119,13 +2011,13 @@
         <v>0</v>
       </c>
       <c r="BX8">
-        <v>5.45</v>
+        <v>4.04</v>
       </c>
       <c r="BY8">
-        <v>0</v>
+        <v>10.17</v>
       </c>
       <c r="BZ8">
-        <v>5.45</v>
+        <v>4.04</v>
       </c>
       <c r="CA8">
         <v>0</v>
@@ -2137,13 +2029,13 @@
         <v>0</v>
       </c>
       <c r="CD8">
-        <v>5.45</v>
+        <v>14.21</v>
       </c>
       <c r="CE8">
-        <v>0</v>
+        <v>10.17</v>
       </c>
       <c r="CF8">
-        <v>5.45</v>
+        <v>4.04</v>
       </c>
       <c r="CG8">
         <v>0</v>
@@ -2155,30 +2047,30 @@
         <v>0</v>
       </c>
       <c r="CJ8">
-        <v>5.45</v>
+        <v>14.21</v>
       </c>
       <c r="CK8">
-        <v>1433.0420969023</v>
+        <v>1425.46875</v>
       </c>
       <c r="CL8">
-        <v>1486.4063272368</v>
+        <v>1479.5653584171</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>487375</v>
+        <v>214756</v>
       </c>
       <c r="B9" t="str">
-        <v>660056</v>
+        <v>407636</v>
       </c>
       <c r="C9" t="str">
-        <v>386081</v>
+        <v>180059</v>
       </c>
       <c r="E9" t="str">
-        <v>SANTILLAN INES</v>
+        <v>PUEYRREDON FERNANDO AGUSTIN</v>
       </c>
       <c r="F9" s="1">
-        <v>45174</v>
+        <v>44448</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -2193,184 +2085,40 @@
         <v>IFA</v>
       </c>
       <c r="K9" t="str">
-        <v>IFA 3</v>
+        <v>IFA 4</v>
       </c>
       <c r="N9" t="str">
         <v>Argentina</v>
       </c>
       <c r="O9" s="1">
-        <v>45175</v>
+        <v>44476</v>
       </c>
       <c r="P9" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q9">
         <v>1</v>
       </c>
       <c r="R9">
-        <v>3807.65</v>
+        <v>4.36</v>
       </c>
       <c r="S9">
-        <v>201.95</v>
+        <v>0</v>
       </c>
       <c r="T9">
-        <v>866.42</v>
+        <v>0</v>
       </c>
       <c r="U9">
         <v>0</v>
       </c>
-      <c r="V9">
-        <v>54103.73</v>
-      </c>
-      <c r="W9">
-        <v>2701.08</v>
-      </c>
       <c r="Y9">
-        <v>0.44</v>
-      </c>
-      <c r="AA9">
-        <v>54103.73</v>
-      </c>
-      <c r="AB9">
-        <v>54103.73</v>
-      </c>
-      <c r="AC9">
-        <v>0</v>
-      </c>
-      <c r="AD9">
-        <v>2701.08</v>
-      </c>
-      <c r="AE9">
-        <v>2701.08</v>
-      </c>
-      <c r="AF9">
-        <v>2100.32</v>
-      </c>
-      <c r="AG9">
-        <v>5126.24</v>
-      </c>
-      <c r="AH9">
-        <v>2100.32</v>
-      </c>
-      <c r="AI9">
-        <v>0</v>
-      </c>
-      <c r="AJ9">
-        <v>0</v>
-      </c>
-      <c r="AK9">
-        <v>0</v>
-      </c>
-      <c r="AL9">
-        <v>0</v>
-      </c>
-      <c r="AM9">
-        <v>0</v>
-      </c>
-      <c r="AR9">
-        <v>54103.73</v>
-      </c>
-      <c r="AS9">
-        <v>54103.73</v>
-      </c>
-      <c r="AT9">
-        <v>0</v>
-      </c>
-      <c r="AU9">
-        <v>2701.08</v>
-      </c>
-      <c r="AV9">
-        <v>2701.08</v>
-      </c>
-      <c r="AW9">
-        <v>2100.32</v>
-      </c>
-      <c r="AX9">
-        <v>0</v>
-      </c>
-      <c r="AY9">
-        <v>0</v>
-      </c>
-      <c r="AZ9">
-        <v>0</v>
-      </c>
-      <c r="BA9">
-        <v>54103.73</v>
-      </c>
-      <c r="BB9">
-        <v>54103.73</v>
-      </c>
-      <c r="BC9">
-        <v>0</v>
-      </c>
-      <c r="BD9">
-        <v>2701.08</v>
-      </c>
-      <c r="BE9">
-        <v>2701.08</v>
-      </c>
-      <c r="BF9">
-        <v>2100.32</v>
-      </c>
-      <c r="BG9">
-        <v>0</v>
-      </c>
-      <c r="BH9">
-        <v>0</v>
-      </c>
-      <c r="BI9">
-        <v>0</v>
-      </c>
-      <c r="BJ9">
-        <v>54103.73</v>
-      </c>
-      <c r="BK9">
-        <v>54103.73</v>
-      </c>
-      <c r="BL9">
-        <v>0</v>
-      </c>
-      <c r="BM9">
-        <v>2701.08</v>
-      </c>
-      <c r="BN9">
-        <v>2701.08</v>
-      </c>
-      <c r="BO9">
-        <v>2100.32</v>
-      </c>
-      <c r="BP9">
-        <v>0</v>
-      </c>
-      <c r="BQ9">
-        <v>0</v>
-      </c>
-      <c r="BR9">
-        <v>0</v>
-      </c>
-      <c r="BS9">
-        <v>57.25</v>
-      </c>
-      <c r="BT9">
-        <v>4.8</v>
-      </c>
-      <c r="BU9">
-        <v>0</v>
-      </c>
-      <c r="BV9">
-        <v>0</v>
-      </c>
-      <c r="BW9">
-        <v>0</v>
-      </c>
-      <c r="BX9">
-        <v>62.05</v>
+        <v>4.36</v>
       </c>
       <c r="BY9">
-        <v>106.61</v>
+        <v>1.89</v>
       </c>
       <c r="BZ9">
-        <v>11.68</v>
+        <v>0</v>
       </c>
       <c r="CA9">
         <v>0</v>
@@ -2382,13 +2130,13 @@
         <v>0</v>
       </c>
       <c r="CD9">
-        <v>118.29</v>
+        <v>1.89</v>
       </c>
       <c r="CE9">
-        <v>202.85</v>
+        <v>4.92</v>
       </c>
       <c r="CF9">
-        <v>12.39</v>
+        <v>0</v>
       </c>
       <c r="CG9">
         <v>0</v>
@@ -2397,33 +2145,33 @@
         <v>0</v>
       </c>
       <c r="CI9">
-        <v>0.52</v>
+        <v>0.08</v>
       </c>
       <c r="CJ9">
-        <v>215.76</v>
+        <v>5</v>
       </c>
       <c r="CK9">
-        <v>1433.0420969023</v>
+        <v>1425.46875</v>
       </c>
       <c r="CL9">
-        <v>1486.4063272368</v>
+        <v>1479.5653584171</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>1047523</v>
+        <v>298596</v>
       </c>
       <c r="B10" t="str">
-        <v>1183060</v>
+        <v>488720</v>
       </c>
       <c r="C10" t="str">
-        <v>668507</v>
+        <v>262340</v>
       </c>
       <c r="E10" t="str">
-        <v>VIDELA MARIANA</v>
+        <v>SACKMANN INES</v>
       </c>
       <c r="F10" s="1">
-        <v>45602</v>
+        <v>44942</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -2444,52 +2192,43 @@
         <v>Argentina</v>
       </c>
       <c r="O10" s="1">
-        <v>45672</v>
+        <v>44946</v>
       </c>
       <c r="P10" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R10">
-        <v>21264.69</v>
+        <v>1.76</v>
       </c>
       <c r="S10">
-        <v>7168.42</v>
+        <v>0</v>
       </c>
       <c r="T10">
-        <v>14027.34</v>
+        <v>0</v>
       </c>
       <c r="U10">
         <v>0</v>
       </c>
       <c r="V10">
-        <v>6534.83</v>
-      </c>
-      <c r="W10">
-        <v>33.49</v>
-      </c>
-      <c r="X10">
-        <v>18.22</v>
-      </c>
-      <c r="Y10">
-        <v>12.65</v>
+        <v>2510.08</v>
       </c>
       <c r="AA10">
-        <v>6534.83</v>
+        <v>2510.08</v>
       </c>
       <c r="AB10">
-        <v>6534.83</v>
+        <v>2510.08</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>2510.08</v>
       </c>
       <c r="AD10">
-        <v>33.49</v>
+        <v>0</v>
       </c>
       <c r="AE10">
-        <v>33.49</v>
+        <v>0</v>
       </c>
       <c r="AF10">
         <v>0</v>
@@ -2501,177 +2240,123 @@
         <v>0</v>
       </c>
       <c r="AI10">
-        <v>18.22</v>
+        <v>0</v>
       </c>
       <c r="AJ10">
-        <v>18.22</v>
+        <v>0</v>
       </c>
       <c r="AK10">
         <v>0</v>
       </c>
       <c r="AL10">
-        <v>1099.43</v>
+        <v>0</v>
       </c>
       <c r="AM10">
         <v>0</v>
       </c>
       <c r="AR10">
-        <v>6534.83</v>
+        <v>2510.08</v>
       </c>
       <c r="AS10">
-        <v>6534.83</v>
+        <v>2510.08</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>2510.08</v>
       </c>
       <c r="AU10">
-        <v>33.49</v>
+        <v>0</v>
       </c>
       <c r="AV10">
-        <v>33.49</v>
+        <v>0</v>
       </c>
       <c r="AW10">
         <v>0</v>
       </c>
       <c r="AX10">
-        <v>18.22</v>
+        <v>0</v>
       </c>
       <c r="AY10">
-        <v>18.22</v>
+        <v>0</v>
       </c>
       <c r="AZ10">
         <v>0</v>
       </c>
       <c r="BA10">
-        <v>6534.83</v>
+        <v>2510.08</v>
       </c>
       <c r="BB10">
-        <v>6534.83</v>
+        <v>2510.08</v>
       </c>
       <c r="BC10">
-        <v>0</v>
+        <v>2510.08</v>
       </c>
       <c r="BD10">
-        <v>33.49</v>
+        <v>0</v>
       </c>
       <c r="BE10">
-        <v>33.49</v>
+        <v>0</v>
       </c>
       <c r="BF10">
         <v>0</v>
       </c>
       <c r="BG10">
-        <v>18.22</v>
+        <v>0</v>
       </c>
       <c r="BH10">
-        <v>18.22</v>
+        <v>0</v>
       </c>
       <c r="BI10">
         <v>0</v>
       </c>
       <c r="BJ10">
-        <v>6534.83</v>
+        <v>2510.08</v>
       </c>
       <c r="BK10">
-        <v>6534.83</v>
+        <v>2510.08</v>
       </c>
       <c r="BL10">
-        <v>0</v>
+        <v>2510.08</v>
       </c>
       <c r="BM10">
-        <v>33.49</v>
+        <v>0</v>
       </c>
       <c r="BN10">
-        <v>33.49</v>
+        <v>0</v>
       </c>
       <c r="BO10">
         <v>0</v>
       </c>
       <c r="BP10">
-        <v>18.22</v>
+        <v>0</v>
       </c>
       <c r="BQ10">
-        <v>18.22</v>
+        <v>0</v>
       </c>
       <c r="BR10">
         <v>0</v>
       </c>
-      <c r="BS10">
-        <v>3.52</v>
-      </c>
-      <c r="BT10">
-        <v>30.17</v>
-      </c>
-      <c r="BU10">
-        <v>0</v>
-      </c>
-      <c r="BV10">
-        <v>0</v>
-      </c>
-      <c r="BW10">
-        <v>0</v>
-      </c>
-      <c r="BX10">
-        <v>33.69</v>
-      </c>
-      <c r="BY10">
-        <v>20.79</v>
-      </c>
-      <c r="BZ10">
-        <v>46.14</v>
-      </c>
-      <c r="CA10">
-        <v>0</v>
-      </c>
-      <c r="CB10">
-        <v>0</v>
-      </c>
-      <c r="CC10">
-        <v>0.02</v>
-      </c>
-      <c r="CD10">
-        <v>66.95</v>
-      </c>
-      <c r="CE10">
-        <v>34.46</v>
-      </c>
-      <c r="CF10">
-        <v>76.65</v>
-      </c>
-      <c r="CG10">
-        <v>0</v>
-      </c>
-      <c r="CH10">
-        <v>0</v>
-      </c>
-      <c r="CI10">
-        <v>0.06</v>
-      </c>
-      <c r="CJ10">
-        <v>111.17</v>
-      </c>
       <c r="CK10">
-        <v>1433.0420969023</v>
+        <v>1425.46875</v>
       </c>
       <c r="CL10">
-        <v>1486.4063272368</v>
+        <v>1479.5653584171</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>1239877</v>
+        <v>317096</v>
       </c>
       <c r="B11" t="str">
-        <v>1365529</v>
+        <v>506385</v>
       </c>
       <c r="C11" t="str">
-        <v>737353</v>
+        <v>280147</v>
       </c>
       <c r="E11" t="str">
-        <v>COSENZA MATIAS</v>
+        <v>GONZALEZ BRISIGHELLI VICTORIA GRACIELA</v>
       </c>
       <c r="F11" s="1">
-        <v>45763</v>
+        <v>44991</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -2686,13 +2371,13 @@
         <v>IFA</v>
       </c>
       <c r="K11" t="str">
-        <v>IFA 3</v>
+        <v>IFA 4</v>
       </c>
       <c r="N11" t="str">
         <v>Argentina</v>
       </c>
       <c r="O11" s="1">
-        <v>45773</v>
+        <v>45278</v>
       </c>
       <c r="P11" t="str">
         <v>1</v>
@@ -2701,46 +2386,43 @@
         <v>1</v>
       </c>
       <c r="R11">
-        <v>10594.06</v>
+        <v>5100.75</v>
       </c>
       <c r="S11">
-        <v>409.21</v>
+        <v>0</v>
       </c>
       <c r="T11">
-        <v>177.9</v>
+        <v>5093.43</v>
       </c>
       <c r="U11">
         <v>0</v>
       </c>
       <c r="V11">
-        <v>430.2</v>
-      </c>
-      <c r="W11">
-        <v>10006.65</v>
+        <v>10441.78</v>
       </c>
       <c r="AA11">
-        <v>430.2</v>
+        <v>10441.78</v>
       </c>
       <c r="AB11">
-        <v>430.2</v>
+        <v>10441.78</v>
       </c>
       <c r="AC11">
-        <v>430.2</v>
+        <v>10441.78</v>
       </c>
       <c r="AD11">
-        <v>10006.65</v>
+        <v>0</v>
       </c>
       <c r="AE11">
-        <v>6.65</v>
+        <v>0</v>
       </c>
       <c r="AF11">
-        <v>0.86</v>
+        <v>0</v>
       </c>
       <c r="AG11">
-        <v>399.74</v>
+        <v>0</v>
       </c>
       <c r="AH11">
-        <v>0.86</v>
+        <v>0</v>
       </c>
       <c r="AI11">
         <v>0</v>
@@ -2758,22 +2440,22 @@
         <v>0</v>
       </c>
       <c r="AR11">
-        <v>430.2</v>
+        <v>10441.78</v>
       </c>
       <c r="AS11">
-        <v>430.2</v>
+        <v>10441.78</v>
       </c>
       <c r="AT11">
-        <v>430.2</v>
+        <v>10441.78</v>
       </c>
       <c r="AU11">
-        <v>10006.65</v>
+        <v>0</v>
       </c>
       <c r="AV11">
-        <v>6.65</v>
+        <v>0</v>
       </c>
       <c r="AW11">
-        <v>0.86</v>
+        <v>0</v>
       </c>
       <c r="AX11">
         <v>0</v>
@@ -2785,22 +2467,22 @@
         <v>0</v>
       </c>
       <c r="BA11">
-        <v>430.2</v>
+        <v>10441.78</v>
       </c>
       <c r="BB11">
-        <v>430.2</v>
+        <v>10441.78</v>
       </c>
       <c r="BC11">
-        <v>430.2</v>
+        <v>10441.78</v>
       </c>
       <c r="BD11">
-        <v>10006.65</v>
+        <v>0</v>
       </c>
       <c r="BE11">
-        <v>6.65</v>
+        <v>0</v>
       </c>
       <c r="BF11">
-        <v>0.86</v>
+        <v>0</v>
       </c>
       <c r="BG11">
         <v>0</v>
@@ -2812,22 +2494,22 @@
         <v>0</v>
       </c>
       <c r="BJ11">
-        <v>430.2</v>
+        <v>10441.78</v>
       </c>
       <c r="BK11">
-        <v>430.2</v>
+        <v>10441.78</v>
       </c>
       <c r="BL11">
-        <v>430.2</v>
+        <v>10441.78</v>
       </c>
       <c r="BM11">
-        <v>10006.65</v>
+        <v>0</v>
       </c>
       <c r="BN11">
-        <v>6.65</v>
+        <v>0</v>
       </c>
       <c r="BO11">
-        <v>0.86</v>
+        <v>0</v>
       </c>
       <c r="BP11">
         <v>0</v>
@@ -2839,10 +2521,10 @@
         <v>0</v>
       </c>
       <c r="BS11">
-        <v>33.63</v>
+        <v>0</v>
       </c>
       <c r="BT11">
-        <v>0.53</v>
+        <v>10.03</v>
       </c>
       <c r="BU11">
         <v>0</v>
@@ -2854,13 +2536,13 @@
         <v>0</v>
       </c>
       <c r="BX11">
-        <v>34.16</v>
+        <v>10.03</v>
       </c>
       <c r="BY11">
-        <v>33.63</v>
+        <v>0</v>
       </c>
       <c r="BZ11">
-        <v>1</v>
+        <v>11.38</v>
       </c>
       <c r="CA11">
         <v>0</v>
@@ -2872,13 +2554,13 @@
         <v>0</v>
       </c>
       <c r="CD11">
-        <v>34.63</v>
+        <v>11.38</v>
       </c>
       <c r="CE11">
-        <v>33.63</v>
+        <v>0</v>
       </c>
       <c r="CF11">
-        <v>1.86</v>
+        <v>11.38</v>
       </c>
       <c r="CG11">
         <v>0</v>
@@ -2890,30 +2572,30 @@
         <v>0</v>
       </c>
       <c r="CJ11">
-        <v>35.49</v>
+        <v>11.38</v>
       </c>
       <c r="CK11">
-        <v>1433.0420969023</v>
+        <v>1425.46875</v>
       </c>
       <c r="CL11">
-        <v>1486.4063272368</v>
+        <v>1479.5653584171</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>1243660</v>
+        <v>469465</v>
       </c>
       <c r="B12" t="str">
-        <v>1368615</v>
+        <v>643364</v>
       </c>
       <c r="C12" t="str">
-        <v>738111</v>
+        <v>374621</v>
       </c>
       <c r="E12" t="str">
-        <v>SERJAI HERNAN LEONARDO</v>
+        <v>PACIOS NOELIA BELEN</v>
       </c>
       <c r="F12" s="1">
-        <v>45768</v>
+        <v>45162</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -2933,31 +2615,103 @@
       <c r="N12" t="str">
         <v>Argentina</v>
       </c>
+      <c r="O12" s="1">
+        <v>46062</v>
+      </c>
       <c r="P12" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>5087.95</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>5087.95</v>
+      </c>
+      <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="BS12">
+        <v>0</v>
+      </c>
+      <c r="BT12">
+        <v>6.3</v>
+      </c>
+      <c r="BU12">
+        <v>0</v>
+      </c>
+      <c r="BV12">
+        <v>0</v>
+      </c>
+      <c r="BW12">
+        <v>0</v>
+      </c>
+      <c r="BX12">
+        <v>6.3</v>
+      </c>
+      <c r="BY12">
+        <v>0</v>
+      </c>
+      <c r="BZ12">
+        <v>7.27</v>
+      </c>
+      <c r="CA12">
+        <v>0</v>
+      </c>
+      <c r="CB12">
+        <v>0</v>
+      </c>
+      <c r="CC12">
+        <v>0</v>
+      </c>
+      <c r="CD12">
+        <v>7.27</v>
+      </c>
+      <c r="CE12">
+        <v>0</v>
+      </c>
+      <c r="CF12">
+        <v>7.27</v>
+      </c>
+      <c r="CG12">
+        <v>0</v>
+      </c>
+      <c r="CH12">
+        <v>0</v>
+      </c>
+      <c r="CI12">
+        <v>0</v>
+      </c>
+      <c r="CJ12">
+        <v>7.27</v>
+      </c>
+      <c r="CK12">
+        <v>1425.46875</v>
+      </c>
+      <c r="CL12">
+        <v>1479.5653584171</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>1251226</v>
+        <v>487375</v>
       </c>
       <c r="B13" t="str">
-        <v>1375361</v>
+        <v>660056</v>
       </c>
       <c r="C13" t="str">
-        <v>740033</v>
+        <v>386081</v>
       </c>
       <c r="E13" t="str">
-        <v>GONZALEZ JUAN EMILIO</v>
+        <v>SANTILLAN INES</v>
       </c>
       <c r="F13" s="1">
-        <v>45770</v>
+        <v>45174</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -2978,7 +2732,7 @@
         <v>Argentina</v>
       </c>
       <c r="O13" s="1">
-        <v>45776</v>
+        <v>45175</v>
       </c>
       <c r="P13" t="str">
         <v>1</v>
@@ -2987,43 +2741,46 @@
         <v>1</v>
       </c>
       <c r="R13">
-        <v>7597.93</v>
+        <v>5990.81</v>
       </c>
       <c r="S13">
-        <v>5942.11</v>
+        <v>600.29</v>
       </c>
       <c r="T13">
-        <v>1623.11</v>
+        <v>4883.51</v>
       </c>
       <c r="U13">
         <v>0</v>
       </c>
       <c r="V13">
-        <v>5982.97</v>
+        <v>-853.92</v>
+      </c>
+      <c r="W13">
+        <v>507.16</v>
       </c>
       <c r="Y13">
-        <v>28.55</v>
+        <v>0.44</v>
       </c>
       <c r="AA13">
-        <v>5982.97</v>
+        <v>-853.92</v>
       </c>
       <c r="AB13">
-        <v>5982.97</v>
+        <v>-853.92</v>
       </c>
       <c r="AC13">
         <v>0</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>507.16</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>507.16</v>
       </c>
       <c r="AF13">
         <v>0</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>4926.24</v>
       </c>
       <c r="AH13">
         <v>0</v>
@@ -3044,19 +2801,19 @@
         <v>0</v>
       </c>
       <c r="AR13">
-        <v>5982.97</v>
+        <v>-853.92</v>
       </c>
       <c r="AS13">
-        <v>5982.97</v>
+        <v>-853.92</v>
       </c>
       <c r="AT13">
         <v>0</v>
       </c>
       <c r="AU13">
-        <v>0</v>
+        <v>507.16</v>
       </c>
       <c r="AV13">
-        <v>0</v>
+        <v>507.16</v>
       </c>
       <c r="AW13">
         <v>0</v>
@@ -3071,19 +2828,19 @@
         <v>0</v>
       </c>
       <c r="BA13">
-        <v>5982.97</v>
+        <v>-853.92</v>
       </c>
       <c r="BB13">
-        <v>5982.97</v>
+        <v>-853.92</v>
       </c>
       <c r="BC13">
         <v>0</v>
       </c>
       <c r="BD13">
-        <v>0</v>
+        <v>507.16</v>
       </c>
       <c r="BE13">
-        <v>0</v>
+        <v>507.16</v>
       </c>
       <c r="BF13">
         <v>0</v>
@@ -3098,19 +2855,19 @@
         <v>0</v>
       </c>
       <c r="BJ13">
-        <v>5982.97</v>
+        <v>-853.92</v>
       </c>
       <c r="BK13">
-        <v>5982.97</v>
+        <v>-853.92</v>
       </c>
       <c r="BL13">
         <v>0</v>
       </c>
       <c r="BM13">
-        <v>0</v>
+        <v>507.16</v>
       </c>
       <c r="BN13">
-        <v>0</v>
+        <v>507.16</v>
       </c>
       <c r="BO13">
         <v>0</v>
@@ -3125,10 +2882,10 @@
         <v>0</v>
       </c>
       <c r="BS13">
-        <v>14.83</v>
+        <v>56.05</v>
       </c>
       <c r="BT13">
-        <v>7.7</v>
+        <v>5.13</v>
       </c>
       <c r="BU13">
         <v>0</v>
@@ -3137,16 +2894,16 @@
         <v>0</v>
       </c>
       <c r="BW13">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="BX13">
-        <v>22.53</v>
+        <v>61.2</v>
       </c>
       <c r="BY13">
-        <v>15.58</v>
+        <v>93.96</v>
       </c>
       <c r="BZ13">
-        <v>10.86</v>
+        <v>13.05</v>
       </c>
       <c r="CA13">
         <v>0</v>
@@ -3155,16 +2912,16 @@
         <v>0</v>
       </c>
       <c r="CC13">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="CD13">
-        <v>26.49</v>
+        <v>107.03</v>
       </c>
       <c r="CE13">
-        <v>39.72</v>
+        <v>206.89</v>
       </c>
       <c r="CF13">
-        <v>16.74</v>
+        <v>14.22</v>
       </c>
       <c r="CG13">
         <v>0</v>
@@ -3173,33 +2930,33 @@
         <v>0</v>
       </c>
       <c r="CI13">
-        <v>0.16</v>
+        <v>0.45</v>
       </c>
       <c r="CJ13">
-        <v>56.62</v>
+        <v>221.56</v>
       </c>
       <c r="CK13">
-        <v>1433.0420969023</v>
+        <v>1425.46875</v>
       </c>
       <c r="CL13">
-        <v>1486.4063272368</v>
+        <v>1479.5653584171</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>1263431</v>
+        <v>1047523</v>
       </c>
       <c r="B14" t="str">
-        <v>1385990</v>
+        <v>1183060</v>
       </c>
       <c r="C14" t="str">
-        <v>742621</v>
+        <v>668507</v>
       </c>
       <c r="E14" t="str">
-        <v>QUIRELLI MAXIMO</v>
+        <v>VIDELA MARIANA</v>
       </c>
       <c r="F14" s="1">
-        <v>45777</v>
+        <v>45602</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -3214,13 +2971,13 @@
         <v>IFA</v>
       </c>
       <c r="K14" t="str">
-        <v>IFA 2</v>
+        <v>IFA 4</v>
       </c>
       <c r="N14" t="str">
         <v>Argentina</v>
       </c>
       <c r="O14" s="1">
-        <v>45779</v>
+        <v>45672</v>
       </c>
       <c r="P14" t="str">
         <v>1</v>
@@ -3229,148 +2986,154 @@
         <v>1</v>
       </c>
       <c r="R14">
-        <v>5059.5</v>
+        <v>21492.05</v>
       </c>
       <c r="S14">
-        <v>2036.05</v>
+        <v>7337.29</v>
       </c>
       <c r="T14">
-        <v>3007.15</v>
+        <v>14081.68</v>
       </c>
       <c r="U14">
         <v>0</v>
       </c>
       <c r="V14">
-        <v>-4692.62</v>
+        <v>9789.74</v>
       </c>
       <c r="W14">
-        <v>19.56</v>
+        <v>33.49</v>
+      </c>
+      <c r="X14">
+        <v>18.22</v>
+      </c>
+      <c r="Y14">
+        <v>14.48</v>
       </c>
       <c r="AA14">
-        <v>-4692.62</v>
+        <v>9789.74</v>
       </c>
       <c r="AB14">
-        <v>-4692.62</v>
+        <v>9789.74</v>
       </c>
       <c r="AC14">
         <v>0</v>
       </c>
       <c r="AD14">
-        <v>19.56</v>
+        <v>33.49</v>
       </c>
       <c r="AE14">
-        <v>19.56</v>
+        <v>33.49</v>
       </c>
       <c r="AF14">
-        <v>19.56</v>
+        <v>0</v>
       </c>
       <c r="AG14">
         <v>0</v>
       </c>
       <c r="AH14">
-        <v>19.56</v>
+        <v>0</v>
       </c>
       <c r="AI14">
-        <v>0</v>
+        <v>18.22</v>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>18.22</v>
       </c>
       <c r="AK14">
         <v>0</v>
       </c>
       <c r="AL14">
-        <v>0</v>
+        <v>1099.43</v>
       </c>
       <c r="AM14">
         <v>0</v>
       </c>
       <c r="AR14">
-        <v>-4692.62</v>
+        <v>9789.74</v>
       </c>
       <c r="AS14">
-        <v>-4692.62</v>
+        <v>9789.74</v>
       </c>
       <c r="AT14">
         <v>0</v>
       </c>
       <c r="AU14">
-        <v>19.56</v>
+        <v>33.49</v>
       </c>
       <c r="AV14">
-        <v>19.56</v>
+        <v>33.49</v>
       </c>
       <c r="AW14">
-        <v>19.56</v>
+        <v>0</v>
       </c>
       <c r="AX14">
-        <v>0</v>
+        <v>18.22</v>
       </c>
       <c r="AY14">
-        <v>0</v>
+        <v>18.22</v>
       </c>
       <c r="AZ14">
         <v>0</v>
       </c>
       <c r="BA14">
-        <v>-4692.62</v>
+        <v>9789.74</v>
       </c>
       <c r="BB14">
-        <v>-4692.62</v>
+        <v>9789.74</v>
       </c>
       <c r="BC14">
         <v>0</v>
       </c>
       <c r="BD14">
-        <v>19.56</v>
+        <v>33.49</v>
       </c>
       <c r="BE14">
-        <v>19.56</v>
+        <v>33.49</v>
       </c>
       <c r="BF14">
-        <v>19.56</v>
+        <v>0</v>
       </c>
       <c r="BG14">
-        <v>0</v>
+        <v>18.22</v>
       </c>
       <c r="BH14">
-        <v>0</v>
+        <v>18.22</v>
       </c>
       <c r="BI14">
         <v>0</v>
       </c>
       <c r="BJ14">
-        <v>-4692.62</v>
+        <v>9789.74</v>
       </c>
       <c r="BK14">
-        <v>-4692.62</v>
+        <v>9789.74</v>
       </c>
       <c r="BL14">
         <v>0</v>
       </c>
       <c r="BM14">
-        <v>19.56</v>
+        <v>33.49</v>
       </c>
       <c r="BN14">
-        <v>19.56</v>
+        <v>33.49</v>
       </c>
       <c r="BO14">
-        <v>19.56</v>
+        <v>0</v>
       </c>
       <c r="BP14">
-        <v>0</v>
+        <v>18.22</v>
       </c>
       <c r="BQ14">
-        <v>0</v>
+        <v>18.22</v>
       </c>
       <c r="BR14">
         <v>0</v>
       </c>
       <c r="BS14">
-        <v>14.74</v>
+        <v>3.52</v>
       </c>
       <c r="BT14">
-        <v>1.56</v>
+        <v>31.65</v>
       </c>
       <c r="BU14">
         <v>0</v>
@@ -3379,16 +3142,16 @@
         <v>0</v>
       </c>
       <c r="BW14">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="BX14">
-        <v>16.3</v>
+        <v>35.18</v>
       </c>
       <c r="BY14">
-        <v>14.74</v>
+        <v>14.72</v>
       </c>
       <c r="BZ14">
-        <v>1.56</v>
+        <v>51.05</v>
       </c>
       <c r="CA14">
         <v>0</v>
@@ -3397,16 +3160,16 @@
         <v>0</v>
       </c>
       <c r="CC14">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="CD14">
-        <v>16.3</v>
+        <v>65.79</v>
       </c>
       <c r="CE14">
-        <v>14.74</v>
+        <v>30.12</v>
       </c>
       <c r="CF14">
-        <v>18.61</v>
+        <v>82.92</v>
       </c>
       <c r="CG14">
         <v>0</v>
@@ -3415,33 +3178,33 @@
         <v>0</v>
       </c>
       <c r="CI14">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="CJ14">
-        <v>33.35</v>
+        <v>113.09</v>
       </c>
       <c r="CK14">
-        <v>1433.0420969023</v>
+        <v>1425.46875</v>
       </c>
       <c r="CL14">
-        <v>1486.4063272368</v>
+        <v>1479.5653584171</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>1273461</v>
+        <v>1239877</v>
       </c>
       <c r="B15" t="str">
-        <v>1395432</v>
+        <v>1365529</v>
       </c>
       <c r="C15" t="str">
-        <v>746143</v>
+        <v>737353</v>
       </c>
       <c r="E15" t="str">
-        <v>LOPEZ FONTAN ROCIO</v>
+        <v>COSENZA MATIAS</v>
       </c>
       <c r="F15" s="1">
-        <v>45789</v>
+        <v>45763</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -3462,7 +3225,7 @@
         <v>Argentina</v>
       </c>
       <c r="O15" s="1">
-        <v>45848</v>
+        <v>45773</v>
       </c>
       <c r="P15" t="str">
         <v>1</v>
@@ -3471,46 +3234,46 @@
         <v>1</v>
       </c>
       <c r="R15">
-        <v>7107.63</v>
+        <v>65656.77</v>
       </c>
       <c r="S15">
-        <v>3881.69</v>
+        <v>408.56</v>
       </c>
       <c r="T15">
-        <v>3217.4</v>
+        <v>50231.67</v>
       </c>
       <c r="U15">
         <v>0</v>
       </c>
       <c r="V15">
-        <v>433.3</v>
-      </c>
-      <c r="Y15">
-        <v>8.25</v>
+        <v>454.01</v>
+      </c>
+      <c r="W15">
+        <v>15016.22</v>
       </c>
       <c r="AA15">
-        <v>433.3</v>
+        <v>454.01</v>
       </c>
       <c r="AB15">
-        <v>433.3</v>
+        <v>454.01</v>
       </c>
       <c r="AC15">
         <v>0</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>15016.22</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>15016.22</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>5009.04</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>399.74</v>
       </c>
       <c r="AH15">
-        <v>0</v>
+        <v>5009.04</v>
       </c>
       <c r="AI15">
         <v>0</v>
@@ -3528,22 +3291,22 @@
         <v>0</v>
       </c>
       <c r="AR15">
-        <v>433.3</v>
+        <v>454.01</v>
       </c>
       <c r="AS15">
-        <v>433.3</v>
+        <v>454.01</v>
       </c>
       <c r="AT15">
         <v>0</v>
       </c>
       <c r="AU15">
-        <v>0</v>
+        <v>15016.22</v>
       </c>
       <c r="AV15">
-        <v>0</v>
+        <v>15016.22</v>
       </c>
       <c r="AW15">
-        <v>0</v>
+        <v>5009.04</v>
       </c>
       <c r="AX15">
         <v>0</v>
@@ -3555,22 +3318,22 @@
         <v>0</v>
       </c>
       <c r="BA15">
-        <v>433.3</v>
+        <v>454.01</v>
       </c>
       <c r="BB15">
-        <v>433.3</v>
+        <v>454.01</v>
       </c>
       <c r="BC15">
         <v>0</v>
       </c>
       <c r="BD15">
-        <v>0</v>
+        <v>15016.22</v>
       </c>
       <c r="BE15">
-        <v>0</v>
+        <v>15016.22</v>
       </c>
       <c r="BF15">
-        <v>0</v>
+        <v>5009.04</v>
       </c>
       <c r="BG15">
         <v>0</v>
@@ -3582,22 +3345,22 @@
         <v>0</v>
       </c>
       <c r="BJ15">
-        <v>433.3</v>
+        <v>454.01</v>
       </c>
       <c r="BK15">
-        <v>433.3</v>
+        <v>454.01</v>
       </c>
       <c r="BL15">
         <v>0</v>
       </c>
       <c r="BM15">
-        <v>0</v>
+        <v>15016.22</v>
       </c>
       <c r="BN15">
-        <v>0</v>
+        <v>15016.22</v>
       </c>
       <c r="BO15">
-        <v>0</v>
+        <v>5009.04</v>
       </c>
       <c r="BP15">
         <v>0</v>
@@ -3609,10 +3372,10 @@
         <v>0</v>
       </c>
       <c r="BS15">
-        <v>18.12</v>
+        <v>725.13</v>
       </c>
       <c r="BT15">
-        <v>7.35</v>
+        <v>6.56</v>
       </c>
       <c r="BU15">
         <v>0</v>
@@ -3621,16 +3384,16 @@
         <v>0</v>
       </c>
       <c r="BW15">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="BX15">
-        <v>25.48</v>
+        <v>731.69</v>
       </c>
       <c r="BY15">
-        <v>31.41</v>
+        <v>730.12</v>
       </c>
       <c r="BZ15">
-        <v>10.59</v>
+        <v>7.04</v>
       </c>
       <c r="CA15">
         <v>0</v>
@@ -3639,16 +3402,16 @@
         <v>0</v>
       </c>
       <c r="CC15">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="CD15">
-        <v>42.03</v>
+        <v>737.16</v>
       </c>
       <c r="CE15">
-        <v>41.55</v>
+        <v>730.12</v>
       </c>
       <c r="CF15">
-        <v>13.9</v>
+        <v>8.01</v>
       </c>
       <c r="CG15">
         <v>0</v>
@@ -3657,33 +3420,33 @@
         <v>0</v>
       </c>
       <c r="CI15">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="CJ15">
-        <v>55.49</v>
+        <v>738.13</v>
       </c>
       <c r="CK15">
-        <v>1433.0420969023</v>
+        <v>1425.46875</v>
       </c>
       <c r="CL15">
-        <v>1486.4063272368</v>
+        <v>1479.5653584171</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>1338717</v>
+        <v>1243660</v>
       </c>
       <c r="B16" t="str">
-        <v>1459225</v>
+        <v>1368615</v>
       </c>
       <c r="C16" t="str">
-        <v>785695</v>
+        <v>738111</v>
       </c>
       <c r="E16" t="str">
-        <v>UGARTE ROSARIO</v>
+        <v>SERJAI HERNAN LEONARDO</v>
       </c>
       <c r="F16" s="1">
-        <v>45894</v>
+        <v>45768</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -3698,234 +3461,36 @@
         <v>IFA</v>
       </c>
       <c r="K16" t="str">
-        <v>IFA 3</v>
+        <v>IFA 4</v>
       </c>
       <c r="N16" t="str">
         <v>Argentina</v>
       </c>
-      <c r="O16" s="1">
-        <v>45895</v>
-      </c>
       <c r="P16" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16">
-        <v>174442.56</v>
-      </c>
-      <c r="S16">
-        <v>14583.8</v>
-      </c>
-      <c r="T16">
-        <v>159795.9</v>
-      </c>
-      <c r="U16">
-        <v>0</v>
-      </c>
-      <c r="V16">
-        <v>30481.69</v>
-      </c>
-      <c r="W16">
-        <v>41.57</v>
-      </c>
-      <c r="AA16">
-        <v>30481.69</v>
-      </c>
-      <c r="AB16">
-        <v>30481.69</v>
-      </c>
-      <c r="AC16">
-        <v>0</v>
-      </c>
-      <c r="AD16">
-        <v>41.57</v>
-      </c>
-      <c r="AE16">
-        <v>41.57</v>
-      </c>
-      <c r="AF16">
-        <v>0</v>
-      </c>
-      <c r="AG16">
-        <v>0</v>
-      </c>
-      <c r="AH16">
-        <v>0</v>
-      </c>
-      <c r="AI16">
-        <v>0</v>
-      </c>
-      <c r="AJ16">
-        <v>0</v>
-      </c>
-      <c r="AK16">
-        <v>0</v>
-      </c>
-      <c r="AL16">
-        <v>0</v>
-      </c>
-      <c r="AM16">
-        <v>0</v>
-      </c>
-      <c r="AR16">
-        <v>30481.69</v>
-      </c>
-      <c r="AS16">
-        <v>30481.69</v>
-      </c>
-      <c r="AT16">
-        <v>0</v>
-      </c>
-      <c r="AU16">
-        <v>41.57</v>
-      </c>
-      <c r="AV16">
-        <v>41.57</v>
-      </c>
-      <c r="AW16">
-        <v>0</v>
-      </c>
-      <c r="AX16">
-        <v>0</v>
-      </c>
-      <c r="AY16">
-        <v>0</v>
-      </c>
-      <c r="AZ16">
-        <v>0</v>
-      </c>
-      <c r="BA16">
-        <v>30481.69</v>
-      </c>
-      <c r="BB16">
-        <v>30481.69</v>
-      </c>
-      <c r="BC16">
-        <v>0</v>
-      </c>
-      <c r="BD16">
-        <v>41.57</v>
-      </c>
-      <c r="BE16">
-        <v>41.57</v>
-      </c>
-      <c r="BF16">
-        <v>0</v>
-      </c>
-      <c r="BG16">
-        <v>0</v>
-      </c>
-      <c r="BH16">
-        <v>0</v>
-      </c>
-      <c r="BI16">
-        <v>0</v>
-      </c>
-      <c r="BJ16">
-        <v>30481.69</v>
-      </c>
-      <c r="BK16">
-        <v>30481.69</v>
-      </c>
-      <c r="BL16">
-        <v>0</v>
-      </c>
-      <c r="BM16">
-        <v>41.57</v>
-      </c>
-      <c r="BN16">
-        <v>41.57</v>
-      </c>
-      <c r="BO16">
-        <v>0</v>
-      </c>
-      <c r="BP16">
-        <v>0</v>
-      </c>
-      <c r="BQ16">
-        <v>0</v>
-      </c>
-      <c r="BR16">
-        <v>0</v>
-      </c>
-      <c r="BS16">
-        <v>59.51</v>
-      </c>
-      <c r="BT16">
-        <v>263.66</v>
-      </c>
-      <c r="BU16">
-        <v>0</v>
-      </c>
-      <c r="BV16">
-        <v>0</v>
-      </c>
-      <c r="BW16">
-        <v>0</v>
-      </c>
-      <c r="BX16">
-        <v>323.17</v>
-      </c>
-      <c r="BY16">
-        <v>89.51</v>
-      </c>
-      <c r="BZ16">
-        <v>368.37</v>
-      </c>
-      <c r="CA16">
-        <v>0</v>
-      </c>
-      <c r="CB16">
-        <v>0</v>
-      </c>
-      <c r="CC16">
-        <v>0</v>
-      </c>
-      <c r="CD16">
-        <v>457.88</v>
-      </c>
-      <c r="CE16">
-        <v>296.61</v>
-      </c>
-      <c r="CF16">
-        <v>368.37</v>
-      </c>
-      <c r="CG16">
-        <v>0</v>
-      </c>
-      <c r="CH16">
-        <v>0</v>
-      </c>
-      <c r="CI16">
-        <v>0</v>
-      </c>
-      <c r="CJ16">
-        <v>664.98</v>
-      </c>
-      <c r="CK16">
-        <v>1433.0420969023</v>
-      </c>
-      <c r="CL16">
-        <v>1486.4063272368</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>1344135</v>
+        <v>1251226</v>
       </c>
       <c r="B17" t="str">
-        <v>1463223</v>
+        <v>1375361</v>
       </c>
       <c r="C17" t="str">
-        <v>788923</v>
+        <v>740033</v>
       </c>
       <c r="E17" t="str">
-        <v>LOPEZ PAULA</v>
+        <v>GONZALEZ JUAN EMILIO</v>
       </c>
       <c r="F17" s="1">
-        <v>45901</v>
+        <v>45770</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -3946,7 +3511,7 @@
         <v>Argentina</v>
       </c>
       <c r="O17" s="1">
-        <v>46051</v>
+        <v>45776</v>
       </c>
       <c r="P17" t="str">
         <v>1</v>
@@ -3955,25 +3520,28 @@
         <v>1</v>
       </c>
       <c r="R17">
-        <v>4058.61</v>
+        <v>7773.18</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>5999.45</v>
       </c>
       <c r="T17">
-        <v>3814.37</v>
+        <v>1661.52</v>
       </c>
       <c r="U17">
         <v>0</v>
       </c>
       <c r="V17">
-        <v>350000</v>
+        <v>116997.13</v>
+      </c>
+      <c r="Y17">
+        <v>30.11</v>
       </c>
       <c r="AA17">
-        <v>350000</v>
+        <v>116997.13</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>116997.13</v>
       </c>
       <c r="AC17">
         <v>0</v>
@@ -4009,10 +3577,10 @@
         <v>0</v>
       </c>
       <c r="AR17">
-        <v>350000</v>
+        <v>116997.13</v>
       </c>
       <c r="AS17">
-        <v>0</v>
+        <v>116997.13</v>
       </c>
       <c r="AT17">
         <v>0</v>
@@ -4036,10 +3604,10 @@
         <v>0</v>
       </c>
       <c r="BA17">
-        <v>350000</v>
+        <v>116997.13</v>
       </c>
       <c r="BB17">
-        <v>0</v>
+        <v>116997.13</v>
       </c>
       <c r="BC17">
         <v>0</v>
@@ -4063,10 +3631,10 @@
         <v>0</v>
       </c>
       <c r="BJ17">
-        <v>350000</v>
+        <v>116997.13</v>
       </c>
       <c r="BK17">
-        <v>0</v>
+        <v>116997.13</v>
       </c>
       <c r="BL17">
         <v>0</v>
@@ -4093,7 +3661,7 @@
         <v>0</v>
       </c>
       <c r="BT17">
-        <v>5.18</v>
+        <v>9.37</v>
       </c>
       <c r="BU17">
         <v>0</v>
@@ -4102,16 +3670,16 @@
         <v>0</v>
       </c>
       <c r="BW17">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="BX17">
-        <v>5.18</v>
+        <v>9.38</v>
       </c>
       <c r="BY17">
-        <v>0</v>
+        <v>14.83</v>
       </c>
       <c r="BZ17">
-        <v>5.18</v>
+        <v>12.74</v>
       </c>
       <c r="CA17">
         <v>0</v>
@@ -4120,16 +3688,16 @@
         <v>0</v>
       </c>
       <c r="CC17">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="CD17">
-        <v>5.18</v>
+        <v>27.62</v>
       </c>
       <c r="CE17">
-        <v>0</v>
+        <v>19.87</v>
       </c>
       <c r="CF17">
-        <v>5.18</v>
+        <v>18.76</v>
       </c>
       <c r="CG17">
         <v>0</v>
@@ -4138,33 +3706,33 @@
         <v>0</v>
       </c>
       <c r="CI17">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="CJ17">
-        <v>5.18</v>
+        <v>38.78</v>
       </c>
       <c r="CK17">
-        <v>1433.0420969023</v>
+        <v>1425.46875</v>
       </c>
       <c r="CL17">
-        <v>1486.4063272368</v>
+        <v>1479.5653584171</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>1363846</v>
+        <v>1263431</v>
       </c>
       <c r="B18" t="str">
-        <v>1477220</v>
+        <v>1385990</v>
       </c>
       <c r="C18" t="str">
-        <v>797694</v>
+        <v>742621</v>
       </c>
       <c r="E18" t="str">
-        <v>BUTLER JAIME</v>
+        <v>QUIRELLI MAXIMO</v>
       </c>
       <c r="F18" s="1">
-        <v>45924</v>
+        <v>45777</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -4179,13 +3747,13 @@
         <v>IFA</v>
       </c>
       <c r="K18" t="str">
-        <v>IFA 3</v>
+        <v>IFA 2</v>
       </c>
       <c r="N18" t="str">
         <v>Argentina</v>
       </c>
       <c r="O18" s="1">
-        <v>45943</v>
+        <v>45779</v>
       </c>
       <c r="P18" t="str">
         <v>1</v>
@@ -4194,49 +3762,49 @@
         <v>1</v>
       </c>
       <c r="R18">
-        <v>4430.07</v>
+        <v>5166.76</v>
       </c>
       <c r="S18">
-        <v>3906.26</v>
+        <v>2138.51</v>
       </c>
       <c r="T18">
-        <v>508.3</v>
+        <v>3008.71</v>
       </c>
       <c r="U18">
         <v>0</v>
       </c>
       <c r="V18">
-        <v>-0.42</v>
+        <v>-4932.51</v>
       </c>
       <c r="W18">
-        <v>10.61</v>
+        <v>19.56</v>
       </c>
       <c r="Y18">
-        <v>4.9</v>
+        <v>3.45</v>
       </c>
       <c r="AA18">
-        <v>-0.42</v>
+        <v>-4932.51</v>
       </c>
       <c r="AB18">
-        <v>-0.42</v>
+        <v>-4932.51</v>
       </c>
       <c r="AC18">
         <v>0</v>
       </c>
       <c r="AD18">
-        <v>10.61</v>
+        <v>19.56</v>
       </c>
       <c r="AE18">
-        <v>10.61</v>
+        <v>19.56</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>19.56</v>
       </c>
       <c r="AG18">
         <v>0</v>
       </c>
       <c r="AH18">
-        <v>0</v>
+        <v>19.56</v>
       </c>
       <c r="AI18">
         <v>0</v>
@@ -4254,22 +3822,22 @@
         <v>0</v>
       </c>
       <c r="AR18">
-        <v>-0.42</v>
+        <v>-4932.51</v>
       </c>
       <c r="AS18">
-        <v>-0.42</v>
+        <v>-4932.51</v>
       </c>
       <c r="AT18">
         <v>0</v>
       </c>
       <c r="AU18">
-        <v>10.61</v>
+        <v>19.56</v>
       </c>
       <c r="AV18">
-        <v>10.61</v>
+        <v>19.56</v>
       </c>
       <c r="AW18">
-        <v>0</v>
+        <v>19.56</v>
       </c>
       <c r="AX18">
         <v>0</v>
@@ -4281,22 +3849,22 @@
         <v>0</v>
       </c>
       <c r="BA18">
-        <v>-0.42</v>
+        <v>-4932.51</v>
       </c>
       <c r="BB18">
-        <v>-0.42</v>
+        <v>-4932.51</v>
       </c>
       <c r="BC18">
         <v>0</v>
       </c>
       <c r="BD18">
-        <v>10.61</v>
+        <v>19.56</v>
       </c>
       <c r="BE18">
-        <v>10.61</v>
+        <v>19.56</v>
       </c>
       <c r="BF18">
-        <v>0</v>
+        <v>19.56</v>
       </c>
       <c r="BG18">
         <v>0</v>
@@ -4308,22 +3876,22 @@
         <v>0</v>
       </c>
       <c r="BJ18">
-        <v>-0.42</v>
+        <v>-4932.51</v>
       </c>
       <c r="BK18">
-        <v>-0.42</v>
+        <v>-4932.51</v>
       </c>
       <c r="BL18">
         <v>0</v>
       </c>
       <c r="BM18">
-        <v>10.61</v>
+        <v>19.56</v>
       </c>
       <c r="BN18">
-        <v>10.61</v>
+        <v>19.56</v>
       </c>
       <c r="BO18">
-        <v>0</v>
+        <v>19.56</v>
       </c>
       <c r="BP18">
         <v>0</v>
@@ -4335,10 +3903,10 @@
         <v>0</v>
       </c>
       <c r="BS18">
-        <v>10.31</v>
+        <v>0</v>
       </c>
       <c r="BT18">
-        <v>1.51</v>
+        <v>1.74</v>
       </c>
       <c r="BU18">
         <v>0</v>
@@ -4350,13 +3918,13 @@
         <v>0.01</v>
       </c>
       <c r="BX18">
-        <v>11.83</v>
+        <v>1.75</v>
       </c>
       <c r="BY18">
-        <v>18.58</v>
+        <v>14.74</v>
       </c>
       <c r="BZ18">
-        <v>3.37</v>
+        <v>2.02</v>
       </c>
       <c r="CA18">
         <v>0</v>
@@ -4368,13 +3936,13 @@
         <v>0.01</v>
       </c>
       <c r="CD18">
-        <v>21.96</v>
+        <v>16.77</v>
       </c>
       <c r="CE18">
-        <v>22.45</v>
+        <v>14.74</v>
       </c>
       <c r="CF18">
-        <v>3.5</v>
+        <v>17.72</v>
       </c>
       <c r="CG18">
         <v>0</v>
@@ -4386,30 +3954,30 @@
         <v>0.01</v>
       </c>
       <c r="CJ18">
-        <v>25.96</v>
+        <v>32.47</v>
       </c>
       <c r="CK18">
-        <v>1433.0420969023</v>
+        <v>1425.46875</v>
       </c>
       <c r="CL18">
-        <v>1486.4063272368</v>
+        <v>1479.5653584171</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>1475082</v>
+        <v>1273461</v>
       </c>
       <c r="B19" t="str">
-        <v>1541578</v>
+        <v>1395432</v>
       </c>
       <c r="C19" t="str">
-        <v>841888</v>
+        <v>746143</v>
       </c>
       <c r="E19" t="str">
-        <v>SCHAPIRO ANDRES MARTIN</v>
+        <v>LOPEZ FONTAN ROCIO</v>
       </c>
       <c r="F19" s="1">
-        <v>46024</v>
+        <v>45789</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -4430,7 +3998,7 @@
         <v>Argentina</v>
       </c>
       <c r="O19" s="1">
-        <v>46024</v>
+        <v>45848</v>
       </c>
       <c r="P19" t="str">
         <v>1</v>
@@ -4439,13 +4007,148 @@
         <v>1</v>
       </c>
       <c r="R19">
+        <v>7640.09</v>
+      </c>
+      <c r="S19">
+        <v>4508.28</v>
+      </c>
+      <c r="T19">
+        <v>3121.19</v>
+      </c>
+      <c r="U19">
+        <v>0</v>
+      </c>
+      <c r="V19">
+        <v>-0.03</v>
+      </c>
+      <c r="Y19">
+        <v>10.61</v>
+      </c>
+      <c r="AA19">
+        <v>-0.03</v>
+      </c>
+      <c r="AB19">
+        <v>-0.03</v>
+      </c>
+      <c r="AC19">
+        <v>0</v>
+      </c>
+      <c r="AD19">
+        <v>0</v>
+      </c>
+      <c r="AE19">
+        <v>0</v>
+      </c>
+      <c r="AF19">
+        <v>0</v>
+      </c>
+      <c r="AG19">
+        <v>0</v>
+      </c>
+      <c r="AH19">
+        <v>0</v>
+      </c>
+      <c r="AI19">
+        <v>0</v>
+      </c>
+      <c r="AJ19">
+        <v>0</v>
+      </c>
+      <c r="AK19">
+        <v>0</v>
+      </c>
+      <c r="AL19">
+        <v>0</v>
+      </c>
+      <c r="AM19">
+        <v>0</v>
+      </c>
+      <c r="AR19">
+        <v>-0.03</v>
+      </c>
+      <c r="AS19">
+        <v>-0.03</v>
+      </c>
+      <c r="AT19">
+        <v>0</v>
+      </c>
+      <c r="AU19">
+        <v>0</v>
+      </c>
+      <c r="AV19">
+        <v>0</v>
+      </c>
+      <c r="AW19">
+        <v>0</v>
+      </c>
+      <c r="AX19">
+        <v>0</v>
+      </c>
+      <c r="AY19">
+        <v>0</v>
+      </c>
+      <c r="AZ19">
+        <v>0</v>
+      </c>
+      <c r="BA19">
+        <v>-0.03</v>
+      </c>
+      <c r="BB19">
+        <v>-0.03</v>
+      </c>
+      <c r="BC19">
+        <v>0</v>
+      </c>
+      <c r="BD19">
+        <v>0</v>
+      </c>
+      <c r="BE19">
+        <v>0</v>
+      </c>
+      <c r="BF19">
+        <v>0</v>
+      </c>
+      <c r="BG19">
+        <v>0</v>
+      </c>
+      <c r="BH19">
+        <v>0</v>
+      </c>
+      <c r="BI19">
+        <v>0</v>
+      </c>
+      <c r="BJ19">
+        <v>-0.03</v>
+      </c>
+      <c r="BK19">
+        <v>-0.03</v>
+      </c>
+      <c r="BL19">
+        <v>0</v>
+      </c>
+      <c r="BM19">
+        <v>0</v>
+      </c>
+      <c r="BN19">
+        <v>0</v>
+      </c>
+      <c r="BO19">
+        <v>0</v>
+      </c>
+      <c r="BP19">
+        <v>0</v>
+      </c>
+      <c r="BQ19">
+        <v>0</v>
+      </c>
+      <c r="BR19">
         <v>0</v>
       </c>
       <c r="BS19">
-        <v>0.08</v>
+        <v>5</v>
       </c>
       <c r="BT19">
-        <v>1.18</v>
+        <v>8.57</v>
       </c>
       <c r="BU19">
         <v>0</v>
@@ -4454,16 +4157,16 @@
         <v>0</v>
       </c>
       <c r="BW19">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="BX19">
-        <v>1.26</v>
+        <v>13.59</v>
       </c>
       <c r="BY19">
-        <v>0.91</v>
+        <v>32.62</v>
       </c>
       <c r="BZ19">
-        <v>1.7</v>
+        <v>12.31</v>
       </c>
       <c r="CA19">
         <v>0</v>
@@ -4472,16 +4175,16 @@
         <v>0</v>
       </c>
       <c r="CC19">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="CD19">
-        <v>2.61</v>
+        <v>44.97</v>
       </c>
       <c r="CE19">
-        <v>0.91</v>
+        <v>44.42</v>
       </c>
       <c r="CF19">
-        <v>1.7</v>
+        <v>16.45</v>
       </c>
       <c r="CG19">
         <v>0</v>
@@ -4490,27 +4193,33 @@
         <v>0</v>
       </c>
       <c r="CI19">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="CJ19">
-        <v>2.61</v>
+        <v>60.92</v>
+      </c>
+      <c r="CK19">
+        <v>1425.46875</v>
+      </c>
+      <c r="CL19">
+        <v>1479.5653584171</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>1483077</v>
+        <v>1338717</v>
       </c>
       <c r="B20" t="str">
-        <v>1547305</v>
+        <v>1459225</v>
       </c>
       <c r="C20" t="str">
-        <v>846219</v>
+        <v>785695</v>
       </c>
       <c r="E20" t="str">
-        <v>VERDUGA SANTILLAN JUAN</v>
+        <v>UGARTE ROSARIO</v>
       </c>
       <c r="F20" s="1">
-        <v>46030</v>
+        <v>45894</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -4530,31 +4239,229 @@
       <c r="N20" t="str">
         <v>Argentina</v>
       </c>
+      <c r="O20" s="1">
+        <v>45895</v>
+      </c>
       <c r="P20" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>174590.2</v>
+      </c>
+      <c r="S20">
+        <v>26618.52</v>
+      </c>
+      <c r="T20">
+        <v>147953.4</v>
+      </c>
+      <c r="U20">
+        <v>0</v>
+      </c>
+      <c r="V20">
+        <v>23410.68</v>
+      </c>
+      <c r="W20">
+        <v>1.88</v>
+      </c>
+      <c r="AA20">
+        <v>23410.68</v>
+      </c>
+      <c r="AB20">
+        <v>23410.68</v>
+      </c>
+      <c r="AC20">
+        <v>0</v>
+      </c>
+      <c r="AD20">
+        <v>1.88</v>
+      </c>
+      <c r="AE20">
+        <v>1.88</v>
+      </c>
+      <c r="AF20">
+        <v>0</v>
+      </c>
+      <c r="AG20">
+        <v>0</v>
+      </c>
+      <c r="AH20">
+        <v>0</v>
+      </c>
+      <c r="AI20">
+        <v>0</v>
+      </c>
+      <c r="AJ20">
+        <v>0</v>
+      </c>
+      <c r="AK20">
+        <v>0</v>
+      </c>
+      <c r="AL20">
+        <v>0</v>
+      </c>
+      <c r="AM20">
+        <v>0</v>
+      </c>
+      <c r="AR20">
+        <v>23410.68</v>
+      </c>
+      <c r="AS20">
+        <v>23410.68</v>
+      </c>
+      <c r="AT20">
+        <v>0</v>
+      </c>
+      <c r="AU20">
+        <v>1.88</v>
+      </c>
+      <c r="AV20">
+        <v>1.88</v>
+      </c>
+      <c r="AW20">
+        <v>0</v>
+      </c>
+      <c r="AX20">
+        <v>0</v>
+      </c>
+      <c r="AY20">
+        <v>0</v>
+      </c>
+      <c r="AZ20">
+        <v>0</v>
+      </c>
+      <c r="BA20">
+        <v>23410.68</v>
+      </c>
+      <c r="BB20">
+        <v>23410.68</v>
+      </c>
+      <c r="BC20">
+        <v>0</v>
+      </c>
+      <c r="BD20">
+        <v>1.88</v>
+      </c>
+      <c r="BE20">
+        <v>1.88</v>
+      </c>
+      <c r="BF20">
+        <v>0</v>
+      </c>
+      <c r="BG20">
+        <v>0</v>
+      </c>
+      <c r="BH20">
+        <v>0</v>
+      </c>
+      <c r="BI20">
+        <v>0</v>
+      </c>
+      <c r="BJ20">
+        <v>23410.68</v>
+      </c>
+      <c r="BK20">
+        <v>23410.68</v>
+      </c>
+      <c r="BL20">
+        <v>0</v>
+      </c>
+      <c r="BM20">
+        <v>1.88</v>
+      </c>
+      <c r="BN20">
+        <v>1.88</v>
+      </c>
+      <c r="BO20">
+        <v>0</v>
+      </c>
+      <c r="BP20">
+        <v>0</v>
+      </c>
+      <c r="BQ20">
+        <v>0</v>
+      </c>
+      <c r="BR20">
+        <v>0</v>
+      </c>
+      <c r="BS20">
+        <v>138.33</v>
+      </c>
+      <c r="BT20">
+        <v>284.63</v>
+      </c>
+      <c r="BU20">
+        <v>0</v>
+      </c>
+      <c r="BV20">
+        <v>0</v>
+      </c>
+      <c r="BW20">
+        <v>0</v>
+      </c>
+      <c r="BX20">
+        <v>422.96</v>
+      </c>
+      <c r="BY20">
+        <v>197.64</v>
+      </c>
+      <c r="BZ20">
+        <v>459.63</v>
+      </c>
+      <c r="CA20">
+        <v>0</v>
+      </c>
+      <c r="CB20">
+        <v>0</v>
+      </c>
+      <c r="CC20">
+        <v>0</v>
+      </c>
+      <c r="CD20">
+        <v>657.27</v>
+      </c>
+      <c r="CE20">
+        <v>404.73</v>
+      </c>
+      <c r="CF20">
+        <v>459.63</v>
+      </c>
+      <c r="CG20">
+        <v>0</v>
+      </c>
+      <c r="CH20">
+        <v>0</v>
+      </c>
+      <c r="CI20">
+        <v>0</v>
+      </c>
+      <c r="CJ20">
+        <v>864.36</v>
+      </c>
+      <c r="CK20">
+        <v>1425.46875</v>
+      </c>
+      <c r="CL20">
+        <v>1479.5653584171</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>1487371</v>
+        <v>1344135</v>
       </c>
       <c r="B21" t="str">
-        <v>1550463</v>
+        <v>1463223</v>
       </c>
       <c r="C21" t="str">
-        <v>848470</v>
+        <v>788923</v>
       </c>
       <c r="E21" t="str">
-        <v>DEGANO GREGORIO MARTIN</v>
+        <v>LOPEZ PAULA</v>
       </c>
       <c r="F21" s="1">
-        <v>46034</v>
+        <v>45901</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -4575,7 +4482,7 @@
         <v>Argentina</v>
       </c>
       <c r="O21" s="1">
-        <v>46049</v>
+        <v>46051</v>
       </c>
       <c r="P21" t="str">
         <v>1</v>
@@ -4584,148 +4491,22 @@
         <v>1</v>
       </c>
       <c r="R21">
-        <v>1598.62</v>
+        <v>4084.47</v>
       </c>
       <c r="S21">
-        <v>583.45</v>
+        <v>0</v>
       </c>
       <c r="T21">
-        <v>1015.16</v>
+        <v>4084.48</v>
       </c>
       <c r="U21">
         <v>0</v>
       </c>
-      <c r="V21">
-        <v>-1552.44</v>
-      </c>
-      <c r="W21">
-        <v>1.09</v>
-      </c>
-      <c r="AA21">
-        <v>-1552.44</v>
-      </c>
-      <c r="AB21">
-        <v>-1552.44</v>
-      </c>
-      <c r="AC21">
-        <v>0</v>
-      </c>
-      <c r="AD21">
-        <v>1.09</v>
-      </c>
-      <c r="AE21">
-        <v>1.09</v>
-      </c>
-      <c r="AF21">
-        <v>1.09</v>
-      </c>
-      <c r="AG21">
-        <v>0</v>
-      </c>
-      <c r="AH21">
-        <v>1.09</v>
-      </c>
-      <c r="AI21">
-        <v>0</v>
-      </c>
-      <c r="AJ21">
-        <v>0</v>
-      </c>
-      <c r="AK21">
-        <v>0</v>
-      </c>
-      <c r="AL21">
-        <v>0</v>
-      </c>
-      <c r="AM21">
-        <v>0</v>
-      </c>
-      <c r="AR21">
-        <v>-1552.44</v>
-      </c>
-      <c r="AS21">
-        <v>-1552.44</v>
-      </c>
-      <c r="AT21">
-        <v>0</v>
-      </c>
-      <c r="AU21">
-        <v>1.09</v>
-      </c>
-      <c r="AV21">
-        <v>1.09</v>
-      </c>
-      <c r="AW21">
-        <v>1.09</v>
-      </c>
-      <c r="AX21">
-        <v>0</v>
-      </c>
-      <c r="AY21">
-        <v>0</v>
-      </c>
-      <c r="AZ21">
-        <v>0</v>
-      </c>
-      <c r="BA21">
-        <v>-1552.44</v>
-      </c>
-      <c r="BB21">
-        <v>-1552.44</v>
-      </c>
-      <c r="BC21">
-        <v>0</v>
-      </c>
-      <c r="BD21">
-        <v>1.09</v>
-      </c>
-      <c r="BE21">
-        <v>1.09</v>
-      </c>
-      <c r="BF21">
-        <v>1.09</v>
-      </c>
-      <c r="BG21">
-        <v>0</v>
-      </c>
-      <c r="BH21">
-        <v>0</v>
-      </c>
-      <c r="BI21">
-        <v>0</v>
-      </c>
-      <c r="BJ21">
-        <v>-1552.44</v>
-      </c>
-      <c r="BK21">
-        <v>-1552.44</v>
-      </c>
-      <c r="BL21">
-        <v>0</v>
-      </c>
-      <c r="BM21">
-        <v>1.09</v>
-      </c>
-      <c r="BN21">
-        <v>1.09</v>
-      </c>
-      <c r="BO21">
-        <v>1.09</v>
-      </c>
-      <c r="BP21">
-        <v>0</v>
-      </c>
-      <c r="BQ21">
-        <v>0</v>
-      </c>
-      <c r="BR21">
-        <v>0</v>
-      </c>
       <c r="BS21">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="BT21">
-        <v>1.25</v>
+        <v>7.58</v>
       </c>
       <c r="BU21">
         <v>0</v>
@@ -4737,13 +4518,13 @@
         <v>0</v>
       </c>
       <c r="BX21">
-        <v>4.82</v>
+        <v>7.58</v>
       </c>
       <c r="BY21">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="BZ21">
-        <v>1.25</v>
+        <v>8.06</v>
       </c>
       <c r="CA21">
         <v>0</v>
@@ -4755,13 +4536,13 @@
         <v>0</v>
       </c>
       <c r="CD21">
-        <v>4.82</v>
+        <v>8.06</v>
       </c>
       <c r="CE21">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="CF21">
-        <v>1.25</v>
+        <v>8.06</v>
       </c>
       <c r="CG21">
         <v>0</v>
@@ -4773,30 +4554,30 @@
         <v>0</v>
       </c>
       <c r="CJ21">
-        <v>4.82</v>
+        <v>8.06</v>
       </c>
       <c r="CK21">
-        <v>1433.0420969023</v>
+        <v>1425.46875</v>
       </c>
       <c r="CL21">
-        <v>1486.4063272368</v>
+        <v>1479.5653584171</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>1492377</v>
+        <v>1363846</v>
       </c>
       <c r="B22" t="str">
-        <v>1554161</v>
+        <v>1477220</v>
       </c>
       <c r="C22" t="str">
-        <v>851472</v>
+        <v>797694</v>
       </c>
       <c r="E22" t="str">
-        <v>YEDLIN MAGALI DENISE</v>
+        <v>BUTLER JAIME</v>
       </c>
       <c r="F22" s="1">
-        <v>46037</v>
+        <v>45924</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -4817,7 +4598,7 @@
         <v>Argentina</v>
       </c>
       <c r="O22" s="1">
-        <v>46037</v>
+        <v>45943</v>
       </c>
       <c r="P22" t="str">
         <v>1</v>
@@ -4826,22 +4607,151 @@
         <v>1</v>
       </c>
       <c r="R22">
-        <v>842.3</v>
+        <v>4759.48</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>4381.79</v>
       </c>
       <c r="T22">
-        <v>842.3</v>
+        <v>335.68</v>
       </c>
       <c r="U22">
         <v>0</v>
       </c>
+      <c r="V22">
+        <v>35731.84</v>
+      </c>
+      <c r="W22">
+        <v>10.61</v>
+      </c>
+      <c r="Y22">
+        <v>6.34</v>
+      </c>
+      <c r="AA22">
+        <v>35731.84</v>
+      </c>
+      <c r="AB22">
+        <v>35731.84</v>
+      </c>
+      <c r="AC22">
+        <v>0</v>
+      </c>
+      <c r="AD22">
+        <v>10.61</v>
+      </c>
+      <c r="AE22">
+        <v>10.61</v>
+      </c>
+      <c r="AF22">
+        <v>0</v>
+      </c>
+      <c r="AG22">
+        <v>0</v>
+      </c>
+      <c r="AH22">
+        <v>0</v>
+      </c>
+      <c r="AI22">
+        <v>0</v>
+      </c>
+      <c r="AJ22">
+        <v>0</v>
+      </c>
+      <c r="AK22">
+        <v>0</v>
+      </c>
+      <c r="AL22">
+        <v>0</v>
+      </c>
+      <c r="AM22">
+        <v>0</v>
+      </c>
+      <c r="AR22">
+        <v>35731.84</v>
+      </c>
+      <c r="AS22">
+        <v>35731.84</v>
+      </c>
+      <c r="AT22">
+        <v>0</v>
+      </c>
+      <c r="AU22">
+        <v>10.61</v>
+      </c>
+      <c r="AV22">
+        <v>10.61</v>
+      </c>
+      <c r="AW22">
+        <v>0</v>
+      </c>
+      <c r="AX22">
+        <v>0</v>
+      </c>
+      <c r="AY22">
+        <v>0</v>
+      </c>
+      <c r="AZ22">
+        <v>0</v>
+      </c>
+      <c r="BA22">
+        <v>35731.84</v>
+      </c>
+      <c r="BB22">
+        <v>35731.84</v>
+      </c>
+      <c r="BC22">
+        <v>0</v>
+      </c>
+      <c r="BD22">
+        <v>10.61</v>
+      </c>
+      <c r="BE22">
+        <v>10.61</v>
+      </c>
+      <c r="BF22">
+        <v>0</v>
+      </c>
+      <c r="BG22">
+        <v>0</v>
+      </c>
+      <c r="BH22">
+        <v>0</v>
+      </c>
+      <c r="BI22">
+        <v>0</v>
+      </c>
+      <c r="BJ22">
+        <v>35731.84</v>
+      </c>
+      <c r="BK22">
+        <v>35731.84</v>
+      </c>
+      <c r="BL22">
+        <v>0</v>
+      </c>
+      <c r="BM22">
+        <v>10.61</v>
+      </c>
+      <c r="BN22">
+        <v>10.61</v>
+      </c>
+      <c r="BO22">
+        <v>0</v>
+      </c>
+      <c r="BP22">
+        <v>0</v>
+      </c>
+      <c r="BQ22">
+        <v>0</v>
+      </c>
+      <c r="BR22">
+        <v>0</v>
+      </c>
       <c r="BS22">
-        <v>0.4</v>
+        <v>12.44</v>
       </c>
       <c r="BT22">
-        <v>4.33</v>
+        <v>1.3</v>
       </c>
       <c r="BU22">
         <v>0</v>
@@ -4850,16 +4760,16 @@
         <v>0</v>
       </c>
       <c r="BW22">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="BX22">
-        <v>4.73</v>
+        <v>13.75</v>
       </c>
       <c r="BY22">
-        <v>0.73</v>
+        <v>15.83</v>
       </c>
       <c r="BZ22">
-        <v>4.57</v>
+        <v>3.1</v>
       </c>
       <c r="CA22">
         <v>0</v>
@@ -4868,16 +4778,16 @@
         <v>0</v>
       </c>
       <c r="CC22">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="CD22">
-        <v>5.3</v>
+        <v>18.94</v>
       </c>
       <c r="CE22">
-        <v>0.73</v>
+        <v>24.59</v>
       </c>
       <c r="CF22">
-        <v>4.57</v>
+        <v>3.81</v>
       </c>
       <c r="CG22">
         <v>0</v>
@@ -4886,33 +4796,33 @@
         <v>0</v>
       </c>
       <c r="CI22">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="CJ22">
-        <v>5.3</v>
+        <v>28.41</v>
       </c>
       <c r="CK22">
-        <v>1433.0420969023</v>
+        <v>1425.46875</v>
       </c>
       <c r="CL22">
-        <v>1486.4063272368</v>
+        <v>1479.5653584171</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>1504882</v>
+        <v>1475082</v>
       </c>
       <c r="B23" t="str">
-        <v>1562613</v>
+        <v>1541578</v>
       </c>
       <c r="C23" t="str">
-        <v>857783</v>
+        <v>841888</v>
       </c>
       <c r="E23" t="str">
-        <v>PRICKETT SHANNON LYNN</v>
+        <v>SCHAPIRO ANDRES MARTIN</v>
       </c>
       <c r="F23" s="1">
-        <v>46048</v>
+        <v>46024</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -4927,181 +4837,28 @@
         <v>IFA</v>
       </c>
       <c r="K23" t="str">
-        <v>IFA 2</v>
+        <v>IFA 4</v>
       </c>
       <c r="N23" t="str">
         <v>Argentina</v>
       </c>
       <c r="O23" s="1">
-        <v>46052</v>
+        <v>46024</v>
       </c>
       <c r="P23" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q23">
         <v>1</v>
       </c>
       <c r="R23">
-        <v>27094.87</v>
-      </c>
-      <c r="S23">
-        <v>0</v>
-      </c>
-      <c r="T23">
-        <v>27094.65</v>
-      </c>
-      <c r="U23">
-        <v>0</v>
-      </c>
-      <c r="V23">
-        <v>-0.62</v>
-      </c>
-      <c r="W23">
-        <v>0.22</v>
-      </c>
-      <c r="AA23">
-        <v>-0.62</v>
-      </c>
-      <c r="AB23">
-        <v>-0.62</v>
-      </c>
-      <c r="AC23">
-        <v>0</v>
-      </c>
-      <c r="AD23">
-        <v>0.22</v>
-      </c>
-      <c r="AE23">
-        <v>0.22</v>
-      </c>
-      <c r="AF23">
-        <v>0</v>
-      </c>
-      <c r="AG23">
-        <v>0</v>
-      </c>
-      <c r="AH23">
-        <v>0</v>
-      </c>
-      <c r="AI23">
-        <v>0</v>
-      </c>
-      <c r="AJ23">
-        <v>0</v>
-      </c>
-      <c r="AK23">
-        <v>0</v>
-      </c>
-      <c r="AL23">
-        <v>0</v>
-      </c>
-      <c r="AM23">
-        <v>0</v>
-      </c>
-      <c r="AR23">
-        <v>-0.62</v>
-      </c>
-      <c r="AS23">
-        <v>-0.62</v>
-      </c>
-      <c r="AT23">
-        <v>0</v>
-      </c>
-      <c r="AU23">
-        <v>0.22</v>
-      </c>
-      <c r="AV23">
-        <v>0.22</v>
-      </c>
-      <c r="AW23">
-        <v>0</v>
-      </c>
-      <c r="AX23">
-        <v>0</v>
-      </c>
-      <c r="AY23">
-        <v>0</v>
-      </c>
-      <c r="AZ23">
-        <v>0</v>
-      </c>
-      <c r="BA23">
-        <v>-0.62</v>
-      </c>
-      <c r="BB23">
-        <v>-0.62</v>
-      </c>
-      <c r="BC23">
-        <v>0</v>
-      </c>
-      <c r="BD23">
-        <v>0.22</v>
-      </c>
-      <c r="BE23">
-        <v>0.22</v>
-      </c>
-      <c r="BF23">
-        <v>0</v>
-      </c>
-      <c r="BG23">
-        <v>0</v>
-      </c>
-      <c r="BH23">
-        <v>0</v>
-      </c>
-      <c r="BI23">
-        <v>0</v>
-      </c>
-      <c r="BJ23">
-        <v>-0.62</v>
-      </c>
-      <c r="BK23">
-        <v>-0.62</v>
-      </c>
-      <c r="BL23">
-        <v>0</v>
-      </c>
-      <c r="BM23">
-        <v>0.22</v>
-      </c>
-      <c r="BN23">
-        <v>0.22</v>
-      </c>
-      <c r="BO23">
-        <v>0</v>
-      </c>
-      <c r="BP23">
-        <v>0</v>
-      </c>
-      <c r="BQ23">
-        <v>0</v>
-      </c>
-      <c r="BR23">
-        <v>0</v>
-      </c>
-      <c r="BS23">
-        <v>19.34</v>
-      </c>
-      <c r="BT23">
-        <v>37.04</v>
-      </c>
-      <c r="BU23">
-        <v>0</v>
-      </c>
-      <c r="BV23">
-        <v>0</v>
-      </c>
-      <c r="BW23">
-        <v>0</v>
-      </c>
-      <c r="BX23">
-        <v>56.38</v>
+        <v>0</v>
       </c>
       <c r="BY23">
-        <v>19.34</v>
+        <v>0.91</v>
       </c>
       <c r="BZ23">
-        <v>37.04</v>
+        <v>1.7</v>
       </c>
       <c r="CA23">
         <v>0</v>
@@ -5113,13 +4870,13 @@
         <v>0</v>
       </c>
       <c r="CD23">
-        <v>56.38</v>
+        <v>2.61</v>
       </c>
       <c r="CE23">
-        <v>19.34</v>
+        <v>0.91</v>
       </c>
       <c r="CF23">
-        <v>37.04</v>
+        <v>1.7</v>
       </c>
       <c r="CG23">
         <v>0</v>
@@ -5131,33 +4888,27 @@
         <v>0</v>
       </c>
       <c r="CJ23">
-        <v>56.38</v>
-      </c>
-      <c r="CK23">
-        <v>1433.0420969023</v>
-      </c>
-      <c r="CL23">
-        <v>1486.4063272368</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>1508138</v>
+        <v>1483077</v>
       </c>
       <c r="B24" t="str">
-        <v>163247</v>
+        <v>1547305</v>
       </c>
       <c r="C24" t="str">
-        <v>859664</v>
+        <v>846219</v>
       </c>
       <c r="E24" t="str">
-        <v>ASOCIACIÓN CIVIL SUMATORIA PARA UNA NUEVA ECONOMIA</v>
+        <v>VERDUGA SANTILLAN JUAN</v>
       </c>
       <c r="F24" s="1">
-        <v>46050</v>
+        <v>46030</v>
       </c>
       <c r="G24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H24" t="str">
         <v>IFA 5767</v>
@@ -5169,231 +4920,36 @@
         <v>IFA</v>
       </c>
       <c r="K24" t="str">
-        <v>IFA 4</v>
+        <v>IFA 3</v>
       </c>
       <c r="N24" t="str">
         <v>Argentina</v>
       </c>
-      <c r="O24" s="1">
-        <v>46128</v>
-      </c>
       <c r="P24" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24">
-        <v>10892.47</v>
-      </c>
-      <c r="S24">
-        <v>0</v>
-      </c>
-      <c r="T24">
-        <v>7019.46</v>
-      </c>
-      <c r="U24">
-        <v>0</v>
-      </c>
-      <c r="W24">
-        <v>3873</v>
-      </c>
-      <c r="AA24">
-        <v>0</v>
-      </c>
-      <c r="AB24">
-        <v>0</v>
-      </c>
-      <c r="AC24">
-        <v>0</v>
-      </c>
-      <c r="AD24">
-        <v>3873</v>
-      </c>
-      <c r="AE24">
-        <v>3873</v>
-      </c>
-      <c r="AF24">
-        <v>3873</v>
-      </c>
-      <c r="AG24">
-        <v>0</v>
-      </c>
-      <c r="AH24">
-        <v>3873</v>
-      </c>
-      <c r="AI24">
-        <v>0</v>
-      </c>
-      <c r="AJ24">
-        <v>0</v>
-      </c>
-      <c r="AK24">
-        <v>0</v>
-      </c>
-      <c r="AL24">
-        <v>0</v>
-      </c>
-      <c r="AM24">
-        <v>0</v>
-      </c>
-      <c r="AR24">
-        <v>0</v>
-      </c>
-      <c r="AS24">
-        <v>0</v>
-      </c>
-      <c r="AT24">
-        <v>0</v>
-      </c>
-      <c r="AU24">
-        <v>3873</v>
-      </c>
-      <c r="AV24">
-        <v>3873</v>
-      </c>
-      <c r="AW24">
-        <v>3873</v>
-      </c>
-      <c r="AX24">
-        <v>0</v>
-      </c>
-      <c r="AY24">
-        <v>0</v>
-      </c>
-      <c r="AZ24">
-        <v>0</v>
-      </c>
-      <c r="BA24">
-        <v>0</v>
-      </c>
-      <c r="BB24">
-        <v>0</v>
-      </c>
-      <c r="BC24">
-        <v>0</v>
-      </c>
-      <c r="BD24">
-        <v>3873</v>
-      </c>
-      <c r="BE24">
-        <v>3873</v>
-      </c>
-      <c r="BF24">
-        <v>3873</v>
-      </c>
-      <c r="BG24">
-        <v>0</v>
-      </c>
-      <c r="BH24">
-        <v>0</v>
-      </c>
-      <c r="BI24">
-        <v>0</v>
-      </c>
-      <c r="BJ24">
-        <v>0</v>
-      </c>
-      <c r="BK24">
-        <v>0</v>
-      </c>
-      <c r="BL24">
-        <v>0</v>
-      </c>
-      <c r="BM24">
-        <v>3873</v>
-      </c>
-      <c r="BN24">
-        <v>3873</v>
-      </c>
-      <c r="BO24">
-        <v>3873</v>
-      </c>
-      <c r="BP24">
-        <v>0</v>
-      </c>
-      <c r="BQ24">
-        <v>0</v>
-      </c>
-      <c r="BR24">
-        <v>0</v>
-      </c>
-      <c r="BS24">
-        <v>0.12</v>
-      </c>
-      <c r="BT24">
-        <v>5.34</v>
-      </c>
-      <c r="BU24">
-        <v>0</v>
-      </c>
-      <c r="BV24">
-        <v>0</v>
-      </c>
-      <c r="BW24">
-        <v>0</v>
-      </c>
-      <c r="BX24">
-        <v>5.46</v>
-      </c>
-      <c r="BY24">
-        <v>0.12</v>
-      </c>
-      <c r="BZ24">
-        <v>5.34</v>
-      </c>
-      <c r="CA24">
-        <v>0</v>
-      </c>
-      <c r="CB24">
-        <v>0</v>
-      </c>
-      <c r="CC24">
-        <v>0</v>
-      </c>
-      <c r="CD24">
-        <v>5.46</v>
-      </c>
-      <c r="CE24">
-        <v>0.12</v>
-      </c>
-      <c r="CF24">
-        <v>5.34</v>
-      </c>
-      <c r="CG24">
-        <v>0</v>
-      </c>
-      <c r="CH24">
-        <v>0</v>
-      </c>
-      <c r="CI24">
-        <v>0</v>
-      </c>
-      <c r="CJ24">
-        <v>5.46</v>
-      </c>
-      <c r="CK24">
-        <v>1433.0420969023</v>
-      </c>
-      <c r="CL24">
-        <v>1486.4063272368</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>1513060</v>
+        <v>1487371</v>
       </c>
       <c r="B25" t="str">
-        <v>1568624</v>
+        <v>1550463</v>
       </c>
       <c r="C25" t="str">
-        <v>862473</v>
+        <v>848470</v>
       </c>
       <c r="E25" t="str">
-        <v>ROTILI DIEGO HERNAN</v>
+        <v>DEGANO GREGORIO MARTIN</v>
       </c>
       <c r="F25" s="1">
-        <v>46055</v>
+        <v>46034</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -5414,7 +4970,7 @@
         <v>Argentina</v>
       </c>
       <c r="O25" s="1">
-        <v>46064</v>
+        <v>46049</v>
       </c>
       <c r="P25" t="str">
         <v>1</v>
@@ -5423,25 +4979,148 @@
         <v>1</v>
       </c>
       <c r="R25">
-        <v>7393.26</v>
+        <v>1617.36</v>
       </c>
       <c r="S25">
-        <v>4578.08</v>
+        <v>599.77</v>
       </c>
       <c r="T25">
-        <v>2810.03</v>
+        <v>1017.58</v>
       </c>
       <c r="U25">
         <v>0</v>
       </c>
-      <c r="Y25">
-        <v>5.12</v>
+      <c r="V25">
+        <v>-1552.44</v>
+      </c>
+      <c r="W25">
+        <v>1.09</v>
+      </c>
+      <c r="AA25">
+        <v>-1552.44</v>
+      </c>
+      <c r="AB25">
+        <v>-1552.44</v>
+      </c>
+      <c r="AC25">
+        <v>0</v>
+      </c>
+      <c r="AD25">
+        <v>1.09</v>
+      </c>
+      <c r="AE25">
+        <v>1.09</v>
+      </c>
+      <c r="AF25">
+        <v>1.09</v>
+      </c>
+      <c r="AG25">
+        <v>0</v>
+      </c>
+      <c r="AH25">
+        <v>1.09</v>
+      </c>
+      <c r="AI25">
+        <v>0</v>
+      </c>
+      <c r="AJ25">
+        <v>0</v>
+      </c>
+      <c r="AK25">
+        <v>0</v>
+      </c>
+      <c r="AL25">
+        <v>0</v>
+      </c>
+      <c r="AM25">
+        <v>0</v>
+      </c>
+      <c r="AR25">
+        <v>-1552.44</v>
+      </c>
+      <c r="AS25">
+        <v>-1552.44</v>
+      </c>
+      <c r="AT25">
+        <v>0</v>
+      </c>
+      <c r="AU25">
+        <v>1.09</v>
+      </c>
+      <c r="AV25">
+        <v>1.09</v>
+      </c>
+      <c r="AW25">
+        <v>1.09</v>
+      </c>
+      <c r="AX25">
+        <v>0</v>
+      </c>
+      <c r="AY25">
+        <v>0</v>
+      </c>
+      <c r="AZ25">
+        <v>0</v>
+      </c>
+      <c r="BA25">
+        <v>-1552.44</v>
+      </c>
+      <c r="BB25">
+        <v>-1552.44</v>
+      </c>
+      <c r="BC25">
+        <v>0</v>
+      </c>
+      <c r="BD25">
+        <v>1.09</v>
+      </c>
+      <c r="BE25">
+        <v>1.09</v>
+      </c>
+      <c r="BF25">
+        <v>1.09</v>
+      </c>
+      <c r="BG25">
+        <v>0</v>
+      </c>
+      <c r="BH25">
+        <v>0</v>
+      </c>
+      <c r="BI25">
+        <v>0</v>
+      </c>
+      <c r="BJ25">
+        <v>-1552.44</v>
+      </c>
+      <c r="BK25">
+        <v>-1552.44</v>
+      </c>
+      <c r="BL25">
+        <v>0</v>
+      </c>
+      <c r="BM25">
+        <v>1.09</v>
+      </c>
+      <c r="BN25">
+        <v>1.09</v>
+      </c>
+      <c r="BO25">
+        <v>1.09</v>
+      </c>
+      <c r="BP25">
+        <v>0</v>
+      </c>
+      <c r="BQ25">
+        <v>0</v>
+      </c>
+      <c r="BR25">
+        <v>0</v>
       </c>
       <c r="BS25">
-        <v>26.6</v>
+        <v>3.57</v>
       </c>
       <c r="BT25">
-        <v>23.37</v>
+        <v>2</v>
       </c>
       <c r="BU25">
         <v>0</v>
@@ -5450,16 +5129,16 @@
         <v>0</v>
       </c>
       <c r="BW25">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="BX25">
-        <v>49.98</v>
+        <v>5.57</v>
       </c>
       <c r="BY25">
-        <v>26.6</v>
+        <v>3.57</v>
       </c>
       <c r="BZ25">
-        <v>23.37</v>
+        <v>2.05</v>
       </c>
       <c r="CA25">
         <v>0</v>
@@ -5468,16 +5147,16 @@
         <v>0</v>
       </c>
       <c r="CC25">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="CD25">
-        <v>49.98</v>
+        <v>5.62</v>
       </c>
       <c r="CE25">
-        <v>26.6</v>
+        <v>3.57</v>
       </c>
       <c r="CF25">
-        <v>23.37</v>
+        <v>2.05</v>
       </c>
       <c r="CG25">
         <v>0</v>
@@ -5486,33 +5165,33 @@
         <v>0</v>
       </c>
       <c r="CI25">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="CJ25">
-        <v>49.98</v>
+        <v>5.62</v>
       </c>
       <c r="CK25">
-        <v>1433.0420969023</v>
+        <v>1425.46875</v>
       </c>
       <c r="CL25">
-        <v>1486.4063272368</v>
+        <v>1479.5653584171</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>1523084</v>
+        <v>1492377</v>
       </c>
       <c r="B26" t="str">
-        <v>1576169</v>
+        <v>1554161</v>
       </c>
       <c r="C26" t="str">
-        <v>868572</v>
+        <v>851472</v>
       </c>
       <c r="E26" t="str">
-        <v>IRRAZABAL JONAS</v>
+        <v>YEDLIN MAGALI DENISE</v>
       </c>
       <c r="F26" s="1">
-        <v>46062</v>
+        <v>46037</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -5527,13 +5206,13 @@
         <v>IFA</v>
       </c>
       <c r="K26" t="str">
-        <v>IFA 2</v>
+        <v>IFA 3</v>
       </c>
       <c r="N26" t="str">
         <v>Argentina</v>
       </c>
       <c r="O26" s="1">
-        <v>46063</v>
+        <v>46037</v>
       </c>
       <c r="P26" t="str">
         <v>1</v>
@@ -5542,13 +5221,13 @@
         <v>1</v>
       </c>
       <c r="R26">
-        <v>5024.53</v>
+        <v>866.61</v>
       </c>
       <c r="S26">
         <v>0</v>
       </c>
       <c r="T26">
-        <v>5024.53</v>
+        <v>866.61</v>
       </c>
       <c r="U26">
         <v>0</v>
@@ -5557,7 +5236,7 @@
         <v>0</v>
       </c>
       <c r="BT26">
-        <v>3.47</v>
+        <v>5.2</v>
       </c>
       <c r="BU26">
         <v>0</v>
@@ -5569,13 +5248,13 @@
         <v>0</v>
       </c>
       <c r="BX26">
-        <v>3.47</v>
+        <v>5.2</v>
       </c>
       <c r="BY26">
-        <v>0</v>
+        <v>0.73</v>
       </c>
       <c r="BZ26">
-        <v>3.47</v>
+        <v>6.13</v>
       </c>
       <c r="CA26">
         <v>0</v>
@@ -5587,13 +5266,13 @@
         <v>0</v>
       </c>
       <c r="CD26">
-        <v>3.47</v>
+        <v>6.86</v>
       </c>
       <c r="CE26">
-        <v>0</v>
+        <v>0.73</v>
       </c>
       <c r="CF26">
-        <v>3.47</v>
+        <v>6.13</v>
       </c>
       <c r="CG26">
         <v>0</v>
@@ -5605,30 +5284,30 @@
         <v>0</v>
       </c>
       <c r="CJ26">
-        <v>3.47</v>
+        <v>6.86</v>
       </c>
       <c r="CK26">
-        <v>1433.0420969023</v>
+        <v>1425.46875</v>
       </c>
       <c r="CL26">
-        <v>1486.4063272368</v>
+        <v>1479.5653584171</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>1523376</v>
+        <v>1504882</v>
       </c>
       <c r="B27" t="str">
-        <v>1576380</v>
+        <v>1562613</v>
       </c>
       <c r="C27" t="str">
-        <v>868741</v>
+        <v>857783</v>
       </c>
       <c r="E27" t="str">
-        <v>PEREZ FACUNDO MARTIN</v>
+        <v>PRICKETT SHANNON LYNN</v>
       </c>
       <c r="F27" s="1">
-        <v>46062</v>
+        <v>46048</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -5649,7 +5328,7 @@
         <v>Argentina</v>
       </c>
       <c r="O27" s="1">
-        <v>46063</v>
+        <v>46052</v>
       </c>
       <c r="P27" t="str">
         <v>1</v>
@@ -5658,34 +5337,34 @@
         <v>1</v>
       </c>
       <c r="R27">
-        <v>5128.24</v>
+        <v>23147.68</v>
       </c>
       <c r="S27">
         <v>0</v>
       </c>
       <c r="T27">
-        <v>5127.25</v>
+        <v>23147.69</v>
       </c>
       <c r="U27">
         <v>0</v>
       </c>
-      <c r="W27">
-        <v>0.99</v>
+      <c r="V27">
+        <v>-0.62</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>-0.62</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>-0.62</v>
       </c>
       <c r="AC27">
         <v>0</v>
       </c>
       <c r="AD27">
-        <v>0.99</v>
+        <v>0</v>
       </c>
       <c r="AE27">
-        <v>0.99</v>
+        <v>0</v>
       </c>
       <c r="AF27">
         <v>0</v>
@@ -5712,19 +5391,19 @@
         <v>0</v>
       </c>
       <c r="AR27">
-        <v>0</v>
+        <v>-0.62</v>
       </c>
       <c r="AS27">
-        <v>0</v>
+        <v>-0.62</v>
       </c>
       <c r="AT27">
         <v>0</v>
       </c>
       <c r="AU27">
-        <v>0.99</v>
+        <v>0</v>
       </c>
       <c r="AV27">
-        <v>0.99</v>
+        <v>0</v>
       </c>
       <c r="AW27">
         <v>0</v>
@@ -5739,19 +5418,19 @@
         <v>0</v>
       </c>
       <c r="BA27">
-        <v>0</v>
+        <v>-0.62</v>
       </c>
       <c r="BB27">
-        <v>0</v>
+        <v>-0.62</v>
       </c>
       <c r="BC27">
         <v>0</v>
       </c>
       <c r="BD27">
-        <v>0.99</v>
+        <v>0</v>
       </c>
       <c r="BE27">
-        <v>0.99</v>
+        <v>0</v>
       </c>
       <c r="BF27">
         <v>0</v>
@@ -5766,19 +5445,19 @@
         <v>0</v>
       </c>
       <c r="BJ27">
-        <v>0</v>
+        <v>-0.62</v>
       </c>
       <c r="BK27">
-        <v>0</v>
+        <v>-0.62</v>
       </c>
       <c r="BL27">
         <v>0</v>
       </c>
       <c r="BM27">
-        <v>0.99</v>
+        <v>0</v>
       </c>
       <c r="BN27">
-        <v>0.99</v>
+        <v>0</v>
       </c>
       <c r="BO27">
         <v>0</v>
@@ -5793,10 +5472,10 @@
         <v>0</v>
       </c>
       <c r="BS27">
-        <v>0</v>
+        <v>19.34</v>
       </c>
       <c r="BT27">
-        <v>11.84</v>
+        <v>41.27</v>
       </c>
       <c r="BU27">
         <v>0</v>
@@ -5808,13 +5487,13 @@
         <v>0</v>
       </c>
       <c r="BX27">
-        <v>11.84</v>
+        <v>60.61</v>
       </c>
       <c r="BY27">
-        <v>0</v>
+        <v>19.34</v>
       </c>
       <c r="BZ27">
-        <v>11.84</v>
+        <v>48.65</v>
       </c>
       <c r="CA27">
         <v>0</v>
@@ -5826,13 +5505,13 @@
         <v>0</v>
       </c>
       <c r="CD27">
-        <v>11.84</v>
+        <v>67.99</v>
       </c>
       <c r="CE27">
-        <v>0</v>
+        <v>19.34</v>
       </c>
       <c r="CF27">
-        <v>11.84</v>
+        <v>48.65</v>
       </c>
       <c r="CG27">
         <v>0</v>
@@ -5844,33 +5523,33 @@
         <v>0</v>
       </c>
       <c r="CJ27">
-        <v>11.84</v>
+        <v>67.99</v>
       </c>
       <c r="CK27">
-        <v>1433.0420969023</v>
+        <v>1425.46875</v>
       </c>
       <c r="CL27">
-        <v>1486.4063272368</v>
+        <v>1479.5653584171</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>1524903</v>
+        <v>1508138</v>
       </c>
       <c r="B28" t="str">
-        <v>1577315</v>
+        <v>163247</v>
       </c>
       <c r="C28" t="str">
-        <v>869420</v>
+        <v>859664</v>
       </c>
       <c r="E28" t="str">
-        <v>LAROTONDA LANZO LAUTARO</v>
+        <v>ASOCIACIÓN CIVIL SUMATORIA PARA UNA NUEVA ECONOMIA</v>
       </c>
       <c r="F28" s="1">
-        <v>46063</v>
+        <v>46050</v>
       </c>
       <c r="G28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28" t="str">
         <v>IFA 5767</v>
@@ -5882,13 +5561,13 @@
         <v>IFA</v>
       </c>
       <c r="K28" t="str">
-        <v>IFA 2</v>
+        <v>IFA 4</v>
       </c>
       <c r="N28" t="str">
         <v>Argentina</v>
       </c>
       <c r="O28" s="1">
-        <v>46077</v>
+        <v>46128</v>
       </c>
       <c r="P28" t="str">
         <v>1</v>
@@ -5897,19 +5576,19 @@
         <v>1</v>
       </c>
       <c r="R28">
-        <v>5000</v>
+        <v>7125.25</v>
       </c>
       <c r="S28">
         <v>0</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>7120.03</v>
       </c>
       <c r="U28">
         <v>0</v>
       </c>
       <c r="W28">
-        <v>5000</v>
+        <v>5.23</v>
       </c>
       <c r="AA28">
         <v>0</v>
@@ -5921,19 +5600,19 @@
         <v>0</v>
       </c>
       <c r="AD28">
-        <v>5000</v>
+        <v>5.23</v>
       </c>
       <c r="AE28">
-        <v>5000</v>
+        <v>5.23</v>
       </c>
       <c r="AF28">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>24.02</v>
       </c>
       <c r="AH28">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="AI28">
         <v>0</v>
@@ -5960,13 +5639,13 @@
         <v>0</v>
       </c>
       <c r="AU28">
-        <v>5000</v>
+        <v>5.23</v>
       </c>
       <c r="AV28">
-        <v>5000</v>
+        <v>5.23</v>
       </c>
       <c r="AW28">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="AX28">
         <v>0</v>
@@ -5987,13 +5666,13 @@
         <v>0</v>
       </c>
       <c r="BD28">
-        <v>5000</v>
+        <v>5.23</v>
       </c>
       <c r="BE28">
-        <v>5000</v>
+        <v>5.23</v>
       </c>
       <c r="BF28">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="BG28">
         <v>0</v>
@@ -6014,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="BM28">
-        <v>5000</v>
+        <v>5.23</v>
       </c>
       <c r="BN28">
-        <v>5000</v>
+        <v>5.23</v>
       </c>
       <c r="BO28">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="BP28">
         <v>0</v>
@@ -6031,28 +5710,82 @@
       <c r="BR28">
         <v>0</v>
       </c>
+      <c r="BS28">
+        <v>45.55</v>
+      </c>
+      <c r="BT28">
+        <v>9.78</v>
+      </c>
+      <c r="BU28">
+        <v>0</v>
+      </c>
+      <c r="BV28">
+        <v>0</v>
+      </c>
+      <c r="BW28">
+        <v>0</v>
+      </c>
+      <c r="BX28">
+        <v>55.33</v>
+      </c>
+      <c r="BY28">
+        <v>45.55</v>
+      </c>
+      <c r="BZ28">
+        <v>9.78</v>
+      </c>
+      <c r="CA28">
+        <v>0</v>
+      </c>
+      <c r="CB28">
+        <v>0</v>
+      </c>
+      <c r="CC28">
+        <v>0</v>
+      </c>
+      <c r="CD28">
+        <v>55.33</v>
+      </c>
+      <c r="CE28">
+        <v>45.55</v>
+      </c>
+      <c r="CF28">
+        <v>9.78</v>
+      </c>
+      <c r="CG28">
+        <v>0</v>
+      </c>
+      <c r="CH28">
+        <v>0</v>
+      </c>
+      <c r="CI28">
+        <v>0</v>
+      </c>
+      <c r="CJ28">
+        <v>55.33</v>
+      </c>
       <c r="CK28">
-        <v>1433.0420969023</v>
+        <v>1425.46875</v>
       </c>
       <c r="CL28">
-        <v>1486.4063272368</v>
+        <v>1479.5653584171</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>1538085</v>
+        <v>1513060</v>
       </c>
       <c r="B29" t="str">
-        <v>1586508</v>
+        <v>1568624</v>
       </c>
       <c r="C29" t="str">
-        <v>876241</v>
+        <v>862473</v>
       </c>
       <c r="E29" t="str">
-        <v>LUISELLO PAULA DENISE</v>
+        <v>ROTILI DIEGO HERNAN</v>
       </c>
       <c r="F29" s="1">
-        <v>46076</v>
+        <v>46055</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -6073,7 +5806,7 @@
         <v>Argentina</v>
       </c>
       <c r="O29" s="1">
-        <v>46084</v>
+        <v>46064</v>
       </c>
       <c r="P29" t="str">
         <v>1</v>
@@ -6082,37 +5815,40 @@
         <v>1</v>
       </c>
       <c r="R29">
-        <v>68872.26</v>
+        <v>10978.15</v>
       </c>
       <c r="S29">
-        <v>11904.55</v>
+        <v>8061.32</v>
       </c>
       <c r="T29">
-        <v>56920.93</v>
+        <v>2883.9</v>
       </c>
       <c r="U29">
         <v>0</v>
       </c>
       <c r="V29">
-        <v>58427.33</v>
+        <v>37683.72</v>
+      </c>
+      <c r="W29">
+        <v>0.82</v>
       </c>
       <c r="Y29">
-        <v>5.99</v>
+        <v>5.69</v>
       </c>
       <c r="AA29">
-        <v>58427.33</v>
+        <v>37683.72</v>
       </c>
       <c r="AB29">
-        <v>58427.33</v>
+        <v>37683.72</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>37683.72</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>0.82</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>0.82</v>
       </c>
       <c r="AF29">
         <v>0</v>
@@ -6139,19 +5875,19 @@
         <v>0</v>
       </c>
       <c r="AR29">
-        <v>58427.33</v>
+        <v>37683.72</v>
       </c>
       <c r="AS29">
-        <v>58427.33</v>
+        <v>37683.72</v>
       </c>
       <c r="AT29">
-        <v>0</v>
+        <v>37683.72</v>
       </c>
       <c r="AU29">
-        <v>0</v>
+        <v>0.82</v>
       </c>
       <c r="AV29">
-        <v>0</v>
+        <v>0.82</v>
       </c>
       <c r="AW29">
         <v>0</v>
@@ -6166,19 +5902,19 @@
         <v>0</v>
       </c>
       <c r="BA29">
-        <v>58427.33</v>
+        <v>37683.72</v>
       </c>
       <c r="BB29">
-        <v>58427.33</v>
+        <v>37683.72</v>
       </c>
       <c r="BC29">
-        <v>0</v>
+        <v>37683.72</v>
       </c>
       <c r="BD29">
-        <v>0</v>
+        <v>0.82</v>
       </c>
       <c r="BE29">
-        <v>0</v>
+        <v>0.82</v>
       </c>
       <c r="BF29">
         <v>0</v>
@@ -6193,19 +5929,19 @@
         <v>0</v>
       </c>
       <c r="BJ29">
-        <v>58427.33</v>
+        <v>37683.72</v>
       </c>
       <c r="BK29">
-        <v>58427.33</v>
+        <v>37683.72</v>
       </c>
       <c r="BL29">
-        <v>0</v>
+        <v>37683.72</v>
       </c>
       <c r="BM29">
-        <v>0</v>
+        <v>0.82</v>
       </c>
       <c r="BN29">
-        <v>0</v>
+        <v>0.82</v>
       </c>
       <c r="BO29">
         <v>0</v>
@@ -6220,10 +5956,10 @@
         <v>0</v>
       </c>
       <c r="BS29">
-        <v>70.87</v>
+        <v>29.51</v>
       </c>
       <c r="BT29">
-        <v>61.62</v>
+        <v>23.69</v>
       </c>
       <c r="BU29">
         <v>0</v>
@@ -6235,13 +5971,13 @@
         <v>0.01</v>
       </c>
       <c r="BX29">
-        <v>132.5</v>
+        <v>53.21</v>
       </c>
       <c r="BY29">
-        <v>70.87</v>
+        <v>45.71</v>
       </c>
       <c r="BZ29">
-        <v>61.62</v>
+        <v>28.35</v>
       </c>
       <c r="CA29">
         <v>0</v>
@@ -6253,13 +5989,13 @@
         <v>0.01</v>
       </c>
       <c r="CD29">
-        <v>132.5</v>
+        <v>74.07</v>
       </c>
       <c r="CE29">
-        <v>70.87</v>
+        <v>45.71</v>
       </c>
       <c r="CF29">
-        <v>61.62</v>
+        <v>28.35</v>
       </c>
       <c r="CG29">
         <v>0</v>
@@ -6271,27 +6007,30 @@
         <v>0.01</v>
       </c>
       <c r="CJ29">
-        <v>132.5</v>
+        <v>74.07</v>
       </c>
       <c r="CK29">
-        <v>1433.0420969023</v>
+        <v>1425.46875</v>
       </c>
       <c r="CL29">
-        <v>1486.4063272368</v>
+        <v>1479.5653584171</v>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>1557739</v>
-      </c>
-      <c r="D30" t="str">
-        <v>5000991</v>
+        <v>1523084</v>
+      </c>
+      <c r="B30" t="str">
+        <v>1576169</v>
+      </c>
+      <c r="C30" t="str">
+        <v>868572</v>
       </c>
       <c r="E30" t="str">
-        <v>BONFANTI DIEGO ALEJANDRO</v>
+        <v>IRRAZABAL JONAS</v>
       </c>
       <c r="F30" s="1">
-        <v>46097</v>
+        <v>46062</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -6305,34 +6044,109 @@
       <c r="J30" t="str">
         <v>IFA</v>
       </c>
+      <c r="K30" t="str">
+        <v>IFA 2</v>
+      </c>
       <c r="N30" t="str">
-        <v>Internacional</v>
+        <v>Argentina</v>
+      </c>
+      <c r="O30" s="1">
+        <v>46063</v>
       </c>
       <c r="P30" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>5028.26</v>
+      </c>
+      <c r="S30">
+        <v>0</v>
+      </c>
+      <c r="T30">
+        <v>5028.27</v>
+      </c>
+      <c r="U30">
+        <v>0</v>
+      </c>
+      <c r="BS30">
+        <v>0</v>
+      </c>
+      <c r="BT30">
+        <v>4.39</v>
+      </c>
+      <c r="BU30">
+        <v>0</v>
+      </c>
+      <c r="BV30">
+        <v>0</v>
+      </c>
+      <c r="BW30">
+        <v>0</v>
+      </c>
+      <c r="BX30">
+        <v>4.39</v>
+      </c>
+      <c r="BY30">
+        <v>0</v>
+      </c>
+      <c r="BZ30">
+        <v>4.68</v>
+      </c>
+      <c r="CA30">
+        <v>0</v>
+      </c>
+      <c r="CB30">
+        <v>0</v>
+      </c>
+      <c r="CC30">
+        <v>0</v>
+      </c>
+      <c r="CD30">
+        <v>4.68</v>
+      </c>
+      <c r="CE30">
+        <v>0</v>
+      </c>
+      <c r="CF30">
+        <v>4.68</v>
+      </c>
+      <c r="CG30">
+        <v>0</v>
+      </c>
+      <c r="CH30">
+        <v>0</v>
+      </c>
+      <c r="CI30">
+        <v>0</v>
+      </c>
+      <c r="CJ30">
+        <v>4.68</v>
+      </c>
+      <c r="CK30">
+        <v>1425.46875</v>
+      </c>
+      <c r="CL30">
+        <v>1479.5653584171</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <v>1567825</v>
+        <v>1523376</v>
       </c>
       <c r="B31" t="str">
-        <v>1607966</v>
+        <v>1576380</v>
       </c>
       <c r="C31" t="str">
-        <v>892025</v>
+        <v>868741</v>
       </c>
       <c r="E31" t="str">
-        <v>GATTO LUCAS GONZALO</v>
+        <v>PEREZ FACUNDO MARTIN</v>
       </c>
       <c r="F31" s="1">
-        <v>46111</v>
+        <v>46062</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -6347,13 +6161,13 @@
         <v>IFA</v>
       </c>
       <c r="K31" t="str">
-        <v>IFA 4</v>
+        <v>IFA 2</v>
       </c>
       <c r="N31" t="str">
         <v>Argentina</v>
       </c>
       <c r="O31" s="1">
-        <v>46118</v>
+        <v>46063</v>
       </c>
       <c r="P31" t="str">
         <v>1</v>
@@ -6362,19 +6176,19 @@
         <v>1</v>
       </c>
       <c r="R31">
-        <v>36.58</v>
+        <v>5140.41</v>
       </c>
       <c r="S31">
-        <v>29.34</v>
+        <v>0</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>5139.42</v>
       </c>
       <c r="U31">
         <v>0</v>
       </c>
       <c r="W31">
-        <v>7.24</v>
+        <v>0.99</v>
       </c>
       <c r="AA31">
         <v>0</v>
@@ -6386,19 +6200,19 @@
         <v>0</v>
       </c>
       <c r="AD31">
-        <v>7.24</v>
+        <v>0.99</v>
       </c>
       <c r="AE31">
-        <v>7.24</v>
+        <v>0.99</v>
       </c>
       <c r="AF31">
-        <v>7.24</v>
+        <v>0</v>
       </c>
       <c r="AG31">
         <v>0</v>
       </c>
       <c r="AH31">
-        <v>7.24</v>
+        <v>0</v>
       </c>
       <c r="AI31">
         <v>0</v>
@@ -6425,13 +6239,13 @@
         <v>0</v>
       </c>
       <c r="AU31">
-        <v>7.24</v>
+        <v>0.99</v>
       </c>
       <c r="AV31">
-        <v>7.24</v>
+        <v>0.99</v>
       </c>
       <c r="AW31">
-        <v>7.24</v>
+        <v>0</v>
       </c>
       <c r="AX31">
         <v>0</v>
@@ -6452,13 +6266,13 @@
         <v>0</v>
       </c>
       <c r="BD31">
-        <v>7.24</v>
+        <v>0.99</v>
       </c>
       <c r="BE31">
-        <v>7.24</v>
+        <v>0.99</v>
       </c>
       <c r="BF31">
-        <v>7.24</v>
+        <v>0</v>
       </c>
       <c r="BG31">
         <v>0</v>
@@ -6479,13 +6293,13 @@
         <v>0</v>
       </c>
       <c r="BM31">
-        <v>7.24</v>
+        <v>0.99</v>
       </c>
       <c r="BN31">
-        <v>7.24</v>
+        <v>0.99</v>
       </c>
       <c r="BO31">
-        <v>7.24</v>
+        <v>0</v>
       </c>
       <c r="BP31">
         <v>0</v>
@@ -6497,10 +6311,10 @@
         <v>0</v>
       </c>
       <c r="BS31">
-        <v>29.74</v>
+        <v>0</v>
       </c>
       <c r="BT31">
-        <v>0</v>
+        <v>15.11</v>
       </c>
       <c r="BU31">
         <v>0</v>
@@ -6512,13 +6326,13 @@
         <v>0</v>
       </c>
       <c r="BX31">
-        <v>29.74</v>
+        <v>15.11</v>
       </c>
       <c r="BY31">
-        <v>29.74</v>
+        <v>0</v>
       </c>
       <c r="BZ31">
-        <v>0</v>
+        <v>16.25</v>
       </c>
       <c r="CA31">
         <v>0</v>
@@ -6530,13 +6344,13 @@
         <v>0</v>
       </c>
       <c r="CD31">
-        <v>29.74</v>
+        <v>16.25</v>
       </c>
       <c r="CE31">
-        <v>29.74</v>
+        <v>0</v>
       </c>
       <c r="CF31">
-        <v>0</v>
+        <v>16.25</v>
       </c>
       <c r="CG31">
         <v>0</v>
@@ -6548,27 +6362,30 @@
         <v>0</v>
       </c>
       <c r="CJ31">
-        <v>29.74</v>
+        <v>16.25</v>
       </c>
       <c r="CK31">
-        <v>1433.0420969023</v>
+        <v>1425.46875</v>
       </c>
       <c r="CL31">
-        <v>1486.4063272368</v>
+        <v>1479.5653584171</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>1574965</v>
-      </c>
-      <c r="D32" t="str">
-        <v>5001104</v>
+        <v>1524903</v>
+      </c>
+      <c r="B32" t="str">
+        <v>1577315</v>
+      </c>
+      <c r="C32" t="str">
+        <v>869420</v>
       </c>
       <c r="E32" t="str">
-        <v>DEGANO GREGORIO MARTIN</v>
+        <v>LAROTONDA LANZO LAUTARO</v>
       </c>
       <c r="F32" s="1">
-        <v>46119</v>
+        <v>46063</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -6582,22 +6399,789 @@
       <c r="J32" t="str">
         <v>IFA</v>
       </c>
+      <c r="K32" t="str">
+        <v>IFA 2</v>
+      </c>
       <c r="N32" t="str">
+        <v>Argentina</v>
+      </c>
+      <c r="O32" s="1">
+        <v>46077</v>
+      </c>
+      <c r="P32" t="str">
+        <v>1</v>
+      </c>
+      <c r="Q32">
+        <v>1</v>
+      </c>
+      <c r="R32">
+        <v>5039.78</v>
+      </c>
+      <c r="S32">
+        <v>4589.57</v>
+      </c>
+      <c r="T32">
+        <v>450.69</v>
+      </c>
+      <c r="U32">
+        <v>0</v>
+      </c>
+      <c r="V32">
+        <v>-157.74</v>
+      </c>
+      <c r="W32">
+        <v>-0.38</v>
+      </c>
+      <c r="AA32">
+        <v>-157.74</v>
+      </c>
+      <c r="AB32">
+        <v>-157.74</v>
+      </c>
+      <c r="AC32">
+        <v>0</v>
+      </c>
+      <c r="AD32">
+        <v>-0.38</v>
+      </c>
+      <c r="AE32">
+        <v>-0.38</v>
+      </c>
+      <c r="AF32">
+        <v>0</v>
+      </c>
+      <c r="AG32">
+        <v>0</v>
+      </c>
+      <c r="AH32">
+        <v>-0.38</v>
+      </c>
+      <c r="AI32">
+        <v>0</v>
+      </c>
+      <c r="AJ32">
+        <v>0</v>
+      </c>
+      <c r="AK32">
+        <v>0</v>
+      </c>
+      <c r="AL32">
+        <v>0</v>
+      </c>
+      <c r="AM32">
+        <v>0</v>
+      </c>
+      <c r="AR32">
+        <v>-157.74</v>
+      </c>
+      <c r="AS32">
+        <v>-157.74</v>
+      </c>
+      <c r="AT32">
+        <v>0</v>
+      </c>
+      <c r="AU32">
+        <v>-0.38</v>
+      </c>
+      <c r="AV32">
+        <v>-0.38</v>
+      </c>
+      <c r="AW32">
+        <v>0</v>
+      </c>
+      <c r="AX32">
+        <v>0</v>
+      </c>
+      <c r="AY32">
+        <v>0</v>
+      </c>
+      <c r="AZ32">
+        <v>0</v>
+      </c>
+      <c r="BA32">
+        <v>-157.74</v>
+      </c>
+      <c r="BB32">
+        <v>-157.74</v>
+      </c>
+      <c r="BC32">
+        <v>0</v>
+      </c>
+      <c r="BD32">
+        <v>-0.38</v>
+      </c>
+      <c r="BE32">
+        <v>-0.38</v>
+      </c>
+      <c r="BF32">
+        <v>0</v>
+      </c>
+      <c r="BG32">
+        <v>0</v>
+      </c>
+      <c r="BH32">
+        <v>0</v>
+      </c>
+      <c r="BI32">
+        <v>0</v>
+      </c>
+      <c r="BJ32">
+        <v>-157.74</v>
+      </c>
+      <c r="BK32">
+        <v>-157.74</v>
+      </c>
+      <c r="BL32">
+        <v>0</v>
+      </c>
+      <c r="BM32">
+        <v>-0.38</v>
+      </c>
+      <c r="BN32">
+        <v>-0.38</v>
+      </c>
+      <c r="BO32">
+        <v>0</v>
+      </c>
+      <c r="BP32">
+        <v>0</v>
+      </c>
+      <c r="BQ32">
+        <v>0</v>
+      </c>
+      <c r="BR32">
+        <v>0</v>
+      </c>
+      <c r="BS32">
+        <v>33.88</v>
+      </c>
+      <c r="BT32">
+        <v>0.08</v>
+      </c>
+      <c r="BU32">
+        <v>0</v>
+      </c>
+      <c r="BV32">
+        <v>0</v>
+      </c>
+      <c r="BW32">
+        <v>0</v>
+      </c>
+      <c r="BX32">
+        <v>33.96</v>
+      </c>
+      <c r="BY32">
+        <v>33.88</v>
+      </c>
+      <c r="BZ32">
+        <v>0.08</v>
+      </c>
+      <c r="CA32">
+        <v>0</v>
+      </c>
+      <c r="CB32">
+        <v>0</v>
+      </c>
+      <c r="CC32">
+        <v>0</v>
+      </c>
+      <c r="CD32">
+        <v>33.96</v>
+      </c>
+      <c r="CE32">
+        <v>33.88</v>
+      </c>
+      <c r="CF32">
+        <v>0.08</v>
+      </c>
+      <c r="CG32">
+        <v>0</v>
+      </c>
+      <c r="CH32">
+        <v>0</v>
+      </c>
+      <c r="CI32">
+        <v>0</v>
+      </c>
+      <c r="CJ32">
+        <v>33.96</v>
+      </c>
+      <c r="CK32">
+        <v>1425.46875</v>
+      </c>
+      <c r="CL32">
+        <v>1479.5653584171</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>1538085</v>
+      </c>
+      <c r="B33" t="str">
+        <v>1586508</v>
+      </c>
+      <c r="C33" t="str">
+        <v>876241</v>
+      </c>
+      <c r="E33" t="str">
+        <v>LUISELLO PAULA DENISE</v>
+      </c>
+      <c r="F33" s="1">
+        <v>46076</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33" t="str">
+        <v>IFA 5767</v>
+      </c>
+      <c r="I33" t="str">
+        <v>Vicien/DV - Marketing - IFA</v>
+      </c>
+      <c r="J33" t="str">
+        <v>IFA</v>
+      </c>
+      <c r="K33" t="str">
+        <v>IFA 3</v>
+      </c>
+      <c r="N33" t="str">
+        <v>Argentina</v>
+      </c>
+      <c r="O33" s="1">
+        <v>46084</v>
+      </c>
+      <c r="P33" t="str">
+        <v>1</v>
+      </c>
+      <c r="Q33">
+        <v>1</v>
+      </c>
+      <c r="R33">
+        <v>69350.62</v>
+      </c>
+      <c r="S33">
+        <v>12967.75</v>
+      </c>
+      <c r="T33">
+        <v>56332.26</v>
+      </c>
+      <c r="U33">
+        <v>0</v>
+      </c>
+      <c r="V33">
+        <v>56626.42</v>
+      </c>
+      <c r="W33">
+        <v>4.91</v>
+      </c>
+      <c r="Y33">
+        <v>5.99</v>
+      </c>
+      <c r="AA33">
+        <v>56626.42</v>
+      </c>
+      <c r="AB33">
+        <v>56626.42</v>
+      </c>
+      <c r="AC33">
+        <v>0</v>
+      </c>
+      <c r="AD33">
+        <v>4.91</v>
+      </c>
+      <c r="AE33">
+        <v>4.91</v>
+      </c>
+      <c r="AF33">
+        <v>0</v>
+      </c>
+      <c r="AG33">
+        <v>0</v>
+      </c>
+      <c r="AH33">
+        <v>0</v>
+      </c>
+      <c r="AI33">
+        <v>0</v>
+      </c>
+      <c r="AJ33">
+        <v>0</v>
+      </c>
+      <c r="AK33">
+        <v>0</v>
+      </c>
+      <c r="AL33">
+        <v>0</v>
+      </c>
+      <c r="AM33">
+        <v>0</v>
+      </c>
+      <c r="AR33">
+        <v>56626.42</v>
+      </c>
+      <c r="AS33">
+        <v>56626.42</v>
+      </c>
+      <c r="AT33">
+        <v>0</v>
+      </c>
+      <c r="AU33">
+        <v>4.91</v>
+      </c>
+      <c r="AV33">
+        <v>4.91</v>
+      </c>
+      <c r="AW33">
+        <v>0</v>
+      </c>
+      <c r="AX33">
+        <v>0</v>
+      </c>
+      <c r="AY33">
+        <v>0</v>
+      </c>
+      <c r="AZ33">
+        <v>0</v>
+      </c>
+      <c r="BA33">
+        <v>56626.42</v>
+      </c>
+      <c r="BB33">
+        <v>56626.42</v>
+      </c>
+      <c r="BC33">
+        <v>0</v>
+      </c>
+      <c r="BD33">
+        <v>4.91</v>
+      </c>
+      <c r="BE33">
+        <v>4.91</v>
+      </c>
+      <c r="BF33">
+        <v>0</v>
+      </c>
+      <c r="BG33">
+        <v>0</v>
+      </c>
+      <c r="BH33">
+        <v>0</v>
+      </c>
+      <c r="BI33">
+        <v>0</v>
+      </c>
+      <c r="BJ33">
+        <v>56626.42</v>
+      </c>
+      <c r="BK33">
+        <v>56626.42</v>
+      </c>
+      <c r="BL33">
+        <v>0</v>
+      </c>
+      <c r="BM33">
+        <v>4.91</v>
+      </c>
+      <c r="BN33">
+        <v>4.91</v>
+      </c>
+      <c r="BO33">
+        <v>0</v>
+      </c>
+      <c r="BP33">
+        <v>0</v>
+      </c>
+      <c r="BQ33">
+        <v>0</v>
+      </c>
+      <c r="BR33">
+        <v>0</v>
+      </c>
+      <c r="BS33">
+        <v>75.02</v>
+      </c>
+      <c r="BT33">
+        <v>93.06</v>
+      </c>
+      <c r="BU33">
+        <v>0</v>
+      </c>
+      <c r="BV33">
+        <v>0</v>
+      </c>
+      <c r="BW33">
+        <v>0.01</v>
+      </c>
+      <c r="BX33">
+        <v>168.09</v>
+      </c>
+      <c r="BY33">
+        <v>75.02</v>
+      </c>
+      <c r="BZ33">
+        <v>93.06</v>
+      </c>
+      <c r="CA33">
+        <v>0</v>
+      </c>
+      <c r="CB33">
+        <v>0</v>
+      </c>
+      <c r="CC33">
+        <v>0.01</v>
+      </c>
+      <c r="CD33">
+        <v>168.09</v>
+      </c>
+      <c r="CE33">
+        <v>75.02</v>
+      </c>
+      <c r="CF33">
+        <v>93.06</v>
+      </c>
+      <c r="CG33">
+        <v>0</v>
+      </c>
+      <c r="CH33">
+        <v>0</v>
+      </c>
+      <c r="CI33">
+        <v>0.01</v>
+      </c>
+      <c r="CJ33">
+        <v>168.09</v>
+      </c>
+      <c r="CK33">
+        <v>1425.46875</v>
+      </c>
+      <c r="CL33">
+        <v>1479.5653584171</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>1557739</v>
+      </c>
+      <c r="D34" t="str">
+        <v>5000991</v>
+      </c>
+      <c r="E34" t="str">
+        <v>BONFANTI DIEGO ALEJANDRO</v>
+      </c>
+      <c r="F34" s="1">
+        <v>46097</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34" t="str">
+        <v>IFA 5767</v>
+      </c>
+      <c r="I34" t="str">
+        <v>Vicien/DV - Marketing - IFA</v>
+      </c>
+      <c r="J34" t="str">
+        <v>IFA</v>
+      </c>
+      <c r="K34" t="str">
+        <v>Diferenciado</v>
+      </c>
+      <c r="N34" t="str">
         <v>Internacional</v>
       </c>
-      <c r="P32" t="str">
-        <v>0</v>
-      </c>
-      <c r="Q32">
-        <v>0</v>
-      </c>
-      <c r="R32">
+      <c r="P34" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q34">
+        <v>0</v>
+      </c>
+      <c r="R34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>1567825</v>
+      </c>
+      <c r="B35" t="str">
+        <v>1607966</v>
+      </c>
+      <c r="C35" t="str">
+        <v>892025</v>
+      </c>
+      <c r="E35" t="str">
+        <v>GATTO LUCAS GONZALO</v>
+      </c>
+      <c r="F35" s="1">
+        <v>46111</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35" t="str">
+        <v>IFA 5767</v>
+      </c>
+      <c r="I35" t="str">
+        <v>Vicien/DV - Marketing - IFA</v>
+      </c>
+      <c r="J35" t="str">
+        <v>IFA</v>
+      </c>
+      <c r="K35" t="str">
+        <v>IFA 4</v>
+      </c>
+      <c r="N35" t="str">
+        <v>Argentina</v>
+      </c>
+      <c r="O35" s="1">
+        <v>46118</v>
+      </c>
+      <c r="P35" t="str">
+        <v>1</v>
+      </c>
+      <c r="Q35">
+        <v>1</v>
+      </c>
+      <c r="R35">
+        <v>1070.77</v>
+      </c>
+      <c r="S35">
+        <v>1067.82</v>
+      </c>
+      <c r="T35">
+        <v>0</v>
+      </c>
+      <c r="U35">
+        <v>0</v>
+      </c>
+      <c r="W35">
+        <v>2.95</v>
+      </c>
+      <c r="AA35">
+        <v>0</v>
+      </c>
+      <c r="AB35">
+        <v>0</v>
+      </c>
+      <c r="AC35">
+        <v>0</v>
+      </c>
+      <c r="AD35">
+        <v>2.95</v>
+      </c>
+      <c r="AE35">
+        <v>2.95</v>
+      </c>
+      <c r="AF35">
+        <v>2.95</v>
+      </c>
+      <c r="AG35">
+        <v>0</v>
+      </c>
+      <c r="AH35">
+        <v>2.95</v>
+      </c>
+      <c r="AI35">
+        <v>0</v>
+      </c>
+      <c r="AJ35">
+        <v>0</v>
+      </c>
+      <c r="AK35">
+        <v>0</v>
+      </c>
+      <c r="AL35">
+        <v>0</v>
+      </c>
+      <c r="AM35">
+        <v>0</v>
+      </c>
+      <c r="AR35">
+        <v>0</v>
+      </c>
+      <c r="AS35">
+        <v>0</v>
+      </c>
+      <c r="AT35">
+        <v>0</v>
+      </c>
+      <c r="AU35">
+        <v>2.95</v>
+      </c>
+      <c r="AV35">
+        <v>2.95</v>
+      </c>
+      <c r="AW35">
+        <v>2.95</v>
+      </c>
+      <c r="AX35">
+        <v>0</v>
+      </c>
+      <c r="AY35">
+        <v>0</v>
+      </c>
+      <c r="AZ35">
+        <v>0</v>
+      </c>
+      <c r="BA35">
+        <v>0</v>
+      </c>
+      <c r="BB35">
+        <v>0</v>
+      </c>
+      <c r="BC35">
+        <v>0</v>
+      </c>
+      <c r="BD35">
+        <v>2.95</v>
+      </c>
+      <c r="BE35">
+        <v>2.95</v>
+      </c>
+      <c r="BF35">
+        <v>2.95</v>
+      </c>
+      <c r="BG35">
+        <v>0</v>
+      </c>
+      <c r="BH35">
+        <v>0</v>
+      </c>
+      <c r="BI35">
+        <v>0</v>
+      </c>
+      <c r="BJ35">
+        <v>0</v>
+      </c>
+      <c r="BK35">
+        <v>0</v>
+      </c>
+      <c r="BL35">
+        <v>0</v>
+      </c>
+      <c r="BM35">
+        <v>2.95</v>
+      </c>
+      <c r="BN35">
+        <v>2.95</v>
+      </c>
+      <c r="BO35">
+        <v>2.95</v>
+      </c>
+      <c r="BP35">
+        <v>0</v>
+      </c>
+      <c r="BQ35">
+        <v>0</v>
+      </c>
+      <c r="BR35">
+        <v>0</v>
+      </c>
+      <c r="BS35">
+        <v>57.1</v>
+      </c>
+      <c r="BT35">
+        <v>0</v>
+      </c>
+      <c r="BU35">
+        <v>0</v>
+      </c>
+      <c r="BV35">
+        <v>0</v>
+      </c>
+      <c r="BW35">
+        <v>0</v>
+      </c>
+      <c r="BX35">
+        <v>57.1</v>
+      </c>
+      <c r="BY35">
+        <v>57.1</v>
+      </c>
+      <c r="BZ35">
+        <v>0</v>
+      </c>
+      <c r="CA35">
+        <v>0</v>
+      </c>
+      <c r="CB35">
+        <v>0</v>
+      </c>
+      <c r="CC35">
+        <v>0</v>
+      </c>
+      <c r="CD35">
+        <v>57.1</v>
+      </c>
+      <c r="CE35">
+        <v>57.1</v>
+      </c>
+      <c r="CF35">
+        <v>0</v>
+      </c>
+      <c r="CG35">
+        <v>0</v>
+      </c>
+      <c r="CH35">
+        <v>0</v>
+      </c>
+      <c r="CI35">
+        <v>0</v>
+      </c>
+      <c r="CJ35">
+        <v>57.1</v>
+      </c>
+      <c r="CK35">
+        <v>1425.46875</v>
+      </c>
+      <c r="CL35">
+        <v>1479.5653584171</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>1574965</v>
+      </c>
+      <c r="D36" t="str">
+        <v>5001104</v>
+      </c>
+      <c r="E36" t="str">
+        <v>DEGANO GREGORIO MARTIN</v>
+      </c>
+      <c r="F36" s="1">
+        <v>46119</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36" t="str">
+        <v>IFA 5767</v>
+      </c>
+      <c r="I36" t="str">
+        <v>Vicien/DV - Marketing - IFA</v>
+      </c>
+      <c r="J36" t="str">
+        <v>IFA</v>
+      </c>
+      <c r="K36" t="str">
+        <v>Diferenciado</v>
+      </c>
+      <c r="N36" t="str">
+        <v>Internacional</v>
+      </c>
+      <c r="P36" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q36">
+        <v>0</v>
+      </c>
+      <c r="R36">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:CL32"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:CL36"/>
   </ignoredErrors>
 </worksheet>
 </file>